--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55a11f37d9971d4c/! 1.Concordia/!z - COOP director/! PYTHON/WEB_TOOL/PY_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{4D67A9E0-1A6E-4B88-8F82-27FE4B21142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{651CBF57-21B9-4B5C-9BC6-DAC8F062AA3E}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{4D67A9E0-1A6E-4B88-8F82-27FE4B21142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2301FAD7-5A21-4756-A15C-1C1C76A5A3DE}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="343">
   <si>
     <t>ENCS 282</t>
   </si>
@@ -969,9 +969,6 @@
     <t>GRAD</t>
   </si>
   <si>
-    <t>If not already COOP planned as a WT (if not written W-1, W-2 or W-3 above), only students with an internship in hand (including WT extension) are accepted</t>
-  </si>
-  <si>
     <t>GRAD 4001</t>
   </si>
   <si>
@@ -1066,6 +1063,12 @@
   </si>
   <si>
     <t>8-credit generic course</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
   </si>
 </sst>
 </file>
@@ -10553,10 +10556,10 @@
         <v>307</v>
       </c>
       <c r="B252" s="56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C252" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D252" s="16">
         <v>4</v>
@@ -10579,10 +10582,10 @@
         <v>307</v>
       </c>
       <c r="B253" s="56" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C253" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D253" s="16">
         <v>4</v>
@@ -10605,10 +10608,10 @@
         <v>307</v>
       </c>
       <c r="B254" s="56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C254" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D254" s="16">
         <v>4</v>
@@ -10631,10 +10634,10 @@
         <v>307</v>
       </c>
       <c r="B255" s="56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C255" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D255" s="16">
         <v>4</v>
@@ -10657,10 +10660,10 @@
         <v>307</v>
       </c>
       <c r="B256" s="56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C256" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D256" s="16">
         <v>4</v>
@@ -10683,10 +10686,10 @@
         <v>307</v>
       </c>
       <c r="B257" s="56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C257" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D257" s="16">
         <v>4</v>
@@ -10709,10 +10712,10 @@
         <v>307</v>
       </c>
       <c r="B258" s="56" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C258" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D258" s="16">
         <v>4</v>
@@ -10735,10 +10738,10 @@
         <v>307</v>
       </c>
       <c r="B259" s="56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C259" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D259" s="16">
         <v>4</v>
@@ -10761,10 +10764,10 @@
         <v>307</v>
       </c>
       <c r="B260" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C260" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D260" s="16">
         <v>4</v>
@@ -10787,10 +10790,10 @@
         <v>307</v>
       </c>
       <c r="B261" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C261" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D261" s="16">
         <v>4</v>
@@ -10813,10 +10816,10 @@
         <v>307</v>
       </c>
       <c r="B262" s="56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C262" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D262" s="16">
         <v>4</v>
@@ -10839,10 +10842,10 @@
         <v>305</v>
       </c>
       <c r="B263" s="56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C263" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D263" s="16">
         <v>4</v>
@@ -10865,10 +10868,10 @@
         <v>305</v>
       </c>
       <c r="B264" s="56" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C264" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D264" s="16">
         <v>4</v>
@@ -10891,10 +10894,10 @@
         <v>305</v>
       </c>
       <c r="B265" s="56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C265" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D265" s="16">
         <v>4</v>
@@ -10917,10 +10920,10 @@
         <v>305</v>
       </c>
       <c r="B266" s="56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C266" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D266" s="16">
         <v>4</v>
@@ -10943,10 +10946,10 @@
         <v>305</v>
       </c>
       <c r="B267" s="56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C267" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D267" s="16">
         <v>4</v>
@@ -10969,10 +10972,10 @@
         <v>305</v>
       </c>
       <c r="B268" s="56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C268" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D268" s="16">
         <v>4</v>
@@ -10995,10 +10998,10 @@
         <v>305</v>
       </c>
       <c r="B269" s="56" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C269" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D269" s="16">
         <v>4</v>
@@ -11021,10 +11024,10 @@
         <v>305</v>
       </c>
       <c r="B270" s="56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C270" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D270" s="16">
         <v>4</v>
@@ -11047,10 +11050,10 @@
         <v>305</v>
       </c>
       <c r="B271" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C271" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D271" s="16">
         <v>4</v>
@@ -11073,10 +11076,10 @@
         <v>305</v>
       </c>
       <c r="B272" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C272" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D272" s="16">
         <v>4</v>
@@ -11099,10 +11102,10 @@
         <v>305</v>
       </c>
       <c r="B273" s="56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C273" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D273" s="16">
         <v>4</v>
@@ -11125,10 +11128,10 @@
         <v>306</v>
       </c>
       <c r="B274" s="56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C274" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D274" s="16">
         <v>4</v>
@@ -11151,10 +11154,10 @@
         <v>306</v>
       </c>
       <c r="B275" s="56" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C275" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D275" s="16">
         <v>4</v>
@@ -11177,10 +11180,10 @@
         <v>306</v>
       </c>
       <c r="B276" s="56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C276" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D276" s="16">
         <v>4</v>
@@ -11203,10 +11206,10 @@
         <v>306</v>
       </c>
       <c r="B277" s="56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C277" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D277" s="16">
         <v>4</v>
@@ -11229,10 +11232,10 @@
         <v>306</v>
       </c>
       <c r="B278" s="56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C278" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D278" s="16">
         <v>4</v>
@@ -11255,10 +11258,10 @@
         <v>306</v>
       </c>
       <c r="B279" s="56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C279" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D279" s="16">
         <v>4</v>
@@ -11281,10 +11284,10 @@
         <v>306</v>
       </c>
       <c r="B280" s="56" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C280" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D280" s="16">
         <v>4</v>
@@ -11307,10 +11310,10 @@
         <v>306</v>
       </c>
       <c r="B281" s="56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C281" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D281" s="16">
         <v>4</v>
@@ -11333,10 +11336,10 @@
         <v>306</v>
       </c>
       <c r="B282" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C282" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D282" s="16">
         <v>4</v>
@@ -11359,10 +11362,10 @@
         <v>306</v>
       </c>
       <c r="B283" s="56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D283" s="16">
         <v>4</v>
@@ -11385,10 +11388,10 @@
         <v>306</v>
       </c>
       <c r="B284" s="56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C284" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D284" s="16">
         <v>4</v>
@@ -11411,10 +11414,10 @@
         <v>305</v>
       </c>
       <c r="B285" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C285" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D285" s="16">
         <v>5</v>
@@ -11437,10 +11440,10 @@
         <v>305</v>
       </c>
       <c r="B286" s="56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C286" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D286" s="16">
         <v>5</v>
@@ -11463,10 +11466,10 @@
         <v>305</v>
       </c>
       <c r="B287" s="56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C287" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D287" s="16">
         <v>5</v>
@@ -11489,10 +11492,10 @@
         <v>306</v>
       </c>
       <c r="B288" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C288" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D288" s="16">
         <v>5</v>
@@ -11515,10 +11518,10 @@
         <v>306</v>
       </c>
       <c r="B289" s="56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C289" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D289" s="16">
         <v>5</v>
@@ -11541,10 +11544,10 @@
         <v>306</v>
       </c>
       <c r="B290" s="56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C290" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D290" s="16">
         <v>5</v>
@@ -11567,10 +11570,10 @@
         <v>305</v>
       </c>
       <c r="B291" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C291" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D291" s="16">
         <v>5</v>
@@ -11593,10 +11596,10 @@
         <v>307</v>
       </c>
       <c r="B292" s="56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C292" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D292" s="16">
         <v>5</v>
@@ -11619,10 +11622,10 @@
         <v>307</v>
       </c>
       <c r="B293" s="56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C293" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D293" s="16">
         <v>5</v>
@@ -11645,10 +11648,10 @@
         <v>305</v>
       </c>
       <c r="B294" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C294" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D294" s="16">
         <v>6</v>
@@ -11671,10 +11674,10 @@
         <v>305</v>
       </c>
       <c r="B295" s="56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C295" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D295" s="16">
         <v>6</v>
@@ -11697,10 +11700,10 @@
         <v>305</v>
       </c>
       <c r="B296" s="56" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C296" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D296" s="16">
         <v>6</v>
@@ -11723,10 +11726,10 @@
         <v>306</v>
       </c>
       <c r="B297" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C297" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D297" s="16">
         <v>6</v>
@@ -11749,10 +11752,10 @@
         <v>306</v>
       </c>
       <c r="B298" s="56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C298" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D298" s="16">
         <v>6</v>
@@ -11775,10 +11778,10 @@
         <v>306</v>
       </c>
       <c r="B299" s="56" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C299" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D299" s="16">
         <v>6</v>
@@ -11801,10 +11804,10 @@
         <v>305</v>
       </c>
       <c r="B300" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D300" s="16">
         <v>6</v>
@@ -11827,10 +11830,10 @@
         <v>307</v>
       </c>
       <c r="B301" s="56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D301" s="16">
         <v>6</v>
@@ -11853,10 +11856,10 @@
         <v>307</v>
       </c>
       <c r="B302" s="56" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D302" s="16">
         <v>6</v>
@@ -11879,10 +11882,10 @@
         <v>305</v>
       </c>
       <c r="B303" s="56" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D303" s="16">
         <v>1</v>
@@ -11905,10 +11908,10 @@
         <v>305</v>
       </c>
       <c r="B304" s="56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D304" s="16">
         <v>1</v>
@@ -11931,10 +11934,10 @@
         <v>305</v>
       </c>
       <c r="B305" s="56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D305" s="16">
         <v>1</v>
@@ -11957,10 +11960,10 @@
         <v>306</v>
       </c>
       <c r="B306" s="56" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C306" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D306" s="16">
         <v>1</v>
@@ -11983,10 +11986,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C307" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D307" s="16">
         <v>1</v>
@@ -12009,10 +12012,10 @@
         <v>306</v>
       </c>
       <c r="B308" s="56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C308" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D308" s="16">
         <v>1</v>
@@ -12035,10 +12038,10 @@
         <v>305</v>
       </c>
       <c r="B309" s="56" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C309" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D309" s="16">
         <v>1</v>
@@ -12061,10 +12064,10 @@
         <v>307</v>
       </c>
       <c r="B310" s="56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C310" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D310" s="16">
         <v>1</v>
@@ -12087,10 +12090,10 @@
         <v>307</v>
       </c>
       <c r="B311" s="56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C311" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D311" s="16">
         <v>1</v>
@@ -12113,10 +12116,10 @@
         <v>305</v>
       </c>
       <c r="B312" s="56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C312" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D312" s="16">
         <v>7</v>
@@ -12139,10 +12142,10 @@
         <v>305</v>
       </c>
       <c r="B313" s="56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C313" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D313" s="16">
         <v>7</v>
@@ -12165,10 +12168,10 @@
         <v>305</v>
       </c>
       <c r="B314" s="56" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C314" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D314" s="16">
         <v>7</v>
@@ -12191,10 +12194,10 @@
         <v>306</v>
       </c>
       <c r="B315" s="56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C315" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D315" s="16">
         <v>7</v>
@@ -12217,10 +12220,10 @@
         <v>306</v>
       </c>
       <c r="B316" s="56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C316" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D316" s="16">
         <v>7</v>
@@ -12243,10 +12246,10 @@
         <v>306</v>
       </c>
       <c r="B317" s="56" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C317" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D317" s="16">
         <v>7</v>
@@ -12269,10 +12272,10 @@
         <v>305</v>
       </c>
       <c r="B318" s="56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C318" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D318" s="16">
         <v>7</v>
@@ -12295,10 +12298,10 @@
         <v>307</v>
       </c>
       <c r="B319" s="56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D319" s="16">
         <v>7</v>
@@ -12321,10 +12324,10 @@
         <v>307</v>
       </c>
       <c r="B320" s="56" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C320" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D320" s="16">
         <v>7</v>
@@ -12347,10 +12350,10 @@
         <v>305</v>
       </c>
       <c r="B321" s="56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C321" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D321" s="16">
         <v>8</v>
@@ -12373,10 +12376,10 @@
         <v>305</v>
       </c>
       <c r="B322" s="56" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C322" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D322" s="16">
         <v>8</v>
@@ -12399,10 +12402,10 @@
         <v>305</v>
       </c>
       <c r="B323" s="56" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C323" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D323" s="16">
         <v>8</v>
@@ -12425,10 +12428,10 @@
         <v>306</v>
       </c>
       <c r="B324" s="56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C324" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D324" s="16">
         <v>8</v>
@@ -12451,10 +12454,10 @@
         <v>306</v>
       </c>
       <c r="B325" s="56" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C325" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D325" s="16">
         <v>8</v>
@@ -12477,10 +12480,10 @@
         <v>306</v>
       </c>
       <c r="B326" s="56" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C326" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D326" s="16">
         <v>8</v>
@@ -12503,10 +12506,10 @@
         <v>305</v>
       </c>
       <c r="B327" s="56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C327" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D327" s="16">
         <v>8</v>
@@ -12529,10 +12532,10 @@
         <v>307</v>
       </c>
       <c r="B328" s="56" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C328" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D328" s="16">
         <v>8</v>
@@ -12555,10 +12558,10 @@
         <v>307</v>
       </c>
       <c r="B329" s="56" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C329" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D329" s="16">
         <v>8</v>
@@ -12597,7 +12600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D01CF3-C1DE-477D-B94F-245AB2B987BD}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="20" customWidth="1"/>
@@ -12650,7 +12653,7 @@
         <v>161</v>
       </c>
       <c r="G2" s="116" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>292</v>
@@ -12727,6 +12730,26 @@
       </c>
       <c r="H7" s="20" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="117">
+        <v>46055</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="G8" s="116" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55a11f37d9971d4c/! 1.Concordia/!z - COOP director/! PYTHON/WEB_TOOL/PY_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90A3015-C8BC-4376-8435-A37024B56A37}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5844D911-115F-4772-86DE-5C14D574F1AC}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38475" yWindow="0" windowWidth="19380" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
     <sheet name="restrictions" sheetId="2" r:id="rId2"/>
-    <sheet name="Sequences" sheetId="3" r:id="rId3"/>
+    <sheet name="Programs" sheetId="4" r:id="rId3"/>
+    <sheet name="Sequences" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Coursses!$A$1:$K$328</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sequences!$A$1:$F$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sequences!$A$1:$F$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="450">
   <si>
     <t>Date after which takes effect</t>
   </si>
@@ -1377,13 +1378,25 @@
   </si>
   <si>
     <t>Students admitted to Engineering before Fall 2023 should consult the March 2023 Curriculum Change Letter for ongoing transition measures in Basic and Natural Science.</t>
+  </si>
+  <si>
+    <t>Type of credits</t>
+  </si>
+  <si>
+    <t>no of credits</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>UGRD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1427,6 +1440,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1574,7 +1593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1909,6 +1928,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12043,6 +12063,249 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1B670F-7286-4413-AA18-FAB437017A91}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C2" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" s="118" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C5" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C6" s="118" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="118" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9">
+        <f>38.75+50.25</f>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C11" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C12" s="118" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <f>38.75+54.25</f>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C14" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C15" s="118" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15">
+        <f>38.75+49.5</f>
+        <v>88.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16">
+        <v>4.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55a11f37d9971d4c/! 1.Concordia/!z - COOP director/! PYTHON/WEB_TOOL/PY_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5844D911-115F-4772-86DE-5C14D574F1AC}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{926D6C7C-2981-4C6A-BE1D-77F1F1A1E600}"/>
   <bookViews>
-    <workbookView xWindow="-38475" yWindow="0" windowWidth="19380" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3143" uniqueCount="451">
   <si>
     <t>Date after which takes effect</t>
   </si>
@@ -1390,6 +1390,9 @@
   </si>
   <si>
     <t>UGRD</t>
+  </si>
+  <si>
+    <t>level</t>
   </si>
 </sst>
 </file>
@@ -11901,7 +11904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="20" customWidth="1"/>
@@ -11912,7 +11915,7 @@
     <col min="9" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -11937,8 +11940,11 @@
       <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117">
         <v>46055</v>
       </c>
@@ -11960,8 +11966,11 @@
       <c r="H2" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
@@ -11974,8 +11983,11 @@
       <c r="H3" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E4" s="20" t="s">
         <v>10</v>
       </c>
@@ -11985,8 +11997,11 @@
       <c r="H4" s="20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
@@ -11999,8 +12014,11 @@
       <c r="H5" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
         <v>20</v>
       </c>
@@ -12013,8 +12031,11 @@
       <c r="H6" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>13</v>
       </c>
@@ -12033,8 +12054,11 @@
       <c r="H7" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="117">
         <v>46055</v>
       </c>
@@ -12055,6 +12079,9 @@
       </c>
       <c r="H8" s="20" t="s">
         <v>8</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55a11f37d9971d4c/! 1.Concordia/!z - COOP director/! PYTHON/WEB_TOOL/PY_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{926D6C7C-2981-4C6A-BE1D-77F1F1A1E600}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5844D911-115F-4772-86DE-5C14D574F1AC}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38475" yWindow="0" windowWidth="19380" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3143" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="450">
   <si>
     <t>Date after which takes effect</t>
   </si>
@@ -1390,9 +1390,6 @@
   </si>
   <si>
     <t>UGRD</t>
-  </si>
-  <si>
-    <t>level</t>
   </si>
 </sst>
 </file>
@@ -11904,7 +11901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="20" customWidth="1"/>
@@ -11915,7 +11912,7 @@
     <col min="9" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -11940,11 +11937,8 @@
       <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117">
         <v>46055</v>
       </c>
@@ -11966,11 +11960,8 @@
       <c r="H2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
@@ -11983,11 +11974,8 @@
       <c r="H3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E4" s="20" t="s">
         <v>10</v>
       </c>
@@ -11997,11 +11985,8 @@
       <c r="H4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
@@ -12014,11 +11999,8 @@
       <c r="H5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
         <v>20</v>
       </c>
@@ -12031,11 +12013,8 @@
       <c r="H6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>13</v>
       </c>
@@ -12054,11 +12033,8 @@
       <c r="H7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="117">
         <v>46055</v>
       </c>
@@ -12079,9 +12055,6 @@
       </c>
       <c r="H8" s="20" t="s">
         <v>8</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55a11f37d9971d4c/! 1.Concordia/!z - COOP director/! PYTHON/WEB_TOOL/PY_code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5844D911-115F-4772-86DE-5C14D574F1AC}"/>
+  <xr:revisionPtr revIDLastSave="266" documentId="11_D958F8CCC097E9CD7CA39AD58694CA5597D6DE3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF24175C-8D84-44A5-A1D0-AB3B59CB8595}"/>
   <bookViews>
-    <workbookView xWindow="-38475" yWindow="0" windowWidth="19380" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3135" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="472">
   <si>
     <t>Date after which takes effect</t>
   </si>
@@ -1390,6 +1390,96 @@
   </si>
   <si>
     <t>UGRD</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>2027-2028</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>2028-2029</t>
+  </si>
+  <si>
+    <t>INDU 6990A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPSTONE 1 </t>
+  </si>
+  <si>
+    <t>CAPSTONE 2</t>
+  </si>
+  <si>
+    <t>INDU 6990B</t>
+  </si>
+  <si>
+    <t>ENGR 6992</t>
+  </si>
+  <si>
+    <t>Applied Engineering Training 1</t>
+  </si>
+  <si>
+    <t>Applied Engineering Training 2</t>
+  </si>
+  <si>
+    <t>ENGR 6993</t>
+  </si>
+  <si>
+    <t>CORE_select</t>
+  </si>
+  <si>
+    <t>Internship course ENGR 7961</t>
+  </si>
+  <si>
+    <t>Internship course ENGR 7962</t>
+  </si>
+  <si>
+    <t>answer COMPLIANT if sequence complies to:
+INDU GRAD Options 2,3,4 5 and 6 students should take either 
+-	the Capstone INDU 6990 (12CR) or 
+-	two (2) Applied Engineering Training: ENGR 6992 (6CR) &amp; ENGR 6993 (6CR)
+CO-OP Internship and CAPSTONE cannot be taken simultaneously. 
+Engineering Training might be credited for CO-OP Internship
+Options 2,3,4 5 and 6:  
+-	Option II: Lean Systems Engineering
+-	Option III. Supply Chain Engineering
+-	Option IV. Industrial Optimization and Systems Analytics
+-	Option V. Reliability and Maintenance Engineering
+-	Option VI. Industrial Engineering General Stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">answer COMPLIANT if sequence complies to:
+AERO GRAD students should take ENGR 7961 (6CR) = Internship course, credited for CO-OP if registered.  
+AERO GRAD students can choose to take ENGR 7962 (6CR) = 2nd Internship course, also credited for CO-OP if registered.  </t>
+  </si>
+  <si>
+    <t>ENGR 6990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGR 7961 </t>
+  </si>
+  <si>
+    <t>INDU GRAD Options 2,3,4 5 and 6 students should take either 
+-	the Capstone INDU 6990 (12CR) or 
+-	two (2) Applied Engineering Training: ENGR 6992 (6CR) &amp; ENGR 6993 (6CR)
+CO-OP Internship and CAPSTONE cannot be taken simultaneously. 
+Engineering Training might be credited for CO-OP Internship
+Options 2,3,4 5 and 6:  
+-	Option II: Lean Systems Engineering
+-	Option III. Supply Chain Engineering
+-	Option IV. Industrial Optimization and Systems Analytics
+-	Option V. Reliability and Maintenance Engineering
+-	Option VI. Industrial Engineering General Stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AERO GRAD students should take ENGR 7961 (6CR) = Internship course, credited for CO-OP if registered.  
+AERO GRAD students can choose to take ENGR 7962 (6CR) = 2nd Internship course, also credited for CO-OP if registered.  </t>
+  </si>
+  <si>
+    <t>INGORE IRRELEVANT ERRORS - write N/A</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1929,11 +2019,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1941,6 +2034,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2244,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U328"/>
+  <dimension ref="A1:U334"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.5703125" customWidth="1"/>
@@ -11885,13 +11998,145 @@
         <v>310</v>
       </c>
     </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>305</v>
+      </c>
+      <c r="B329" s="56" t="s">
+        <v>454</v>
+      </c>
+      <c r="C329" t="s">
+        <v>455</v>
+      </c>
+      <c r="D329" s="16">
+        <v>6</v>
+      </c>
+      <c r="I329" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K329" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>305</v>
+      </c>
+      <c r="B330" s="56" t="s">
+        <v>457</v>
+      </c>
+      <c r="C330" t="s">
+        <v>456</v>
+      </c>
+      <c r="D330" s="16">
+        <v>6</v>
+      </c>
+      <c r="J330" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K330" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>305</v>
+      </c>
+      <c r="B331" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="C331" t="s">
+        <v>459</v>
+      </c>
+      <c r="D331" s="16">
+        <v>6</v>
+      </c>
+      <c r="I331" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K331" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>305</v>
+      </c>
+      <c r="B332" s="56" t="s">
+        <v>461</v>
+      </c>
+      <c r="C332" t="s">
+        <v>460</v>
+      </c>
+      <c r="D332" s="16">
+        <v>6</v>
+      </c>
+      <c r="J332" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K332" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>307</v>
+      </c>
+      <c r="B333" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="C333" t="s">
+        <v>463</v>
+      </c>
+      <c r="D333" s="16">
+        <v>6</v>
+      </c>
+      <c r="G333" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I333" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J333" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K333" s="119" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>307</v>
+      </c>
+      <c r="B334" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C334" t="s">
+        <v>464</v>
+      </c>
+      <c r="D334" s="16">
+        <v>6</v>
+      </c>
+      <c r="G334" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I334" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J334" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K334" s="9" t="s">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K328" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="PRG">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="PRG">
       <formula>NOT(ISERROR(SEARCH("PRG",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="ENG">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="ENG">
       <formula>NOT(ISERROR(SEARCH("ENG",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11901,7 +12146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="20" customWidth="1"/>
@@ -11912,7 +12157,7 @@
     <col min="9" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -11937,8 +12182,11 @@
       <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117">
         <v>46055</v>
       </c>
@@ -11960,8 +12208,11 @@
       <c r="H2" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
@@ -11974,8 +12225,11 @@
       <c r="H3" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E4" s="20" t="s">
         <v>10</v>
       </c>
@@ -11985,8 +12239,11 @@
       <c r="H4" s="20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
@@ -11999,8 +12256,11 @@
       <c r="H5" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
         <v>20</v>
       </c>
@@ -12013,8 +12273,11 @@
       <c r="H6" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>13</v>
       </c>
@@ -12033,8 +12296,11 @@
       <c r="H7" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="117">
         <v>46055</v>
       </c>
@@ -12055,6 +12321,180 @@
       </c>
       <c r="H8" s="20" t="s">
         <v>8</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="117">
+        <v>46055</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="116" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="117">
+        <v>46055</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="116" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="116" t="s">
+        <v>465</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="G12" s="116" t="s">
+        <v>465</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="G13" s="116" t="s">
+        <v>469</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="116" t="s">
+        <v>470</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="G15" s="116" t="s">
+        <v>466</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="116" t="s">
+        <v>471</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="116" t="s">
+        <v>471</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -12064,7 +12504,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1B670F-7286-4413-AA18-FAB437017A91}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -12300,7 +12740,43 @@
         <v>4.75</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>310</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="C17:C18">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="PRG">
+      <formula>NOT(ISERROR(SEARCH("PRG",C17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="ENG">
+      <formula>NOT(ISERROR(SEARCH("ENG",C17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0 COOP Local\coop-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B221D1E-1284-4127-958F-B257AD2D9D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C612518-53A1-46A4-A06E-45297293D16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3183" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="469">
   <si>
     <t>Date after which takes effect</t>
   </si>
@@ -1468,6 +1468,9 @@
   </si>
   <si>
     <t>Students must select three credits of ​ General Education Humanities and Social Sciences Electives‌​ from one of the lists in ​Section 71.110 Complementary Studies for Engineering and Computer Science Students‌​</t>
+  </si>
+  <si>
+    <t>reserved for AERO students in summer</t>
   </si>
 </sst>
 </file>
@@ -12010,7 +12013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="20" bestFit="1" customWidth="1"/>
@@ -12019,7 +12022,7 @@
     <col min="4" max="4" width="12.140625" style="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="63.42578125" style="112" customWidth="1"/>
+    <col min="7" max="7" width="104.7109375" style="112" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="20" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="20"/>
   </cols>
@@ -12053,7 +12056,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="113">
         <v>46055</v>
       </c>
@@ -12079,7 +12082,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
@@ -12110,7 +12113,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
@@ -12127,7 +12130,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
         <v>20</v>
       </c>
@@ -12144,7 +12147,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>13</v>
       </c>
@@ -12167,7 +12170,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="113">
         <v>46055</v>
       </c>
@@ -12193,7 +12196,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="113">
         <v>46055</v>
       </c>
@@ -12219,7 +12222,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="113">
         <v>46055</v>
       </c>
@@ -12245,7 +12248,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="210" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>13</v>
       </c>
@@ -12262,7 +12265,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="210" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
         <v>13</v>
       </c>
@@ -12279,7 +12282,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="180" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
         <v>13</v>
       </c>
@@ -12296,7 +12299,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
         <v>18</v>
       </c>
@@ -12313,7 +12316,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>18</v>
       </c>
@@ -12364,7 +12367,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="F18" s="20" t="s">
         <v>293</v>
       </c>
@@ -12375,6 +12378,23 @@
         <v>17</v>
       </c>
       <c r="I18" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E19" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="112" t="s">
+        <v>468</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="20" t="s">
         <v>444</v>
       </c>
     </row>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0 COOP Local\coop-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC069D14-BEDA-45BE-9F47-C4EAA8BD09EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675FC789-C407-4C57-98C0-DF10AB7E0262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1704,7 +1704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1959,26 +1959,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1987,13 +1971,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2017,28 +1998,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2071,34 +2046,22 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2491,14 +2454,14 @@
       <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="104" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="10">
         <v>3</v>
       </c>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -2524,10 +2487,9 @@
       <c r="D3" s="35">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="F3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="18"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11" t="s">
@@ -2555,10 +2517,9 @@
       <c r="D4" s="35">
         <v>4</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="F4" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="18"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
@@ -2586,10 +2547,9 @@
       <c r="D5" s="35">
         <v>4</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="18"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
@@ -3540,7 +3500,7 @@
       <c r="U37" s="3"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="93" t="s">
+      <c r="A38" s="78" t="s">
         <v>43</v>
       </c>
       <c r="B38" s="23" t="s">
@@ -3600,20 +3560,20 @@
       <c r="U39" s="3"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="96" t="s">
+      <c r="A40" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="111" t="s">
+      <c r="C40" s="104" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="10">
         <v>3</v>
       </c>
-      <c r="E40" s="111"/>
-      <c r="F40" s="111"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="104"/>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
         <v>34</v>
@@ -4106,16 +4066,16 @@
       <c r="B56" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C56" s="113" t="s">
+      <c r="C56" s="106" t="s">
         <v>130</v>
       </c>
       <c r="D56" s="14">
         <v>3</v>
       </c>
-      <c r="E56" s="113" t="s">
+      <c r="E56" s="106" t="s">
         <v>131</v>
       </c>
-      <c r="F56" s="113"/>
+      <c r="F56" s="106"/>
       <c r="G56" s="15" t="s">
         <v>34</v>
       </c>
@@ -4139,16 +4099,16 @@
       <c r="B57" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C57" s="111" t="s">
+      <c r="C57" s="104" t="s">
         <v>130</v>
       </c>
       <c r="D57" s="10">
         <v>3</v>
       </c>
-      <c r="E57" s="111" t="s">
+      <c r="E57" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="F57" s="111"/>
+      <c r="F57" s="104"/>
       <c r="G57" s="11" t="s">
         <v>34</v>
       </c>
@@ -4259,14 +4219,14 @@
       <c r="B61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="111" t="s">
+      <c r="C61" s="104" t="s">
         <v>132</v>
       </c>
       <c r="D61" s="10">
         <v>1.5</v>
       </c>
-      <c r="E61" s="111"/>
-      <c r="F61" s="111"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
       <c r="G61" s="11" t="s">
         <v>34</v>
       </c>
@@ -4404,14 +4364,14 @@
       <c r="B66" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="113" t="s">
+      <c r="C66" s="106" t="s">
         <v>134</v>
       </c>
       <c r="D66" s="14">
         <v>1.5</v>
       </c>
-      <c r="E66" s="113"/>
-      <c r="F66" s="113"/>
+      <c r="E66" s="106"/>
+      <c r="F66" s="106"/>
       <c r="G66" s="15" t="s">
         <v>34</v>
       </c>
@@ -4433,14 +4393,14 @@
       <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C67" s="111" t="s">
+      <c r="C67" s="104" t="s">
         <v>134</v>
       </c>
       <c r="D67" s="10">
         <v>1.5</v>
       </c>
-      <c r="E67" s="111"/>
-      <c r="F67" s="111"/>
+      <c r="E67" s="104"/>
+      <c r="F67" s="104"/>
       <c r="G67" s="11" t="s">
         <v>34</v>
       </c>
@@ -4561,16 +4521,16 @@
       <c r="B71" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C71" s="111" t="s">
+      <c r="C71" s="104" t="s">
         <v>135</v>
       </c>
       <c r="D71" s="10">
         <v>3</v>
       </c>
-      <c r="E71" s="111" t="s">
+      <c r="E71" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="F71" s="111" t="s">
+      <c r="F71" s="104" t="s">
         <v>100</v>
       </c>
       <c r="G71" s="11" t="s">
@@ -4726,16 +4686,16 @@
       <c r="B76" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C76" s="113" t="s">
+      <c r="C76" s="106" t="s">
         <v>138</v>
       </c>
       <c r="D76" s="14">
         <v>3</v>
       </c>
-      <c r="E76" s="113" t="s">
+      <c r="E76" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="F76" s="113"/>
+      <c r="F76" s="106"/>
       <c r="G76" s="15" t="s">
         <v>34</v>
       </c>
@@ -4759,16 +4719,16 @@
       <c r="B77" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C77" s="111" t="s">
+      <c r="C77" s="104" t="s">
         <v>138</v>
       </c>
       <c r="D77" s="10">
         <v>3</v>
       </c>
-      <c r="E77" s="111" t="s">
+      <c r="E77" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="F77" s="111"/>
+      <c r="F77" s="104"/>
       <c r="G77" s="11" t="s">
         <v>34</v>
       </c>
@@ -4978,20 +4938,18 @@
       <c r="B84" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="C84" s="97" t="s">
+      <c r="C84" t="s">
         <v>143</v>
       </c>
       <c r="D84" s="59">
         <v>3</v>
       </c>
-      <c r="E84" s="97" t="s">
+      <c r="E84" t="s">
         <v>144</v>
       </c>
-      <c r="F84" s="97"/>
       <c r="G84" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H84" s="130"/>
       <c r="I84" s="11" t="s">
         <v>34</v>
       </c>
@@ -5006,7 +4964,7 @@
       <c r="A85" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B85" s="100" t="s">
+      <c r="B85" s="94" t="s">
         <v>142</v>
       </c>
       <c r="C85" s="19" t="s">
@@ -5039,22 +4997,21 @@
       <c r="B86" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="C86" s="97" t="s">
+      <c r="C86" t="s">
         <v>146</v>
       </c>
       <c r="D86" s="59">
         <v>3.75</v>
       </c>
-      <c r="E86" s="97" t="s">
+      <c r="E86" t="s">
         <v>147</v>
       </c>
-      <c r="F86" s="97" t="s">
+      <c r="F86" t="s">
         <v>137</v>
       </c>
       <c r="G86" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H86" s="130"/>
       <c r="I86" s="11" t="s">
         <v>34</v>
       </c>
@@ -5072,22 +5029,21 @@
       <c r="B87" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="97" t="s">
+      <c r="C87" t="s">
         <v>146</v>
       </c>
       <c r="D87" s="59">
         <v>3.75</v>
       </c>
-      <c r="E87" s="97" t="s">
+      <c r="E87" t="s">
         <v>147</v>
       </c>
-      <c r="F87" s="97" t="s">
+      <c r="F87" t="s">
         <v>137</v>
       </c>
       <c r="G87" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H87" s="130"/>
       <c r="I87" s="11" t="s">
         <v>34</v>
       </c>
@@ -5105,22 +5061,21 @@
       <c r="B88" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="C88" s="97" t="s">
+      <c r="C88" t="s">
         <v>146</v>
       </c>
       <c r="D88" s="59">
         <v>3.75</v>
       </c>
-      <c r="E88" s="97" t="s">
+      <c r="E88" t="s">
         <v>147</v>
       </c>
-      <c r="F88" s="97" t="s">
+      <c r="F88" t="s">
         <v>137</v>
       </c>
       <c r="G88" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H88" s="130"/>
       <c r="I88" s="11" t="s">
         <v>34</v>
       </c>
@@ -5168,7 +5123,7 @@
       <c r="A90" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B90" s="100" t="s">
+      <c r="B90" s="94" t="s">
         <v>148</v>
       </c>
       <c r="C90" s="19" t="s">
@@ -5195,7 +5150,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A91" s="94" t="s">
+      <c r="A91" s="77" t="s">
         <v>37</v>
       </c>
       <c r="B91" s="81" t="s">
@@ -5228,32 +5183,32 @@
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A92" s="95" t="s">
+      <c r="A92" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="B92" s="108" t="s">
+      <c r="B92" s="101" t="s">
         <v>151</v>
       </c>
-      <c r="C92" s="120" t="s">
+      <c r="C92" s="111" t="s">
         <v>152</v>
       </c>
-      <c r="D92" s="128">
-        <v>3</v>
-      </c>
-      <c r="E92" s="120" t="s">
+      <c r="D92" s="119">
+        <v>3</v>
+      </c>
+      <c r="E92" s="111" t="s">
         <v>153</v>
       </c>
-      <c r="F92" s="120"/>
-      <c r="G92" s="138" t="s">
-        <v>34</v>
-      </c>
-      <c r="H92" s="138" t="s">
-        <v>34</v>
-      </c>
-      <c r="I92" s="138" t="s">
-        <v>34</v>
-      </c>
-      <c r="J92" s="138" t="s">
+      <c r="F92" s="111"/>
+      <c r="G92" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="I92" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="J92" s="126" t="s">
         <v>34</v>
       </c>
       <c r="K92" s="9" t="s">
@@ -5264,19 +5219,19 @@
       <c r="A93" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="110" t="s">
+      <c r="B93" s="103" t="s">
         <v>151</v>
       </c>
-      <c r="C93" s="121" t="s">
+      <c r="C93" s="112" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="129">
-        <v>3</v>
-      </c>
-      <c r="E93" s="121" t="s">
+      <c r="D93" s="120">
+        <v>3</v>
+      </c>
+      <c r="E93" s="112" t="s">
         <v>153</v>
       </c>
-      <c r="F93" s="121"/>
+      <c r="F93" s="112"/>
       <c r="G93" s="83" t="s">
         <v>34</v>
       </c>
@@ -5399,14 +5354,14 @@
       <c r="B97" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C97" s="111" t="s">
+      <c r="C97" s="104" t="s">
         <v>155</v>
       </c>
       <c r="D97" s="10">
         <v>3</v>
       </c>
-      <c r="E97" s="111"/>
-      <c r="F97" s="111"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="104"/>
       <c r="G97" s="11" t="s">
         <v>34</v>
       </c>
@@ -5532,16 +5487,16 @@
       <c r="B101" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C101" s="113" t="s">
+      <c r="C101" s="106" t="s">
         <v>157</v>
       </c>
       <c r="D101" s="14">
         <v>3</v>
       </c>
-      <c r="E101" s="113" t="s">
+      <c r="E101" s="106" t="s">
         <v>158</v>
       </c>
-      <c r="F101" s="113"/>
+      <c r="F101" s="106"/>
       <c r="G101" s="15" t="s">
         <v>34</v>
       </c>
@@ -5566,16 +5521,16 @@
       <c r="B102" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C102" s="111" t="s">
+      <c r="C102" s="104" t="s">
         <v>157</v>
       </c>
       <c r="D102" s="10">
         <v>3</v>
       </c>
-      <c r="E102" s="111" t="s">
+      <c r="E102" s="104" t="s">
         <v>158</v>
       </c>
-      <c r="F102" s="111"/>
+      <c r="F102" s="104"/>
       <c r="G102" s="11" t="s">
         <v>34</v>
       </c>
@@ -5831,16 +5786,16 @@
       <c r="B110" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C110" s="111" t="s">
+      <c r="C110" s="104" t="s">
         <v>163</v>
       </c>
       <c r="D110" s="10">
         <v>3</v>
       </c>
-      <c r="E110" s="111" t="s">
+      <c r="E110" s="104" t="s">
         <v>158</v>
       </c>
-      <c r="F110" s="111"/>
+      <c r="F110" s="104"/>
       <c r="G110" s="11" t="s">
         <v>34</v>
       </c>
@@ -5866,16 +5821,16 @@
       <c r="B111" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C111" s="111" t="s">
+      <c r="C111" s="104" t="s">
         <v>163</v>
       </c>
       <c r="D111" s="10">
         <v>3</v>
       </c>
-      <c r="E111" s="111" t="s">
+      <c r="E111" s="104" t="s">
         <v>158</v>
       </c>
-      <c r="F111" s="111"/>
+      <c r="F111" s="104"/>
       <c r="G111" s="11" t="s">
         <v>34</v>
       </c>
@@ -6000,16 +5955,16 @@
       <c r="B115" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C115" s="113" t="s">
+      <c r="C115" s="106" t="s">
         <v>165</v>
       </c>
       <c r="D115" s="14">
         <v>3</v>
       </c>
-      <c r="E115" s="113" t="s">
+      <c r="E115" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="F115" s="113"/>
+      <c r="F115" s="106"/>
       <c r="G115" s="15"/>
       <c r="H115" s="15" t="s">
         <v>34</v>
@@ -6166,16 +6121,16 @@
       <c r="B120" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C120" s="111" t="s">
+      <c r="C120" s="104" t="s">
         <v>168</v>
       </c>
       <c r="D120" s="10">
         <v>3</v>
       </c>
-      <c r="E120" s="111" t="s">
+      <c r="E120" s="104" t="s">
         <v>169</v>
       </c>
-      <c r="F120" s="111"/>
+      <c r="F120" s="104"/>
       <c r="G120" s="11" t="s">
         <v>34</v>
       </c>
@@ -6200,16 +6155,16 @@
       <c r="B121" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C121" s="111" t="s">
+      <c r="C121" s="104" t="s">
         <v>168</v>
       </c>
       <c r="D121" s="10">
         <v>3</v>
       </c>
-      <c r="E121" s="111" t="s">
+      <c r="E121" s="104" t="s">
         <v>169</v>
       </c>
-      <c r="F121" s="111"/>
+      <c r="F121" s="104"/>
       <c r="G121" s="11" t="s">
         <v>34</v>
       </c>
@@ -6860,7 +6815,7 @@
       <c r="A143" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B143" s="98" t="s">
+      <c r="B143" s="55" t="s">
         <v>302</v>
       </c>
       <c r="C143" t="s">
@@ -6869,13 +6824,13 @@
       <c r="D143" s="8">
         <v>4</v>
       </c>
-      <c r="G143" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I143" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J143" s="130" t="s">
+      <c r="G143" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I143" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J143" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K143" s="9" t="s">
@@ -6938,7 +6893,7 @@
       <c r="A146" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B146" s="98" t="s">
+      <c r="B146" s="55" t="s">
         <v>303</v>
       </c>
       <c r="C146" t="s">
@@ -6947,13 +6902,13 @@
       <c r="D146" s="8">
         <v>4</v>
       </c>
-      <c r="G146" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I146" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J146" s="130" t="s">
+      <c r="G146" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I146" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J146" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K146" s="9" t="s">
@@ -7025,13 +6980,13 @@
       <c r="D149" s="8">
         <v>4</v>
       </c>
-      <c r="G149" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I149" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J149" s="130" t="s">
+      <c r="G149" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I149" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J149" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K149" s="9" t="s">
@@ -7094,7 +7049,7 @@
       <c r="A152" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B152" s="98" t="s">
+      <c r="B152" s="55" t="s">
         <v>305</v>
       </c>
       <c r="C152" t="s">
@@ -7103,13 +7058,13 @@
       <c r="D152" s="8">
         <v>4</v>
       </c>
-      <c r="G152" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I152" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J152" s="130" t="s">
+      <c r="G152" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I152" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J152" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K152" s="9" t="s">
@@ -7172,7 +7127,7 @@
       <c r="A155" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B155" s="98" t="s">
+      <c r="B155" s="55" t="s">
         <v>306</v>
       </c>
       <c r="C155" t="s">
@@ -7181,13 +7136,13 @@
       <c r="D155" s="8">
         <v>4</v>
       </c>
-      <c r="G155" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I155" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J155" s="130" t="s">
+      <c r="G155" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I155" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J155" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K155" s="9" t="s">
@@ -8103,7 +8058,7 @@
       <c r="J190" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K190" s="135" t="s">
+      <c r="K190" s="22" t="s">
         <v>299</v>
       </c>
     </row>
@@ -8818,25 +8773,25 @@
       <c r="A219" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B219" s="99" t="s">
+      <c r="B219" s="93" t="s">
         <v>153</v>
       </c>
-      <c r="C219" s="114" t="s">
+      <c r="C219" s="107" t="s">
         <v>201</v>
       </c>
       <c r="D219" s="51">
         <v>3</v>
       </c>
-      <c r="E219" s="114"/>
-      <c r="F219" s="114"/>
-      <c r="G219" s="132"/>
-      <c r="H219" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="I219" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="J219" s="132" t="s">
+      <c r="E219" s="107"/>
+      <c r="F219" s="107"/>
+      <c r="G219" s="122"/>
+      <c r="H219" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="I219" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="J219" s="122" t="s">
         <v>34</v>
       </c>
       <c r="K219" s="52" t="s">
@@ -8847,25 +8802,25 @@
       <c r="A220" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B220" s="93" t="s">
+      <c r="B220" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="C220" s="116" t="s">
+      <c r="C220" s="108" t="s">
         <v>201</v>
       </c>
       <c r="D220" s="31">
         <v>3</v>
       </c>
-      <c r="E220" s="116"/>
-      <c r="F220" s="116"/>
-      <c r="G220" s="134"/>
-      <c r="H220" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="I220" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="J220" s="134" t="s">
+      <c r="E220" s="108"/>
+      <c r="F220" s="108"/>
+      <c r="G220" s="123"/>
+      <c r="H220" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="I220" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="J220" s="123" t="s">
         <v>34</v>
       </c>
       <c r="K220" s="32" t="s">
@@ -8876,25 +8831,25 @@
       <c r="A221" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B221" s="102" t="s">
+      <c r="B221" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="C221" s="115" t="s">
+      <c r="C221" s="58" t="s">
         <v>201</v>
       </c>
       <c r="D221" s="41">
         <v>3</v>
       </c>
-      <c r="E221" s="115"/>
-      <c r="F221" s="115"/>
-      <c r="G221" s="133"/>
-      <c r="H221" s="133" t="s">
-        <v>34</v>
-      </c>
-      <c r="I221" s="133" t="s">
-        <v>34</v>
-      </c>
-      <c r="J221" s="133" t="s">
+      <c r="E221" s="58"/>
+      <c r="F221" s="58"/>
+      <c r="G221" s="61"/>
+      <c r="H221" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="I221" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="J221" s="61" t="s">
         <v>34</v>
       </c>
       <c r="K221" s="42" t="s">
@@ -8926,7 +8881,7 @@
       <c r="J222" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="K222" s="139" t="s">
+      <c r="K222" s="60" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8954,7 +8909,7 @@
       <c r="J223" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K223" s="130" t="s">
+      <c r="K223" s="20" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8962,28 +8917,28 @@
       <c r="A224" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B224" s="94" t="s">
+      <c r="B224" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="C224" s="112" t="s">
+      <c r="C224" s="105" t="s">
         <v>203</v>
       </c>
       <c r="D224" s="45">
         <v>3</v>
       </c>
-      <c r="E224" s="112"/>
-      <c r="F224" s="112"/>
-      <c r="G224" s="131"/>
-      <c r="H224" s="131" t="s">
-        <v>34</v>
-      </c>
-      <c r="I224" s="131" t="s">
-        <v>34</v>
-      </c>
-      <c r="J224" s="131" t="s">
-        <v>34</v>
-      </c>
-      <c r="K224" s="131" t="s">
+      <c r="E224" s="105"/>
+      <c r="F224" s="105"/>
+      <c r="G224" s="121"/>
+      <c r="H224" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="I224" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="J224" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="K224" s="121" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8991,19 +8946,19 @@
       <c r="A225" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B225" s="105" t="s">
+      <c r="B225" s="98" t="s">
         <v>202</v>
       </c>
-      <c r="C225" s="118" t="s">
+      <c r="C225" s="109" t="s">
         <v>203</v>
       </c>
-      <c r="D225" s="126">
-        <v>3</v>
-      </c>
-      <c r="E225" s="118"/>
-      <c r="F225" s="118"/>
+      <c r="D225" s="117">
+        <v>3</v>
+      </c>
+      <c r="E225" s="109"/>
+      <c r="F225" s="109"/>
       <c r="G225" s="26"/>
-      <c r="H225" s="136" t="s">
+      <c r="H225" s="124" t="s">
         <v>34</v>
       </c>
       <c r="I225" s="26" t="s">
@@ -9012,7 +8967,7 @@
       <c r="J225" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="K225" s="136" t="s">
+      <c r="K225" s="124" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9020,19 +8975,19 @@
       <c r="A226" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B226" s="109" t="s">
+      <c r="B226" s="102" t="s">
         <v>202</v>
       </c>
-      <c r="C226" s="119" t="s">
+      <c r="C226" s="110" t="s">
         <v>203</v>
       </c>
       <c r="D226" s="59">
         <v>3</v>
       </c>
-      <c r="E226" s="119"/>
-      <c r="F226" s="119"/>
+      <c r="E226" s="110"/>
+      <c r="F226" s="110"/>
       <c r="G226" s="36"/>
-      <c r="H226" s="137" t="s">
+      <c r="H226" s="125" t="s">
         <v>34</v>
       </c>
       <c r="I226" s="36" t="s">
@@ -9041,7 +8996,7 @@
       <c r="J226" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="K226" s="137" t="s">
+      <c r="K226" s="125" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9049,7 +9004,7 @@
       <c r="A227" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B227" s="100" t="s">
+      <c r="B227" s="94" t="s">
         <v>202</v>
       </c>
       <c r="C227" s="19" t="s">
@@ -9070,7 +9025,7 @@
       <c r="J227" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K227" s="130" t="s">
+      <c r="K227" s="20" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9099,7 +9054,7 @@
       <c r="J228" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K228" s="135" t="s">
+      <c r="K228" s="22" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9107,19 +9062,19 @@
       <c r="A229" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B229" s="101" t="s">
+      <c r="B229" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="C229" s="114" t="s">
+      <c r="C229" s="107" t="s">
         <v>205</v>
       </c>
-      <c r="D229" s="123">
-        <v>3</v>
-      </c>
-      <c r="E229" s="114"/>
-      <c r="F229" s="114"/>
+      <c r="D229" s="114">
+        <v>3</v>
+      </c>
+      <c r="E229" s="107"/>
+      <c r="F229" s="107"/>
       <c r="G229" s="52"/>
-      <c r="H229" s="132" t="s">
+      <c r="H229" s="122" t="s">
         <v>34</v>
       </c>
       <c r="I229" s="52" t="s">
@@ -9128,7 +9083,7 @@
       <c r="J229" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="K229" s="132" t="s">
+      <c r="K229" s="122" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9136,19 +9091,19 @@
       <c r="A230" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B230" s="107" t="s">
+      <c r="B230" s="100" t="s">
         <v>204</v>
       </c>
-      <c r="C230" s="116" t="s">
+      <c r="C230" s="108" t="s">
         <v>205</v>
       </c>
-      <c r="D230" s="125">
-        <v>3</v>
-      </c>
-      <c r="E230" s="116"/>
-      <c r="F230" s="116"/>
+      <c r="D230" s="116">
+        <v>3</v>
+      </c>
+      <c r="E230" s="108"/>
+      <c r="F230" s="108"/>
       <c r="G230" s="32"/>
-      <c r="H230" s="134" t="s">
+      <c r="H230" s="123" t="s">
         <v>34</v>
       </c>
       <c r="I230" s="32" t="s">
@@ -9157,7 +9112,7 @@
       <c r="J230" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="K230" s="134" t="s">
+      <c r="K230" s="123" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9165,19 +9120,19 @@
       <c r="A231" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B231" s="106" t="s">
+      <c r="B231" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="C231" s="115" t="s">
+      <c r="C231" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="D231" s="127">
-        <v>3</v>
-      </c>
-      <c r="E231" s="115"/>
-      <c r="F231" s="115"/>
+      <c r="D231" s="118">
+        <v>3</v>
+      </c>
+      <c r="E231" s="58"/>
+      <c r="F231" s="58"/>
       <c r="G231" s="42"/>
-      <c r="H231" s="133" t="s">
+      <c r="H231" s="61" t="s">
         <v>34</v>
       </c>
       <c r="I231" s="42" t="s">
@@ -9186,7 +9141,7 @@
       <c r="J231" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="K231" s="133" t="s">
+      <c r="K231" s="61" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9194,13 +9149,13 @@
       <c r="A232" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B232" s="103" t="s">
+      <c r="B232" s="96" t="s">
         <v>204</v>
       </c>
       <c r="C232" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="D232" s="122">
+      <c r="D232" s="113">
         <v>3</v>
       </c>
       <c r="E232" s="57"/>
@@ -9215,7 +9170,7 @@
       <c r="J232" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="K232" s="139" t="s">
+      <c r="K232" s="60" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9223,7 +9178,7 @@
       <c r="A233" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B233" s="100" t="s">
+      <c r="B233" s="94" t="s">
         <v>204</v>
       </c>
       <c r="C233" s="19" t="s">
@@ -9244,7 +9199,7 @@
       <c r="J233" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K233" s="130" t="s">
+      <c r="K233" s="20" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9271,7 +9226,7 @@
       <c r="J234" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K234" s="135" t="s">
+      <c r="K234" s="22" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9282,25 +9237,23 @@
       <c r="B235" s="56" t="s">
         <v>209</v>
       </c>
-      <c r="C235" s="97" t="s">
+      <c r="C235" t="s">
         <v>210</v>
       </c>
       <c r="D235" s="59">
         <v>3.5</v>
       </c>
-      <c r="E235" s="97" t="s">
+      <c r="E235" t="s">
         <v>211</v>
       </c>
-      <c r="F235" s="97"/>
       <c r="G235" s="11"/>
-      <c r="H235" s="130"/>
       <c r="I235" s="11" t="s">
         <v>34</v>
       </c>
       <c r="J235" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K235" s="130" t="s">
+      <c r="K235" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9311,25 +9264,23 @@
       <c r="B236" s="56" t="s">
         <v>209</v>
       </c>
-      <c r="C236" s="97" t="s">
+      <c r="C236" t="s">
         <v>210</v>
       </c>
       <c r="D236" s="59">
         <v>3.5</v>
       </c>
-      <c r="E236" s="97" t="s">
+      <c r="E236" t="s">
         <v>211</v>
       </c>
-      <c r="F236" s="97"/>
       <c r="G236" s="11"/>
-      <c r="H236" s="130"/>
       <c r="I236" s="11" t="s">
         <v>34</v>
       </c>
       <c r="J236" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K236" s="130" t="s">
+      <c r="K236" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9395,25 +9346,22 @@
       <c r="A239" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B239" s="97" t="s">
+      <c r="B239" t="s">
         <v>215</v>
       </c>
-      <c r="C239" s="97" t="s">
+      <c r="C239" t="s">
         <v>216</v>
       </c>
       <c r="D239" s="35">
         <v>3.5</v>
       </c>
-      <c r="E239" s="97" t="s">
+      <c r="E239" t="s">
         <v>151</v>
       </c>
-      <c r="F239" s="97"/>
-      <c r="G239" s="130"/>
-      <c r="H239" s="130"/>
-      <c r="I239" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J239" s="130" t="s">
+      <c r="I239" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J239" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K239" s="11" t="s">
@@ -9443,7 +9391,7 @@
       <c r="J240" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K240" s="130" t="s">
+      <c r="K240" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9451,25 +9399,22 @@
       <c r="A241" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B241" s="97" t="s">
+      <c r="B241" t="s">
         <v>217</v>
       </c>
-      <c r="C241" s="97" t="s">
+      <c r="C241" t="s">
         <v>218</v>
       </c>
       <c r="D241" s="35">
         <v>3.5</v>
       </c>
-      <c r="E241" s="97" t="s">
+      <c r="E241" t="s">
         <v>219</v>
       </c>
-      <c r="F241" s="97"/>
-      <c r="G241" s="130"/>
-      <c r="H241" s="130"/>
-      <c r="I241" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J241" s="130" t="s">
+      <c r="I241" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J241" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K241" s="11" t="s">
@@ -9501,7 +9446,7 @@
       <c r="J242" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K242" s="135" t="s">
+      <c r="K242" s="22" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9509,28 +9454,25 @@
       <c r="A243" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B243" s="97" t="s">
+      <c r="B243" t="s">
         <v>74</v>
       </c>
-      <c r="C243" s="97" t="s">
+      <c r="C243" t="s">
         <v>220</v>
       </c>
       <c r="D243" s="35">
         <v>3.5</v>
       </c>
-      <c r="E243" s="97" t="s">
+      <c r="E243" t="s">
         <v>159</v>
       </c>
-      <c r="F243" s="97"/>
-      <c r="G243" s="130"/>
-      <c r="H243" s="130"/>
-      <c r="I243" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J243" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="K243" s="130" t="s">
+      <c r="I243" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J243" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="K243" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9557,7 +9499,7 @@
       <c r="J244" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K244" s="130" t="s">
+      <c r="K244" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9586,7 +9528,7 @@
       <c r="J245" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K245" s="135" t="s">
+      <c r="K245" s="22" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9616,7 +9558,7 @@
       <c r="J246" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="K246" s="130" t="s">
+      <c r="K246" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9624,26 +9566,22 @@
       <c r="A247" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B247" s="97" t="s">
+      <c r="B247" t="s">
         <v>227</v>
       </c>
-      <c r="C247" s="97" t="s">
+      <c r="C247" t="s">
         <v>228</v>
       </c>
       <c r="D247" s="59">
         <v>3.5</v>
       </c>
-      <c r="E247" s="97" t="s">
+      <c r="E247" t="s">
         <v>229</v>
       </c>
-      <c r="F247" s="97"/>
-      <c r="G247" s="130"/>
-      <c r="H247" s="130"/>
-      <c r="I247" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J247" s="130"/>
-      <c r="K247" s="130" t="s">
+      <c r="I247" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="K247" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -9670,35 +9608,33 @@
         <v>34</v>
       </c>
       <c r="J248" s="22"/>
-      <c r="K248" s="135" t="s">
+      <c r="K248" s="22" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A249" s="93" t="s">
+      <c r="A249" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B249" s="97" t="s">
+      <c r="B249" t="s">
         <v>230</v>
       </c>
-      <c r="C249" s="97" t="s">
+      <c r="C249" t="s">
         <v>231</v>
       </c>
       <c r="D249" s="59">
         <v>3.5</v>
       </c>
-      <c r="E249" s="97" t="s">
+      <c r="E249" t="s">
         <v>232</v>
       </c>
-      <c r="F249" s="97"/>
-      <c r="G249" s="130"/>
-      <c r="H249" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I249" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J249" s="130" t="s">
+      <c r="H249" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I249" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J249" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K249" s="11" t="s">
@@ -9767,10 +9703,10 @@
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A252" s="93" t="s">
+      <c r="A252" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B252" s="97" t="s">
+      <c r="B252" t="s">
         <v>236</v>
       </c>
       <c r="C252" t="s">
@@ -9782,20 +9718,18 @@
       <c r="E252" t="s">
         <v>238</v>
       </c>
-      <c r="G252" s="130"/>
-      <c r="I252" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J252" s="130"/>
+      <c r="I252" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="K252" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A253" s="93" t="s">
+      <c r="A253" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B253" s="97" t="s">
+      <c r="B253" t="s">
         <v>239</v>
       </c>
       <c r="C253" t="s">
@@ -9807,9 +9741,7 @@
       <c r="E253" t="s">
         <v>241</v>
       </c>
-      <c r="G253" s="130"/>
-      <c r="I253" s="130"/>
-      <c r="J253" s="130" t="s">
+      <c r="J253" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K253" s="11" t="s">
@@ -9817,28 +9749,24 @@
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A254" s="94" t="s">
+      <c r="A254" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B254" s="97" t="s">
+      <c r="B254" t="s">
         <v>242</v>
       </c>
-      <c r="C254" s="97" t="s">
+      <c r="C254" t="s">
         <v>243</v>
       </c>
       <c r="D254" s="59">
         <v>3.5</v>
       </c>
-      <c r="E254" s="97" t="s">
+      <c r="E254" t="s">
         <v>74</v>
       </c>
-      <c r="F254" s="97"/>
-      <c r="G254" s="130"/>
-      <c r="H254" s="130"/>
-      <c r="I254" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J254" s="130"/>
+      <c r="I254" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="K254" s="11" t="s">
         <v>44</v>
       </c>
@@ -9901,25 +9829,22 @@
       <c r="A257" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B257" s="97" t="s">
+      <c r="B257" t="s">
         <v>248</v>
       </c>
-      <c r="C257" s="97" t="s">
+      <c r="C257" t="s">
         <v>249</v>
       </c>
       <c r="D257" s="59">
         <v>3.5</v>
       </c>
-      <c r="E257" s="97"/>
-      <c r="F257" s="97"/>
-      <c r="G257" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H257" s="130"/>
-      <c r="I257" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J257" s="130" t="s">
+      <c r="G257" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I257" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J257" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K257" s="11" t="s">
@@ -9927,10 +9852,10 @@
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A258" s="93" t="s">
+      <c r="A258" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B258" s="97" t="s">
+      <c r="B258" t="s">
         <v>248</v>
       </c>
       <c r="C258" t="s">
@@ -9939,13 +9864,13 @@
       <c r="D258" s="59">
         <v>3.5</v>
       </c>
-      <c r="G258" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I258" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J258" s="130" t="s">
+      <c r="G258" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I258" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J258" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K258" s="11" t="s">
@@ -9953,7 +9878,7 @@
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A259" s="96" t="s">
+      <c r="A259" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B259" s="54" t="s">
@@ -10013,27 +9938,25 @@
       <c r="A261" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B261" s="97" t="s">
+      <c r="B261" t="s">
         <v>250</v>
       </c>
-      <c r="C261" s="97" t="s">
+      <c r="C261" t="s">
         <v>251</v>
       </c>
       <c r="D261" s="59">
         <v>3.5</v>
       </c>
-      <c r="E261" s="97" t="s">
+      <c r="E261" t="s">
         <v>252</v>
       </c>
-      <c r="F261" s="97"/>
-      <c r="G261" s="130"/>
-      <c r="H261" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I261" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J261" s="130" t="s">
+      <c r="H261" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I261" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J261" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K261" s="11" t="s">
@@ -10041,10 +9964,10 @@
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A262" s="93" t="s">
+      <c r="A262" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B262" s="97" t="s">
+      <c r="B262" t="s">
         <v>250</v>
       </c>
       <c r="C262" t="s">
@@ -10056,14 +9979,13 @@
       <c r="E262" t="s">
         <v>252</v>
       </c>
-      <c r="G262" s="130"/>
       <c r="H262" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I262" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J262" s="130" t="s">
+      <c r="I262" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J262" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K262" s="11" t="s">
@@ -10071,7 +9993,7 @@
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A263" s="95" t="s">
+      <c r="A263" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B263" s="53" t="s">
@@ -10080,7 +10002,7 @@
       <c r="C263" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="D263" s="122">
+      <c r="D263" s="113">
         <v>3.5</v>
       </c>
       <c r="E263" s="57" t="s">
@@ -10135,25 +10057,22 @@
       <c r="A265" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B265" s="97" t="s">
+      <c r="B265" t="s">
         <v>253</v>
       </c>
-      <c r="C265" s="97" t="s">
+      <c r="C265" t="s">
         <v>254</v>
       </c>
       <c r="D265" s="59">
         <v>3</v>
       </c>
-      <c r="E265" s="97" t="s">
+      <c r="E265" t="s">
         <v>255</v>
       </c>
-      <c r="F265" s="97"/>
-      <c r="G265" s="130"/>
-      <c r="H265" s="130"/>
-      <c r="I265" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J265" s="130" t="s">
+      <c r="I265" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J265" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K265" s="11" t="s">
@@ -10161,10 +10080,10 @@
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A266" s="93" t="s">
+      <c r="A266" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B266" s="97" t="s">
+      <c r="B266" t="s">
         <v>253</v>
       </c>
       <c r="C266" t="s">
@@ -10176,11 +10095,10 @@
       <c r="E266" t="s">
         <v>255</v>
       </c>
-      <c r="G266" s="130"/>
-      <c r="I266" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J266" s="130" t="s">
+      <c r="I266" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J266" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K266" s="11" t="s">
@@ -10188,7 +10106,7 @@
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A267" s="96" t="s">
+      <c r="A267" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B267" s="54" t="s">
@@ -10244,10 +10162,10 @@
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A269" s="93" t="s">
+      <c r="A269" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B269" s="97" t="s">
+      <c r="B269" t="s">
         <v>238</v>
       </c>
       <c r="C269" t="s">
@@ -10259,19 +10177,18 @@
       <c r="E269" t="s">
         <v>257</v>
       </c>
-      <c r="G269" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I269" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J269" s="130"/>
+      <c r="G269" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I269" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="K269" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A270" s="95" t="s">
+      <c r="A270" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B270" s="53" t="s">
@@ -10280,7 +10197,7 @@
       <c r="C270" s="57" t="s">
         <v>256</v>
       </c>
-      <c r="D270" s="122">
+      <c r="D270" s="113">
         <v>3</v>
       </c>
       <c r="E270" s="57" t="s">
@@ -10327,10 +10244,10 @@
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A272" s="93" t="s">
+      <c r="A272" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B272" s="97" t="s">
+      <c r="B272" t="s">
         <v>258</v>
       </c>
       <c r="C272" t="s">
@@ -10342,19 +10259,18 @@
       <c r="F272" t="s">
         <v>238</v>
       </c>
-      <c r="G272" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I272" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J272" s="130"/>
+      <c r="G272" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I272" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="K272" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A273" s="96" t="s">
+      <c r="A273" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B273" s="54" t="s">
@@ -10413,27 +10329,25 @@
       <c r="A275" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B275" s="97" t="s">
+      <c r="B275" t="s">
         <v>260</v>
       </c>
-      <c r="C275" s="97" t="s">
+      <c r="C275" t="s">
         <v>261</v>
       </c>
       <c r="D275" s="59">
         <v>3.5</v>
       </c>
-      <c r="E275" s="97" t="s">
+      <c r="E275" t="s">
         <v>262</v>
       </c>
-      <c r="F275" s="97"/>
-      <c r="G275" s="130"/>
-      <c r="H275" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I275" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J275" s="130" t="s">
+      <c r="H275" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I275" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J275" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K275" s="11" t="s">
@@ -10441,7 +10355,7 @@
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A276" s="95" t="s">
+      <c r="A276" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B276" s="53" t="s">
@@ -10450,7 +10364,7 @@
       <c r="C276" s="57" t="s">
         <v>261</v>
       </c>
-      <c r="D276" s="122">
+      <c r="D276" s="113">
         <v>3.5</v>
       </c>
       <c r="E276" s="57" t="s">
@@ -10502,7 +10416,7 @@
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A278" s="96" t="s">
+      <c r="A278" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B278" s="54" t="s">
@@ -10558,28 +10472,28 @@
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A280" s="94" t="s">
+      <c r="A280" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B280" s="98" t="s">
+      <c r="B280" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C280" s="117" t="s">
+      <c r="C280" s="21" t="s">
         <v>266</v>
       </c>
       <c r="D280" s="16">
         <v>3.5</v>
       </c>
-      <c r="E280" s="117" t="s">
+      <c r="E280" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="F280" s="117"/>
-      <c r="G280" s="135"/>
-      <c r="H280" s="135"/>
-      <c r="I280" s="135" t="s">
-        <v>34</v>
-      </c>
-      <c r="J280" s="135" t="s">
+      <c r="F280" s="21"/>
+      <c r="G280" s="22"/>
+      <c r="H280" s="22"/>
+      <c r="I280" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J280" s="22" t="s">
         <v>34</v>
       </c>
       <c r="K280" s="9" t="s">
@@ -10590,25 +10504,25 @@
       <c r="A281" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B281" s="98" t="s">
+      <c r="B281" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C281" s="117" t="s">
+      <c r="C281" s="21" t="s">
         <v>266</v>
       </c>
       <c r="D281" s="16">
         <v>3.5</v>
       </c>
-      <c r="E281" s="117" t="s">
+      <c r="E281" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="F281" s="117"/>
-      <c r="G281" s="135"/>
-      <c r="H281" s="135"/>
-      <c r="I281" s="135" t="s">
-        <v>34</v>
-      </c>
-      <c r="J281" s="135" t="s">
+      <c r="F281" s="21"/>
+      <c r="G281" s="22"/>
+      <c r="H281" s="22"/>
+      <c r="I281" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J281" s="22" t="s">
         <v>34</v>
       </c>
       <c r="K281" s="9" t="s">
@@ -10619,25 +10533,25 @@
       <c r="A282" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="B282" s="98" t="s">
+      <c r="B282" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C282" s="117" t="s">
+      <c r="C282" s="21" t="s">
         <v>266</v>
       </c>
       <c r="D282" s="16">
         <v>3.5</v>
       </c>
-      <c r="E282" s="117" t="s">
+      <c r="E282" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="F282" s="117"/>
-      <c r="G282" s="135"/>
-      <c r="H282" s="135"/>
-      <c r="I282" s="135" t="s">
-        <v>34</v>
-      </c>
-      <c r="J282" s="135" t="s">
+      <c r="F282" s="21"/>
+      <c r="G282" s="22"/>
+      <c r="H282" s="22"/>
+      <c r="I282" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J282" s="22" t="s">
         <v>34</v>
       </c>
       <c r="K282" s="9" t="s">
@@ -10645,7 +10559,7 @@
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A283" s="95" t="s">
+      <c r="A283" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B283" s="55" t="s">
@@ -10703,28 +10617,28 @@
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A285" s="94" t="s">
+      <c r="A285" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B285" s="99" t="s">
+      <c r="B285" s="93" t="s">
         <v>150</v>
       </c>
-      <c r="C285" s="114" t="s">
+      <c r="C285" s="107" t="s">
         <v>268</v>
       </c>
-      <c r="D285" s="123">
-        <v>3</v>
-      </c>
-      <c r="E285" s="114"/>
-      <c r="F285" s="114"/>
-      <c r="G285" s="132"/>
-      <c r="H285" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="I285" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="J285" s="132" t="s">
+      <c r="D285" s="114">
+        <v>3</v>
+      </c>
+      <c r="E285" s="107"/>
+      <c r="F285" s="107"/>
+      <c r="G285" s="122"/>
+      <c r="H285" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="I285" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="J285" s="122" t="s">
         <v>34</v>
       </c>
       <c r="K285" s="52" t="s">
@@ -10735,25 +10649,25 @@
       <c r="A286" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B286" s="93" t="s">
+      <c r="B286" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="C286" s="116" t="s">
+      <c r="C286" s="108" t="s">
         <v>268</v>
       </c>
-      <c r="D286" s="125">
-        <v>3</v>
-      </c>
-      <c r="E286" s="116"/>
-      <c r="F286" s="116"/>
-      <c r="G286" s="134"/>
-      <c r="H286" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="I286" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="J286" s="134" t="s">
+      <c r="D286" s="116">
+        <v>3</v>
+      </c>
+      <c r="E286" s="108"/>
+      <c r="F286" s="108"/>
+      <c r="G286" s="123"/>
+      <c r="H286" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="I286" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="J286" s="123" t="s">
         <v>34</v>
       </c>
       <c r="K286" s="32" t="s">
@@ -10764,25 +10678,25 @@
       <c r="A287" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="B287" s="102" t="s">
+      <c r="B287" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="C287" s="115" t="s">
+      <c r="C287" s="58" t="s">
         <v>268</v>
       </c>
-      <c r="D287" s="127">
-        <v>3</v>
-      </c>
-      <c r="E287" s="115"/>
-      <c r="F287" s="115"/>
-      <c r="G287" s="133"/>
-      <c r="H287" s="133" t="s">
-        <v>34</v>
-      </c>
-      <c r="I287" s="133" t="s">
-        <v>34</v>
-      </c>
-      <c r="J287" s="133" t="s">
+      <c r="D287" s="118">
+        <v>3</v>
+      </c>
+      <c r="E287" s="58"/>
+      <c r="F287" s="58"/>
+      <c r="G287" s="61"/>
+      <c r="H287" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="I287" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="J287" s="61" t="s">
         <v>34</v>
       </c>
       <c r="K287" s="42" t="s">
@@ -10790,7 +10704,7 @@
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A288" s="95" t="s">
+      <c r="A288" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B288" s="53" t="s">
@@ -10799,7 +10713,7 @@
       <c r="C288" s="57" t="s">
         <v>268</v>
       </c>
-      <c r="D288" s="122">
+      <c r="D288" s="113">
         <v>3</v>
       </c>
       <c r="E288" s="57"/>
@@ -10847,28 +10761,28 @@
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A290" s="94" t="s">
+      <c r="A290" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B290" s="94" t="s">
+      <c r="B290" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="C290" s="112" t="s">
+      <c r="C290" s="105" t="s">
         <v>270</v>
       </c>
-      <c r="D290" s="124">
-        <v>3</v>
-      </c>
-      <c r="E290" s="112"/>
-      <c r="F290" s="112"/>
-      <c r="G290" s="131"/>
-      <c r="H290" s="131" t="s">
-        <v>34</v>
-      </c>
-      <c r="I290" s="131" t="s">
-        <v>34</v>
-      </c>
-      <c r="J290" s="131" t="s">
+      <c r="D290" s="115">
+        <v>3</v>
+      </c>
+      <c r="E290" s="105"/>
+      <c r="F290" s="105"/>
+      <c r="G290" s="121"/>
+      <c r="H290" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="I290" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="J290" s="121" t="s">
         <v>34</v>
       </c>
       <c r="K290" s="46" t="s">
@@ -10876,28 +10790,28 @@
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A291" s="93" t="s">
+      <c r="A291" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B291" s="104" t="s">
+      <c r="B291" s="97" t="s">
         <v>269</v>
       </c>
-      <c r="C291" s="118" t="s">
+      <c r="C291" s="109" t="s">
         <v>270</v>
       </c>
-      <c r="D291" s="126">
-        <v>3</v>
-      </c>
-      <c r="E291" s="118"/>
-      <c r="F291" s="118"/>
-      <c r="G291" s="136"/>
-      <c r="H291" s="136" t="s">
-        <v>34</v>
-      </c>
-      <c r="I291" s="136" t="s">
-        <v>34</v>
-      </c>
-      <c r="J291" s="136" t="s">
+      <c r="D291" s="117">
+        <v>3</v>
+      </c>
+      <c r="E291" s="109"/>
+      <c r="F291" s="109"/>
+      <c r="G291" s="124"/>
+      <c r="H291" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="I291" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="J291" s="124" t="s">
         <v>34</v>
       </c>
       <c r="K291" s="26" t="s">
@@ -10911,22 +10825,22 @@
       <c r="B292" s="92" t="s">
         <v>269</v>
       </c>
-      <c r="C292" s="119" t="s">
+      <c r="C292" s="110" t="s">
         <v>270</v>
       </c>
       <c r="D292" s="59">
         <v>3</v>
       </c>
-      <c r="E292" s="119"/>
-      <c r="F292" s="119"/>
-      <c r="G292" s="137"/>
-      <c r="H292" s="137" t="s">
-        <v>34</v>
-      </c>
-      <c r="I292" s="137" t="s">
-        <v>34</v>
-      </c>
-      <c r="J292" s="137" t="s">
+      <c r="E292" s="110"/>
+      <c r="F292" s="110"/>
+      <c r="G292" s="125"/>
+      <c r="H292" s="125" t="s">
+        <v>34</v>
+      </c>
+      <c r="I292" s="125" t="s">
+        <v>34</v>
+      </c>
+      <c r="J292" s="125" t="s">
         <v>34</v>
       </c>
       <c r="K292" s="36" t="s">
@@ -10934,7 +10848,7 @@
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A293" s="96" t="s">
+      <c r="A293" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B293" s="54" t="s">
@@ -10994,25 +10908,22 @@
       <c r="A295" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="B295" s="97" t="s">
+      <c r="B295" t="s">
         <v>271</v>
       </c>
-      <c r="C295" s="97" t="s">
+      <c r="C295" t="s">
         <v>272</v>
       </c>
       <c r="D295" s="59">
         <v>4</v>
       </c>
-      <c r="E295" s="97" t="s">
+      <c r="E295" t="s">
         <v>273</v>
       </c>
-      <c r="F295" s="97"/>
-      <c r="G295" s="130"/>
-      <c r="H295" s="130"/>
-      <c r="I295" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J295" s="130" t="s">
+      <c r="I295" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J295" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K295" s="11" t="s">
@@ -11020,7 +10931,7 @@
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A296" s="95" t="s">
+      <c r="A296" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B296" s="53" t="s">
@@ -11029,7 +10940,7 @@
       <c r="C296" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="D296" s="122">
+      <c r="D296" s="113">
         <v>3</v>
       </c>
       <c r="E296" s="57"/>
@@ -11049,30 +10960,28 @@
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A297" s="94" t="s">
+      <c r="A297" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B297" s="97" t="s">
+      <c r="B297" t="s">
         <v>275</v>
       </c>
-      <c r="C297" s="97" t="s">
+      <c r="C297" t="s">
         <v>276</v>
       </c>
       <c r="D297" s="59">
         <v>3</v>
       </c>
-      <c r="E297" s="97"/>
-      <c r="F297" s="97"/>
-      <c r="G297" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H297" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I297" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J297" s="130" t="s">
+      <c r="G297" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H297" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I297" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J297" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K297" s="11" t="s">
@@ -11083,7 +10992,7 @@
       <c r="A298" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="B298" s="97" t="s">
+      <c r="B298" t="s">
         <v>277</v>
       </c>
       <c r="C298" t="s">
@@ -11109,7 +11018,7 @@
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A299" s="96" t="s">
+      <c r="A299" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B299" s="54" t="s">
@@ -11162,30 +11071,28 @@
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A301" s="94" t="s">
+      <c r="A301" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B301" s="97" t="s">
+      <c r="B301" t="s">
         <v>280</v>
       </c>
-      <c r="C301" s="97" t="s">
+      <c r="C301" t="s">
         <v>281</v>
       </c>
       <c r="D301" s="59">
         <v>3</v>
       </c>
-      <c r="E301" s="97"/>
-      <c r="F301" s="97"/>
-      <c r="G301" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H301" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I301" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J301" s="130" t="s">
+      <c r="G301" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H301" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I301" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J301" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K301" s="11" t="s">
@@ -11222,7 +11129,7 @@
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A303" s="95" t="s">
+      <c r="A303" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B303" s="13" t="s">
@@ -11231,7 +11138,7 @@
       <c r="C303" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="D303" s="122">
+      <c r="D303" s="113">
         <v>3</v>
       </c>
       <c r="E303" s="57"/>
@@ -11309,7 +11216,7 @@
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A306" s="95" t="s">
+      <c r="A306" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B306" s="54" t="s">
@@ -11337,30 +11244,30 @@
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A307" s="94" t="s">
+      <c r="A307" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B307" s="99" t="s">
+      <c r="B307" s="93" t="s">
         <v>288</v>
       </c>
-      <c r="C307" s="114" t="s">
+      <c r="C307" s="107" t="s">
         <v>289</v>
       </c>
-      <c r="D307" s="123">
-        <v>3</v>
-      </c>
-      <c r="E307" s="114"/>
-      <c r="F307" s="114"/>
-      <c r="G307" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="H307" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="I307" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="J307" s="132" t="s">
+      <c r="D307" s="114">
+        <v>3</v>
+      </c>
+      <c r="E307" s="107"/>
+      <c r="F307" s="107"/>
+      <c r="G307" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="H307" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="I307" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="J307" s="122" t="s">
         <v>34</v>
       </c>
       <c r="K307" s="52" t="s">
@@ -11368,30 +11275,30 @@
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A308" s="93" t="s">
+      <c r="A308" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B308" s="93" t="s">
+      <c r="B308" s="78" t="s">
         <v>288</v>
       </c>
-      <c r="C308" s="116" t="s">
+      <c r="C308" s="108" t="s">
         <v>289</v>
       </c>
-      <c r="D308" s="125">
-        <v>3</v>
-      </c>
-      <c r="E308" s="116"/>
-      <c r="F308" s="116"/>
-      <c r="G308" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="H308" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="I308" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="J308" s="134" t="s">
+      <c r="D308" s="116">
+        <v>3</v>
+      </c>
+      <c r="E308" s="108"/>
+      <c r="F308" s="108"/>
+      <c r="G308" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="H308" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="I308" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="J308" s="123" t="s">
         <v>34</v>
       </c>
       <c r="K308" s="32" t="s">
@@ -11461,28 +11368,25 @@
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A311" s="94" t="s">
+      <c r="A311" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B311" s="98" t="s">
+      <c r="B311" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="C311" s="97"/>
       <c r="D311" s="16">
         <v>16</v>
       </c>
-      <c r="E311" s="97" t="s">
+      <c r="E311" t="s">
         <v>290</v>
       </c>
-      <c r="F311" s="97"/>
-      <c r="G311" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H311" s="130"/>
-      <c r="I311" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J311" s="130" t="s">
+      <c r="G311" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I311" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J311" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K311" s="18" t="s">
@@ -11490,28 +11394,25 @@
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A312" s="93" t="s">
+      <c r="A312" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B312" s="98" t="s">
+      <c r="B312" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="C312" s="97"/>
       <c r="D312" s="16">
         <v>16</v>
       </c>
-      <c r="E312" s="97" t="s">
+      <c r="E312" t="s">
         <v>290</v>
       </c>
-      <c r="F312" s="97"/>
-      <c r="G312" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H312" s="130"/>
-      <c r="I312" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J312" s="130" t="s">
+      <c r="G312" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I312" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J312" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K312" s="18" t="s">
@@ -11545,7 +11446,7 @@
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A314" s="97" t="s">
+      <c r="A314" t="s">
         <v>296</v>
       </c>
       <c r="B314" s="55" t="s">
@@ -11566,7 +11467,7 @@
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A315" s="97" t="s">
+      <c r="A315" t="s">
         <v>296</v>
       </c>
       <c r="B315" s="55" t="s">
@@ -11592,7 +11493,7 @@
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A316" s="95" t="s">
+      <c r="A316" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B316" s="55" t="s">
@@ -11686,28 +11587,25 @@
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A320" s="94" t="s">
+      <c r="A320" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B320" s="96" t="s">
+      <c r="B320" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="C320" s="97"/>
       <c r="D320" s="17">
         <v>16</v>
       </c>
-      <c r="E320" s="97" t="s">
+      <c r="E320" t="s">
         <v>36</v>
       </c>
-      <c r="F320" s="97"/>
-      <c r="G320" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H320" s="130"/>
-      <c r="I320" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J320" s="130" t="s">
+      <c r="G320" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I320" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J320" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K320" s="18" t="s">
@@ -11715,28 +11613,25 @@
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A321" s="93" t="s">
+      <c r="A321" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B321" s="96" t="s">
+      <c r="B321" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="C321" s="97"/>
       <c r="D321" s="17">
         <v>16</v>
       </c>
-      <c r="E321" s="97" t="s">
+      <c r="E321" t="s">
         <v>36</v>
       </c>
-      <c r="F321" s="97"/>
-      <c r="G321" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H321" s="130"/>
-      <c r="I321" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J321" s="130" t="s">
+      <c r="G321" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I321" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J321" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K321" s="18" t="s">
@@ -11770,7 +11665,7 @@
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A323" s="97" t="s">
+      <c r="A323" t="s">
         <v>296</v>
       </c>
       <c r="B323" s="55" t="s">
@@ -11796,7 +11691,7 @@
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A324" s="95" t="s">
+      <c r="A324" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B324" s="54" t="s">
@@ -11848,28 +11743,25 @@
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A326" s="94" t="s">
+      <c r="A326" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B326" s="98" t="s">
+      <c r="B326" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C326" s="97"/>
       <c r="D326" s="16">
         <v>16</v>
       </c>
-      <c r="E326" s="97" t="s">
+      <c r="E326" t="s">
         <v>42</v>
       </c>
-      <c r="F326" s="97"/>
-      <c r="G326" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H326" s="130"/>
-      <c r="I326" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J326" s="130" t="s">
+      <c r="G326" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I326" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J326" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K326" s="18" t="s">
@@ -11877,28 +11769,25 @@
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A327" s="93" t="s">
+      <c r="A327" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B327" s="98" t="s">
+      <c r="B327" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C327" s="97"/>
       <c r="D327" s="16">
         <v>16</v>
       </c>
-      <c r="E327" s="97" t="s">
+      <c r="E327" t="s">
         <v>42</v>
       </c>
-      <c r="F327" s="97"/>
-      <c r="G327" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H327" s="130"/>
-      <c r="I327" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J327" s="130" t="s">
+      <c r="G327" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I327" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J327" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K327" s="18" t="s">
@@ -11932,7 +11821,7 @@
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A329" s="95" t="s">
+      <c r="A329" s="53" t="s">
         <v>31</v>
       </c>
       <c r="B329" s="55" t="s">
@@ -11984,30 +11873,28 @@
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A331" s="94" t="s">
+      <c r="A331" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B331" s="98" t="s">
+      <c r="B331" s="55" t="s">
         <v>472</v>
       </c>
-      <c r="C331" s="97" t="s">
+      <c r="C331" t="s">
         <v>474</v>
       </c>
       <c r="D331" s="16">
         <v>3</v>
       </c>
-      <c r="E331" s="97"/>
-      <c r="F331" s="97"/>
-      <c r="G331" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H331" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I331" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J331" s="130" t="s">
+      <c r="G331" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H331" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I331" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J331" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K331" s="18" t="s">
@@ -12015,30 +11902,28 @@
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A332" s="93" t="s">
+      <c r="A332" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B332" s="98" t="s">
+      <c r="B332" s="55" t="s">
         <v>472</v>
       </c>
-      <c r="C332" s="97" t="s">
+      <c r="C332" t="s">
         <v>474</v>
       </c>
       <c r="D332" s="16">
         <v>3</v>
       </c>
-      <c r="E332" s="97"/>
-      <c r="F332" s="97"/>
-      <c r="G332" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H332" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I332" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J332" s="130" t="s">
+      <c r="G332" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H332" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I332" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J332" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K332" s="18" t="s">
@@ -12049,10 +11934,10 @@
       <c r="A333" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="B333" s="98" t="s">
+      <c r="B333" s="55" t="s">
         <v>472</v>
       </c>
-      <c r="C333" s="97" t="s">
+      <c r="C333" t="s">
         <v>474</v>
       </c>
       <c r="D333" s="16">
@@ -12075,13 +11960,13 @@
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A334" s="96" t="s">
+      <c r="A334" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B334" s="98" t="s">
+      <c r="B334" s="55" t="s">
         <v>472</v>
       </c>
-      <c r="C334" s="97" t="s">
+      <c r="C334" t="s">
         <v>474</v>
       </c>
       <c r="D334" s="16">
@@ -12107,10 +11992,10 @@
       <c r="A335" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B335" s="98" t="s">
+      <c r="B335" s="55" t="s">
         <v>472</v>
       </c>
-      <c r="C335" s="97" t="s">
+      <c r="C335" t="s">
         <v>474</v>
       </c>
       <c r="D335" s="16">
@@ -12133,30 +12018,28 @@
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A336" s="94" t="s">
+      <c r="A336" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="B336" s="98" t="s">
+      <c r="B336" s="55" t="s">
         <v>473</v>
       </c>
-      <c r="C336" s="97" t="s">
+      <c r="C336" t="s">
         <v>292</v>
       </c>
       <c r="D336" s="16">
         <v>3</v>
       </c>
-      <c r="E336" s="97"/>
-      <c r="F336" s="97"/>
-      <c r="G336" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H336" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I336" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J336" s="130" t="s">
+      <c r="G336" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H336" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I336" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J336" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K336" s="18" t="s">
@@ -12164,30 +12047,28 @@
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A337" s="93" t="s">
+      <c r="A337" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B337" s="98" t="s">
+      <c r="B337" s="55" t="s">
         <v>473</v>
       </c>
-      <c r="C337" s="97" t="s">
+      <c r="C337" t="s">
         <v>292</v>
       </c>
       <c r="D337" s="16">
         <v>3</v>
       </c>
-      <c r="E337" s="97"/>
-      <c r="F337" s="97"/>
-      <c r="G337" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="H337" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="I337" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="J337" s="130" t="s">
+      <c r="G337" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H337" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I337" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J337" s="20" t="s">
         <v>34</v>
       </c>
       <c r="K337" s="18" t="s">
@@ -12198,7 +12079,7 @@
       <c r="A338" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="B338" s="98" t="s">
+      <c r="B338" s="55" t="s">
         <v>473</v>
       </c>
       <c r="C338" t="s">
@@ -12224,10 +12105,10 @@
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A339" s="96" t="s">
+      <c r="A339" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="B339" s="98" t="s">
+      <c r="B339" s="55" t="s">
         <v>473</v>
       </c>
       <c r="C339" t="s">
@@ -12256,7 +12137,7 @@
       <c r="A340" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B340" s="98" t="s">
+      <c r="B340" s="55" t="s">
         <v>473</v>
       </c>
       <c r="C340" t="s">
@@ -12283,7 +12164,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K335" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K335">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K340">
       <sortCondition ref="B1:B335"/>
     </sortState>
   </autoFilter>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0 COOP Local\coop-planner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675FC789-C407-4C57-98C0-DF10AB7E0262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A09F586-6044-4C69-BDAA-5C291465663F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coursses" sheetId="1" r:id="rId1"/>
@@ -1470,37 +1470,38 @@
     <t>PHYS 204; MATH 204; ENGR 213</t>
   </si>
   <si>
+    <t>2026-2027 Summer : If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
+  </si>
+  <si>
+    <t>2026-2027 Fall: If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
+  </si>
+  <si>
+    <t>2027-2028 Winter: If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
+  </si>
+  <si>
+    <t>2028-2029 Summer: If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
+  </si>
+  <si>
+    <t>Z- OTHER 1</t>
+  </si>
+  <si>
+    <t>Z- OTHER 2</t>
+  </si>
+  <si>
+    <t>ECP gen elect - OR  - Course not related to Program (e.g., minor)</t>
+  </si>
+  <si>
     <t>MIAE 383 (answer COMPLIANT if sequence complies to):
-Aero A:
-•	If you complete AERO 446 by Winter 2026, you do not take MIAE383
-•	If you do not complete AERO 446 by Winter 2026, you must take MIAE383.
-Aero B:
-•	If you complete ENGR 251 by Winter 2026, then you do not take AERO253, you must take MECH352 (use OTHER), you do not take MIAE383.
-•	If you do not complete ENGR 251 by Winter 2026, then you must take AERO253 and MIAE383.
-Aero C:
-•	If you complete ENGR251 by Winter 2026, then you do not take AERO 253, you do not take MIAE383.
-•	If you do not complete ENGR 251 by Winter 2026, then you must take AERO253 and MIAE383.</t>
-  </si>
-  <si>
-    <t>2026-2027 Summer : If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
-  </si>
-  <si>
-    <t>2026-2027 Fall: If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
-  </si>
-  <si>
-    <t>2027-2028 Winter: If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
-  </si>
-  <si>
-    <t>2028-2029 Summer: If not already COOP planned as a WT (if not written W-1, W-2 or W-3 in blue above), only students with an internship in hand (including WT extension) are accepted.</t>
-  </si>
-  <si>
-    <t>Z- OTHER 1</t>
-  </si>
-  <si>
-    <t>Z- OTHER 2</t>
-  </si>
-  <si>
-    <t>ECP gen elect - OR  - Course not related to Program (e.g., minor)</t>
+Students who are admitted or re‑admitted in Fall 2026 or later are required to take MIAE 383 as part of their core program requirements. This implies that they must adhere to the new 2026-27 sequence.
+Students who were admitted before Fall 2026, please follow the transition measures below:
+AERO Option A:
+·       You must complete AERO446, you do not need to take MIAE383 (revised on April 2nd, 2026)
+AERO Option B:
+·       If you complete ENGR 251 by Winter 2026, then you do not take AERO253, you must take MECH352, you do not take MIAE383.
+·       If you do not complete ENGR 251 by Winter 2026, then you must take AERO253 and MIAE383.
+Aero Option C:
+·       If you complete ENGR251 by Winter 2026, then you do not take AERO 253, you do not take MIAE383.
+·       If you do not complete ENGR 251 by Winter 2026, then you must take AERO253 and MIAE383.</t>
   </si>
 </sst>
 </file>
@@ -2396,23 +2397,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U340"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.5546875" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" customWidth="1"/>
-    <col min="4" max="4" width="6.109375" customWidth="1"/>
-    <col min="5" max="5" width="56.5546875" customWidth="1"/>
-    <col min="6" max="6" width="36.109375" customWidth="1"/>
-    <col min="7" max="10" width="11.88671875" style="20" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
+    <col min="5" max="5" width="56.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="10" width="11.85546875" style="20" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -2447,7 +2448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>31</v>
       </c>
@@ -2474,7 +2475,7 @@
       <c r="P2" s="2"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>37</v>
       </c>
@@ -2504,7 +2505,7 @@
       <c r="P3" s="2"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
         <v>43</v>
       </c>
@@ -2534,7 +2535,7 @@
       <c r="P4" s="2"/>
       <c r="U4" s="3"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>46</v>
       </c>
@@ -2563,7 +2564,7 @@
       </c>
       <c r="U5" s="3"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>43</v>
       </c>
@@ -2591,7 +2592,7 @@
       </c>
       <c r="U6" s="3"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>46</v>
       </c>
@@ -2619,7 +2620,7 @@
       </c>
       <c r="U7" s="3"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
         <v>37</v>
       </c>
@@ -2651,7 +2652,7 @@
       </c>
       <c r="U8" s="3"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>43</v>
       </c>
@@ -2683,7 +2684,7 @@
       </c>
       <c r="U9" s="3"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>46</v>
       </c>
@@ -2715,7 +2716,7 @@
       </c>
       <c r="U10" s="3"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
         <v>37</v>
       </c>
@@ -2747,7 +2748,7 @@
       </c>
       <c r="U11" s="3"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
         <v>43</v>
       </c>
@@ -2779,7 +2780,7 @@
       </c>
       <c r="U12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>46</v>
       </c>
@@ -2811,7 +2812,7 @@
       </c>
       <c r="U13" s="3"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
         <v>37</v>
       </c>
@@ -2841,7 +2842,7 @@
       </c>
       <c r="U14" s="3"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
         <v>43</v>
       </c>
@@ -2871,7 +2872,7 @@
       </c>
       <c r="U15" s="3"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>46</v>
       </c>
@@ -2901,7 +2902,7 @@
       </c>
       <c r="U16" s="3"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="43" t="s">
         <v>37</v>
       </c>
@@ -2931,7 +2932,7 @@
       </c>
       <c r="U17" s="3"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
         <v>43</v>
       </c>
@@ -2961,7 +2962,7 @@
       </c>
       <c r="U18" s="3"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>46</v>
       </c>
@@ -2991,7 +2992,7 @@
       </c>
       <c r="U19" s="3"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
         <v>43</v>
       </c>
@@ -3019,7 +3020,7 @@
       </c>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>37</v>
       </c>
@@ -3047,7 +3048,7 @@
       </c>
       <c r="U21" s="3"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
         <v>37</v>
       </c>
@@ -3075,7 +3076,7 @@
       </c>
       <c r="U22" s="3"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
         <v>37</v>
       </c>
@@ -3105,7 +3106,7 @@
       </c>
       <c r="U23" s="3"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
         <v>37</v>
       </c>
@@ -3133,7 +3134,7 @@
       </c>
       <c r="U24" s="3"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
         <v>37</v>
       </c>
@@ -3161,7 +3162,7 @@
       </c>
       <c r="U25" s="3"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
         <v>43</v>
       </c>
@@ -3189,7 +3190,7 @@
       </c>
       <c r="U26" s="3"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="33" t="s">
         <v>46</v>
       </c>
@@ -3217,7 +3218,7 @@
       </c>
       <c r="U27" s="3"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>46</v>
       </c>
@@ -3245,7 +3246,7 @@
       </c>
       <c r="U28" s="3"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>43</v>
       </c>
@@ -3273,7 +3274,7 @@
       </c>
       <c r="U29" s="3"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
         <v>43</v>
       </c>
@@ -3301,7 +3302,7 @@
       </c>
       <c r="U30" s="3"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>37</v>
       </c>
@@ -3329,7 +3330,7 @@
       </c>
       <c r="U31" s="3"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>43</v>
       </c>
@@ -3357,7 +3358,7 @@
       </c>
       <c r="U32" s="3"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>46</v>
       </c>
@@ -3385,7 +3386,7 @@
       </c>
       <c r="U33" s="3"/>
     </row>
-    <row r="34" spans="1:21" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" s="66" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="62" t="s">
         <v>37</v>
       </c>
@@ -3413,7 +3414,7 @@
       </c>
       <c r="U34" s="67"/>
     </row>
-    <row r="35" spans="1:21" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" s="66" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
         <v>43</v>
       </c>
@@ -3441,7 +3442,7 @@
       </c>
       <c r="U35" s="67"/>
     </row>
-    <row r="36" spans="1:21" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" s="66" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="69" t="s">
         <v>46</v>
       </c>
@@ -3469,7 +3470,7 @@
       </c>
       <c r="U36" s="67"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>37</v>
       </c>
@@ -3499,7 +3500,7 @@
       </c>
       <c r="U37" s="3"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="78" t="s">
         <v>43</v>
       </c>
@@ -3529,7 +3530,7 @@
       </c>
       <c r="U38" s="3"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="92" t="s">
         <v>46</v>
       </c>
@@ -3559,7 +3560,7 @@
       </c>
       <c r="U39" s="3"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="54" t="s">
         <v>31</v>
       </c>
@@ -3589,7 +3590,7 @@
       </c>
       <c r="U40" s="3"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
@@ -3619,7 +3620,7 @@
       </c>
       <c r="U41" s="3"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
         <v>46</v>
       </c>
@@ -3651,7 +3652,7 @@
       </c>
       <c r="U42" s="3"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>46</v>
       </c>
@@ -3683,7 +3684,7 @@
       </c>
       <c r="U43" s="3"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>46</v>
       </c>
@@ -3715,7 +3716,7 @@
       </c>
       <c r="U44" s="3"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
         <v>46</v>
       </c>
@@ -3747,7 +3748,7 @@
       </c>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
         <v>46</v>
       </c>
@@ -3779,7 +3780,7 @@
       </c>
       <c r="U46" s="3"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>46</v>
       </c>
@@ -3809,7 +3810,7 @@
       </c>
       <c r="U47" s="3"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="33" t="s">
         <v>46</v>
       </c>
@@ -3841,7 +3842,7 @@
       </c>
       <c r="U48" s="3"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="33" t="s">
         <v>46</v>
       </c>
@@ -3873,7 +3874,7 @@
       </c>
       <c r="U49" s="3"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
         <v>46</v>
       </c>
@@ -3905,7 +3906,7 @@
       </c>
       <c r="U50" s="3"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
         <v>46</v>
       </c>
@@ -3933,7 +3934,7 @@
       </c>
       <c r="U51" s="3"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
         <v>46</v>
       </c>
@@ -3960,7 +3961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="43" t="s">
         <v>37</v>
       </c>
@@ -3993,7 +3994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
         <v>43</v>
       </c>
@@ -4026,7 +4027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="33" t="s">
         <v>46</v>
       </c>
@@ -4059,7 +4060,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>31</v>
       </c>
@@ -4092,7 +4093,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>41</v>
       </c>
@@ -4125,7 +4126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>37</v>
       </c>
@@ -4154,7 +4155,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
         <v>43</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="33" t="s">
         <v>46</v>
       </c>
@@ -4212,7 +4213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>31</v>
       </c>
@@ -4241,7 +4242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>41</v>
       </c>
@@ -4270,7 +4271,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>37</v>
       </c>
@@ -4299,7 +4300,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
         <v>43</v>
       </c>
@@ -4328,7 +4329,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="33" t="s">
         <v>46</v>
       </c>
@@ -4357,7 +4358,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
         <v>31</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>41</v>
       </c>
@@ -4415,7 +4416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
         <v>37</v>
       </c>
@@ -4448,7 +4449,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
         <v>43</v>
       </c>
@@ -4481,7 +4482,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
         <v>46</v>
       </c>
@@ -4514,7 +4515,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>31</v>
       </c>
@@ -4547,7 +4548,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>41</v>
       </c>
@@ -4580,7 +4581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>37</v>
       </c>
@@ -4613,7 +4614,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
         <v>43</v>
       </c>
@@ -4646,7 +4647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="33" t="s">
         <v>46</v>
       </c>
@@ -4679,7 +4680,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
         <v>31</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>41</v>
       </c>
@@ -4745,7 +4746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="43" t="s">
         <v>37</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="29" t="s">
         <v>43</v>
       </c>
@@ -4807,7 +4808,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>46</v>
       </c>
@@ -4838,7 +4839,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>41</v>
       </c>
@@ -4869,7 +4870,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="43" t="s">
         <v>37</v>
       </c>
@@ -4900,7 +4901,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="29" t="s">
         <v>43</v>
       </c>
@@ -4931,7 +4932,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>46</v>
       </c>
@@ -4960,7 +4961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>41</v>
       </c>
@@ -4990,7 +4991,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>37</v>
       </c>
@@ -5022,7 +5023,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="29" t="s">
         <v>43</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="s">
         <v>46</v>
       </c>
@@ -5086,7 +5087,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>41</v>
       </c>
@@ -5119,7 +5120,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>31</v>
       </c>
@@ -5149,7 +5150,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="77" t="s">
         <v>37</v>
       </c>
@@ -5182,7 +5183,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="53" t="s">
         <v>31</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="54" t="s">
         <v>41</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="43" t="s">
         <v>37</v>
       </c>
@@ -5281,7 +5282,7 @@
       <c r="P94" s="43"/>
       <c r="U94" s="48"/>
     </row>
-    <row r="95" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="29" t="s">
         <v>43</v>
       </c>
@@ -5314,7 +5315,7 @@
       <c r="P95" s="43"/>
       <c r="U95" s="48"/>
     </row>
-    <row r="96" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
         <v>46</v>
       </c>
@@ -5347,7 +5348,7 @@
       <c r="P96" s="43"/>
       <c r="U96" s="48"/>
     </row>
-    <row r="97" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>31</v>
       </c>
@@ -5380,7 +5381,7 @@
       <c r="P97" s="43"/>
       <c r="U97" s="48"/>
     </row>
-    <row r="98" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>41</v>
       </c>
@@ -5412,7 +5413,7 @@
       </c>
       <c r="U98" s="48"/>
     </row>
-    <row r="99" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="43" t="s">
         <v>37</v>
       </c>
@@ -5446,7 +5447,7 @@
       </c>
       <c r="U99" s="48"/>
     </row>
-    <row r="100" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="29" t="s">
         <v>43</v>
       </c>
@@ -5480,7 +5481,7 @@
       </c>
       <c r="U100" s="48"/>
     </row>
-    <row r="101" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>31</v>
       </c>
@@ -5514,7 +5515,7 @@
       </c>
       <c r="U101" s="48"/>
     </row>
-    <row r="102" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>41</v>
       </c>
@@ -5548,7 +5549,7 @@
       </c>
       <c r="U102" s="48"/>
     </row>
-    <row r="103" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
         <v>37</v>
       </c>
@@ -5580,7 +5581,7 @@
       </c>
       <c r="U103" s="48"/>
     </row>
-    <row r="104" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
         <v>43</v>
       </c>
@@ -5612,7 +5613,7 @@
       </c>
       <c r="U104" s="48"/>
     </row>
-    <row r="105" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33" t="s">
         <v>46</v>
       </c>
@@ -5644,7 +5645,7 @@
       </c>
       <c r="U105" s="48"/>
     </row>
-    <row r="106" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>41</v>
       </c>
@@ -5676,7 +5677,7 @@
       </c>
       <c r="U106" s="48"/>
     </row>
-    <row r="107" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
         <v>37</v>
       </c>
@@ -5710,7 +5711,7 @@
       </c>
       <c r="U107" s="48"/>
     </row>
-    <row r="108" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="29" t="s">
         <v>43</v>
       </c>
@@ -5744,7 +5745,7 @@
       </c>
       <c r="U108" s="48"/>
     </row>
-    <row r="109" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33" t="s">
         <v>46</v>
       </c>
@@ -5779,7 +5780,7 @@
       <c r="P109" s="23"/>
       <c r="U109" s="28"/>
     </row>
-    <row r="110" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>31</v>
       </c>
@@ -5814,7 +5815,7 @@
       <c r="P110" s="29"/>
       <c r="U110" s="28"/>
     </row>
-    <row r="111" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>41</v>
       </c>
@@ -5849,7 +5850,7 @@
       <c r="P111" s="23"/>
       <c r="U111" s="28"/>
     </row>
-    <row r="112" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="43" t="s">
         <v>37</v>
       </c>
@@ -5882,7 +5883,7 @@
       <c r="P112" s="23"/>
       <c r="U112" s="28"/>
     </row>
-    <row r="113" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="29" t="s">
         <v>43</v>
       </c>
@@ -5915,7 +5916,7 @@
       <c r="P113" s="23"/>
       <c r="U113" s="28"/>
     </row>
-    <row r="114" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33" t="s">
         <v>46</v>
       </c>
@@ -5948,7 +5949,7 @@
       <c r="P114" s="23"/>
       <c r="U114" s="28"/>
     </row>
-    <row r="115" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
         <v>31</v>
       </c>
@@ -5980,7 +5981,7 @@
       </c>
       <c r="U115" s="28"/>
     </row>
-    <row r="116" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>41</v>
       </c>
@@ -6012,7 +6013,7 @@
       </c>
       <c r="U116" s="28"/>
     </row>
-    <row r="117" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="43" t="s">
         <v>37</v>
       </c>
@@ -6046,7 +6047,7 @@
       </c>
       <c r="U117" s="28"/>
     </row>
-    <row r="118" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="29" t="s">
         <v>43</v>
       </c>
@@ -6080,7 +6081,7 @@
       </c>
       <c r="U118" s="28"/>
     </row>
-    <row r="119" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="33" t="s">
         <v>46</v>
       </c>
@@ -6114,7 +6115,7 @@
       </c>
       <c r="U119" s="28"/>
     </row>
-    <row r="120" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>31</v>
       </c>
@@ -6148,7 +6149,7 @@
       </c>
       <c r="U120" s="28"/>
     </row>
-    <row r="121" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>41</v>
       </c>
@@ -6182,7 +6183,7 @@
       </c>
       <c r="U121" s="28"/>
     </row>
-    <row r="122" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="18" t="s">
         <v>294</v>
       </c>
@@ -6208,7 +6209,7 @@
       </c>
       <c r="U122" s="28"/>
     </row>
-    <row r="123" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="18" t="s">
         <v>294</v>
       </c>
@@ -6234,7 +6235,7 @@
       </c>
       <c r="U123" s="28"/>
     </row>
-    <row r="124" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
         <v>294</v>
       </c>
@@ -6264,7 +6265,7 @@
       </c>
       <c r="U124" s="28"/>
     </row>
-    <row r="125" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
         <v>295</v>
       </c>
@@ -6294,7 +6295,7 @@
       </c>
       <c r="U125" s="28"/>
     </row>
-    <row r="126" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="18" t="s">
         <v>295</v>
       </c>
@@ -6325,7 +6326,7 @@
       <c r="P126" s="33"/>
       <c r="U126" s="38"/>
     </row>
-    <row r="127" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>296</v>
       </c>
@@ -6356,7 +6357,7 @@
       <c r="P127" s="39"/>
       <c r="U127" s="38"/>
     </row>
-    <row r="128" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="18" t="s">
         <v>294</v>
       </c>
@@ -6387,7 +6388,7 @@
       <c r="P128" s="33"/>
       <c r="U128" s="38"/>
     </row>
-    <row r="129" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
         <v>295</v>
       </c>
@@ -6418,7 +6419,7 @@
       <c r="P129" s="33"/>
       <c r="U129" s="38"/>
     </row>
-    <row r="130" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="18" t="s">
         <v>296</v>
       </c>
@@ -6449,7 +6450,7 @@
       <c r="P130" s="33"/>
       <c r="U130" s="38"/>
     </row>
-    <row r="131" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="18" t="s">
         <v>294</v>
       </c>
@@ -6480,7 +6481,7 @@
       <c r="P131" s="33"/>
       <c r="U131" s="38"/>
     </row>
-    <row r="132" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="18" t="s">
         <v>295</v>
       </c>
@@ -6510,7 +6511,7 @@
       </c>
       <c r="U132" s="38"/>
     </row>
-    <row r="133" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="18" t="s">
         <v>296</v>
       </c>
@@ -6540,7 +6541,7 @@
       </c>
       <c r="U133" s="38"/>
     </row>
-    <row r="134" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="18" t="s">
         <v>294</v>
       </c>
@@ -6570,7 +6571,7 @@
       </c>
       <c r="U134" s="38"/>
     </row>
-    <row r="135" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18" t="s">
         <v>295</v>
       </c>
@@ -6600,7 +6601,7 @@
       </c>
       <c r="U135" s="38"/>
     </row>
-    <row r="136" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>296</v>
       </c>
@@ -6630,7 +6631,7 @@
       </c>
       <c r="U136" s="73"/>
     </row>
-    <row r="137" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="18" t="s">
         <v>294</v>
       </c>
@@ -6660,7 +6661,7 @@
       </c>
       <c r="U137" s="38"/>
     </row>
-    <row r="138" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="18" t="s">
         <v>295</v>
       </c>
@@ -6690,7 +6691,7 @@
       </c>
       <c r="U138" s="38"/>
     </row>
-    <row r="139" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>296</v>
       </c>
@@ -6720,7 +6721,7 @@
       </c>
       <c r="U139" s="38"/>
     </row>
-    <row r="140" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="18" t="s">
         <v>294</v>
       </c>
@@ -6750,7 +6751,7 @@
       </c>
       <c r="U140" s="38"/>
     </row>
-    <row r="141" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="18" t="s">
         <v>295</v>
       </c>
@@ -6780,7 +6781,7 @@
       </c>
       <c r="U141" s="38"/>
     </row>
-    <row r="142" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="18" t="s">
         <v>296</v>
       </c>
@@ -6811,7 +6812,7 @@
       <c r="P142" s="43"/>
       <c r="U142" s="48"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="18" t="s">
         <v>294</v>
       </c>
@@ -6837,7 +6838,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="18" t="s">
         <v>295</v>
       </c>
@@ -6863,7 +6864,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="18" t="s">
         <v>296</v>
       </c>
@@ -6889,7 +6890,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="18" t="s">
         <v>294</v>
       </c>
@@ -6915,7 +6916,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="18" t="s">
         <v>295</v>
       </c>
@@ -6941,7 +6942,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="18" t="s">
         <v>296</v>
       </c>
@@ -6967,7 +6968,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="18" t="s">
         <v>294</v>
       </c>
@@ -6993,7 +6994,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="18" t="s">
         <v>295</v>
       </c>
@@ -7019,7 +7020,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
         <v>296</v>
       </c>
@@ -7045,7 +7046,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="18" t="s">
         <v>294</v>
       </c>
@@ -7071,7 +7072,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
         <v>295</v>
       </c>
@@ -7097,7 +7098,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="18" t="s">
         <v>296</v>
       </c>
@@ -7123,7 +7124,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="18" t="s">
         <v>294</v>
       </c>
@@ -7149,7 +7150,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="18" t="s">
         <v>295</v>
       </c>
@@ -7175,7 +7176,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="18" t="s">
         <v>296</v>
       </c>
@@ -7201,7 +7202,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="18" t="s">
         <v>294</v>
       </c>
@@ -7227,7 +7228,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
         <v>295</v>
       </c>
@@ -7253,7 +7254,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="18" t="s">
         <v>296</v>
       </c>
@@ -7279,7 +7280,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="18" t="s">
         <v>294</v>
       </c>
@@ -7305,7 +7306,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
         <v>295</v>
       </c>
@@ -7331,7 +7332,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="18" t="s">
         <v>296</v>
       </c>
@@ -7357,7 +7358,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="18" t="s">
         <v>294</v>
       </c>
@@ -7383,7 +7384,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="18" t="s">
         <v>295</v>
       </c>
@@ -7409,7 +7410,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
         <v>294</v>
       </c>
@@ -7435,7 +7436,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="18" t="s">
         <v>295</v>
       </c>
@@ -7461,7 +7462,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="18" t="s">
         <v>295</v>
       </c>
@@ -7487,7 +7488,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="18" t="s">
         <v>296</v>
       </c>
@@ -7513,7 +7514,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="18" t="s">
         <v>294</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
         <v>295</v>
       </c>
@@ -7565,7 +7566,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="18" t="s">
         <v>296</v>
       </c>
@@ -7591,7 +7592,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="18" t="s">
         <v>294</v>
       </c>
@@ -7617,7 +7618,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="174" spans="1:11" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" s="66" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="18" t="s">
         <v>295</v>
       </c>
@@ -7646,7 +7647,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="18" t="s">
         <v>294</v>
       </c>
@@ -7672,7 +7673,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="18" t="s">
         <v>295</v>
       </c>
@@ -7698,7 +7699,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="18" t="s">
         <v>295</v>
       </c>
@@ -7724,7 +7725,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="18" t="s">
         <v>296</v>
       </c>
@@ -7750,7 +7751,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="18" t="s">
         <v>294</v>
       </c>
@@ -7776,7 +7777,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="18" t="s">
         <v>295</v>
       </c>
@@ -7802,7 +7803,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="18" t="s">
         <v>296</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="18" t="s">
         <v>294</v>
       </c>
@@ -7854,7 +7855,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="18" t="s">
         <v>295</v>
       </c>
@@ -7880,7 +7881,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="18" t="s">
         <v>294</v>
       </c>
@@ -7906,7 +7907,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="18" t="s">
         <v>295</v>
       </c>
@@ -7932,7 +7933,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="18" t="s">
         <v>295</v>
       </c>
@@ -7958,7 +7959,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="18" t="s">
         <v>296</v>
       </c>
@@ -7984,7 +7985,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="18" t="s">
         <v>294</v>
       </c>
@@ -8010,7 +8011,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="18" t="s">
         <v>295</v>
       </c>
@@ -8036,7 +8037,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="18" t="s">
         <v>296</v>
       </c>
@@ -8062,7 +8063,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="18" t="s">
         <v>294</v>
       </c>
@@ -8088,7 +8089,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="18" t="s">
         <v>295</v>
       </c>
@@ -8114,7 +8115,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="18" t="s">
         <v>294</v>
       </c>
@@ -8140,7 +8141,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="18" t="s">
         <v>295</v>
       </c>
@@ -8166,7 +8167,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="18" t="s">
         <v>295</v>
       </c>
@@ -8192,7 +8193,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="18" t="s">
         <v>296</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>294</v>
       </c>
@@ -8244,7 +8245,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="18" t="s">
         <v>295</v>
       </c>
@@ -8270,7 +8271,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="18" t="s">
         <v>296</v>
       </c>
@@ -8296,7 +8297,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="18" t="s">
         <v>294</v>
       </c>
@@ -8322,7 +8323,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="18" t="s">
         <v>295</v>
       </c>
@@ -8348,7 +8349,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="13" t="s">
         <v>31</v>
       </c>
@@ -8368,7 +8369,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="13" t="s">
         <v>31</v>
       </c>
@@ -8391,7 +8392,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="13" t="s">
         <v>31</v>
       </c>
@@ -8418,7 +8419,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>31</v>
       </c>
@@ -8442,7 +8443,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="13" t="s">
         <v>31</v>
       </c>
@@ -8471,7 +8472,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="13" t="s">
         <v>31</v>
       </c>
@@ -8498,7 +8499,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>31</v>
       </c>
@@ -8524,7 +8525,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>31</v>
       </c>
@@ -8548,7 +8549,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="13" t="s">
         <v>31</v>
       </c>
@@ -8575,7 +8576,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>31</v>
       </c>
@@ -8599,7 +8600,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="13" t="s">
         <v>31</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>31</v>
       </c>
@@ -8652,7 +8653,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="13" t="s">
         <v>31</v>
       </c>
@@ -8676,7 +8677,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>31</v>
       </c>
@@ -8702,7 +8703,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="70" t="s">
         <v>31</v>
       </c>
@@ -8729,7 +8730,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="18" t="s">
         <v>294</v>
       </c>
@@ -8749,7 +8750,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="18" t="s">
         <v>294</v>
       </c>
@@ -8769,7 +8770,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="43" t="s">
         <v>37</v>
       </c>
@@ -8798,7 +8799,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="29" t="s">
         <v>43</v>
       </c>
@@ -8827,7 +8828,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="33" t="s">
         <v>46</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="13" t="s">
         <v>31</v>
       </c>
@@ -8885,7 +8886,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>41</v>
       </c>
@@ -8913,7 +8914,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="43" t="s">
         <v>37</v>
       </c>
@@ -8942,7 +8943,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="29" t="s">
         <v>43</v>
       </c>
@@ -8971,7 +8972,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="33" t="s">
         <v>46</v>
       </c>
@@ -9000,7 +9001,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>31</v>
       </c>
@@ -9029,7 +9030,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>41</v>
       </c>
@@ -9058,7 +9059,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="43" t="s">
         <v>37</v>
       </c>
@@ -9087,7 +9088,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="29" t="s">
         <v>43</v>
       </c>
@@ -9116,7 +9117,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="s">
         <v>46</v>
       </c>
@@ -9145,7 +9146,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="13" t="s">
         <v>31</v>
       </c>
@@ -9174,7 +9175,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>41</v>
       </c>
@@ -9203,7 +9204,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>41</v>
       </c>
@@ -9230,7 +9231,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="43" t="s">
         <v>37</v>
       </c>
@@ -9257,7 +9258,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="29" t="s">
         <v>43</v>
       </c>
@@ -9284,7 +9285,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="54" t="s">
         <v>41</v>
       </c>
@@ -9311,7 +9312,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="55" t="s">
         <v>41</v>
       </c>
@@ -9342,7 +9343,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="43" t="s">
         <v>37</v>
       </c>
@@ -9368,7 +9369,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>41</v>
       </c>
@@ -9395,7 +9396,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="43" t="s">
         <v>37</v>
       </c>
@@ -9421,7 +9422,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>41</v>
       </c>
@@ -9450,7 +9451,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="43" t="s">
         <v>37</v>
       </c>
@@ -9476,7 +9477,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>41</v>
       </c>
@@ -9503,7 +9504,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>41</v>
       </c>
@@ -9532,7 +9533,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>41</v>
       </c>
@@ -9562,7 +9563,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="29" t="s">
         <v>43</v>
       </c>
@@ -9585,7 +9586,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>41</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="78" t="s">
         <v>43</v>
       </c>
@@ -9641,7 +9642,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="54" t="s">
         <v>41</v>
       </c>
@@ -9671,7 +9672,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="55" t="s">
         <v>41</v>
       </c>
@@ -9702,7 +9703,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="78" t="s">
         <v>43</v>
       </c>
@@ -9725,7 +9726,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="78" t="s">
         <v>43</v>
       </c>
@@ -9748,7 +9749,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="77" t="s">
         <v>37</v>
       </c>
@@ -9771,7 +9772,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="55" t="s">
         <v>41</v>
       </c>
@@ -9798,7 +9799,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="80" t="s">
         <v>41</v>
       </c>
@@ -9825,7 +9826,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="77" t="s">
         <v>37</v>
       </c>
@@ -9851,7 +9852,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="78" t="s">
         <v>43</v>
       </c>
@@ -9877,7 +9878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="54" t="s">
         <v>31</v>
       </c>
@@ -9905,7 +9906,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="55" t="s">
         <v>41</v>
       </c>
@@ -9934,7 +9935,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="77" t="s">
         <v>37</v>
       </c>
@@ -9963,7 +9964,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="78" t="s">
         <v>43</v>
       </c>
@@ -9992,7 +9993,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="53" t="s">
         <v>31</v>
       </c>
@@ -10023,7 +10024,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="54" t="s">
         <v>41</v>
       </c>
@@ -10053,7 +10054,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="77" t="s">
         <v>37</v>
       </c>
@@ -10079,7 +10080,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="78" t="s">
         <v>43</v>
       </c>
@@ -10105,7 +10106,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="54" t="s">
         <v>31</v>
       </c>
@@ -10132,7 +10133,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="55" t="s">
         <v>41</v>
       </c>
@@ -10161,7 +10162,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="78" t="s">
         <v>43</v>
       </c>
@@ -10187,7 +10188,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="53" t="s">
         <v>31</v>
       </c>
@@ -10216,7 +10217,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="54" t="s">
         <v>41</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="78" t="s">
         <v>43</v>
       </c>
@@ -10269,7 +10270,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="54" t="s">
         <v>31</v>
       </c>
@@ -10296,7 +10297,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="55" t="s">
         <v>41</v>
       </c>
@@ -10325,7 +10326,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="78" t="s">
         <v>43</v>
       </c>
@@ -10354,7 +10355,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="53" t="s">
         <v>31</v>
       </c>
@@ -10385,7 +10386,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="54" t="s">
         <v>41</v>
       </c>
@@ -10415,7 +10416,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="54" t="s">
         <v>31</v>
       </c>
@@ -10442,7 +10443,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="55" t="s">
         <v>41</v>
       </c>
@@ -10471,7 +10472,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="77" t="s">
         <v>37</v>
       </c>
@@ -10500,7 +10501,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="78" t="s">
         <v>43</v>
       </c>
@@ -10529,7 +10530,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="92" t="s">
         <v>46</v>
       </c>
@@ -10558,7 +10559,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="53" t="s">
         <v>31</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="55" t="s">
         <v>41</v>
       </c>
@@ -10616,7 +10617,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="77" t="s">
         <v>37</v>
       </c>
@@ -10645,7 +10646,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="78" t="s">
         <v>43</v>
       </c>
@@ -10674,7 +10675,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="92" t="s">
         <v>46</v>
       </c>
@@ -10703,7 +10704,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="53" t="s">
         <v>31</v>
       </c>
@@ -10732,7 +10733,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="54" t="s">
         <v>41</v>
       </c>
@@ -10760,7 +10761,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="77" t="s">
         <v>37</v>
       </c>
@@ -10789,7 +10790,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="78" t="s">
         <v>43</v>
       </c>
@@ -10818,7 +10819,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="92" t="s">
         <v>46</v>
       </c>
@@ -10847,7 +10848,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="54" t="s">
         <v>31</v>
       </c>
@@ -10875,7 +10876,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="55" t="s">
         <v>41</v>
       </c>
@@ -10904,7 +10905,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="92" t="s">
         <v>46</v>
       </c>
@@ -10930,7 +10931,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="53" t="s">
         <v>31</v>
       </c>
@@ -10959,7 +10960,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="77" t="s">
         <v>37</v>
       </c>
@@ -10988,7 +10989,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="92" t="s">
         <v>46</v>
       </c>
@@ -11017,7 +11018,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="54" t="s">
         <v>31</v>
       </c>
@@ -11042,7 +11043,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="54" t="s">
         <v>41</v>
       </c>
@@ -11070,7 +11071,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="77" t="s">
         <v>37</v>
       </c>
@@ -11099,7 +11100,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="92" t="s">
         <v>46</v>
       </c>
@@ -11128,7 +11129,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="53" t="s">
         <v>31</v>
       </c>
@@ -11157,7 +11158,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="55" t="s">
         <v>41</v>
       </c>
@@ -11186,7 +11187,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="92" t="s">
         <v>46</v>
       </c>
@@ -11215,7 +11216,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="53" t="s">
         <v>31</v>
       </c>
@@ -11243,7 +11244,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="77" t="s">
         <v>37</v>
       </c>
@@ -11274,7 +11275,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="78" t="s">
         <v>43</v>
       </c>
@@ -11305,7 +11306,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="92" t="s">
         <v>46</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="54" t="s">
         <v>41</v>
       </c>
@@ -11367,7 +11368,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="77" t="s">
         <v>37</v>
       </c>
@@ -11393,7 +11394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="78" t="s">
         <v>43</v>
       </c>
@@ -11419,7 +11420,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" s="92" t="s">
         <v>46</v>
       </c>
@@ -11445,7 +11446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>296</v>
       </c>
@@ -11466,7 +11467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>296</v>
       </c>
@@ -11492,7 +11493,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="53" t="s">
         <v>31</v>
       </c>
@@ -11518,7 +11519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>294</v>
       </c>
@@ -11539,7 +11540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="54" t="s">
         <v>41</v>
       </c>
@@ -11565,7 +11566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>295</v>
       </c>
@@ -11586,7 +11587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="77" t="s">
         <v>37</v>
       </c>
@@ -11612,7 +11613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="78" t="s">
         <v>43</v>
       </c>
@@ -11638,7 +11639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="92" t="s">
         <v>46</v>
       </c>
@@ -11664,7 +11665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>296</v>
       </c>
@@ -11690,7 +11691,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="53" t="s">
         <v>31</v>
       </c>
@@ -11716,7 +11717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="54" t="s">
         <v>41</v>
       </c>
@@ -11742,7 +11743,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="77" t="s">
         <v>37</v>
       </c>
@@ -11768,7 +11769,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="78" t="s">
         <v>43</v>
       </c>
@@ -11794,7 +11795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="92" t="s">
         <v>46</v>
       </c>
@@ -11820,7 +11821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="53" t="s">
         <v>31</v>
       </c>
@@ -11846,7 +11847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="54" t="s">
         <v>41</v>
       </c>
@@ -11872,15 +11873,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="77" t="s">
         <v>37</v>
       </c>
       <c r="B331" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C331" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D331" s="16">
         <v>3</v>
@@ -11901,15 +11902,15 @@
         <v>293</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="78" t="s">
         <v>43</v>
       </c>
       <c r="B332" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C332" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D332" s="16">
         <v>3</v>
@@ -11930,15 +11931,15 @@
         <v>293</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="92" t="s">
         <v>46</v>
       </c>
       <c r="B333" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C333" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D333" s="16">
         <v>3</v>
@@ -11959,15 +11960,15 @@
         <v>293</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B334" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C334" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D334" s="16">
         <v>3</v>
@@ -11988,15 +11989,15 @@
         <v>293</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="54" t="s">
         <v>41</v>
       </c>
       <c r="B335" s="55" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C335" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D335" s="16">
         <v>3</v>
@@ -12017,12 +12018,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="77" t="s">
         <v>37</v>
       </c>
       <c r="B336" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C336" t="s">
         <v>292</v>
@@ -12046,12 +12047,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="78" t="s">
         <v>43</v>
       </c>
       <c r="B337" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C337" t="s">
         <v>292</v>
@@ -12075,12 +12076,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="92" t="s">
         <v>46</v>
       </c>
       <c r="B338" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C338" t="s">
         <v>292</v>
@@ -12104,12 +12105,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="54" t="s">
         <v>31</v>
       </c>
       <c r="B339" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C339" t="s">
         <v>292</v>
@@ -12133,12 +12134,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="54" t="s">
         <v>41</v>
       </c>
       <c r="B340" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C340" t="s">
         <v>292</v>
@@ -12183,20 +12184,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="104.6640625" style="84" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="19"/>
+    <col min="1" max="1" width="28.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="104.7109375" style="84" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="19" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -12225,7 +12226,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="85">
         <v>46055</v>
       </c>
@@ -12242,7 +12243,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="84" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2" s="19" t="s">
         <v>8</v>
@@ -12251,7 +12252,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="19" t="s">
         <v>12</v>
       </c>
@@ -12268,7 +12269,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E4" s="19" t="s">
         <v>10</v>
       </c>
@@ -12282,7 +12283,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
         <v>463</v>
       </c>
@@ -12290,7 +12291,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="84" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="H5" s="19" t="s">
         <v>8</v>
@@ -12299,7 +12300,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
@@ -12316,7 +12317,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
         <v>12</v>
       </c>
@@ -12339,7 +12340,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>46055</v>
       </c>
@@ -12356,7 +12357,7 @@
         <v>11</v>
       </c>
       <c r="G8" s="84" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>8</v>
@@ -12365,7 +12366,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="85">
         <v>46055</v>
       </c>
@@ -12382,7 +12383,7 @@
         <v>11</v>
       </c>
       <c r="G9" s="84" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>8</v>
@@ -12391,7 +12392,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>46055</v>
       </c>
@@ -12408,7 +12409,7 @@
         <v>11</v>
       </c>
       <c r="G10" s="84" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H10" s="19" t="s">
         <v>8</v>
@@ -12417,7 +12418,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="210" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
         <v>12</v>
       </c>
@@ -12434,7 +12435,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="210" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
         <v>12</v>
       </c>
@@ -12451,7 +12452,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="180" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
         <v>12</v>
       </c>
@@ -12468,7 +12469,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>16</v>
       </c>
@@ -12485,7 +12486,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
         <v>16</v>
       </c>
@@ -12502,7 +12503,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
         <v>12</v>
       </c>
@@ -12519,7 +12520,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
         <v>16</v>
       </c>
@@ -12536,7 +12537,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="F18" s="19" t="s">
         <v>288</v>
       </c>
@@ -12550,7 +12551,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="E19" s="19" t="s">
         <v>10</v>
       </c>
@@ -12575,15 +12576,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1B670F-7286-4413-AA18-FAB437017A91}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -12597,7 +12598,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>41</v>
       </c>
@@ -12611,7 +12612,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
         <v>41</v>
       </c>
@@ -12625,7 +12626,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
         <v>41</v>
       </c>
@@ -12639,7 +12640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>31</v>
       </c>
@@ -12653,7 +12654,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
@@ -12667,7 +12668,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>31</v>
       </c>
@@ -12681,7 +12682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
         <v>37</v>
       </c>
@@ -12695,7 +12696,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
         <v>37</v>
       </c>
@@ -12710,7 +12711,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>37</v>
       </c>
@@ -12724,7 +12725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
         <v>43</v>
       </c>
@@ -12738,7 +12739,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
         <v>43</v>
       </c>
@@ -12753,7 +12754,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
         <v>43</v>
       </c>
@@ -12767,7 +12768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>46</v>
       </c>
@@ -12781,7 +12782,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>46</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>88.25</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>46</v>
       </c>
@@ -12810,7 +12811,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>294</v>
       </c>
@@ -12824,7 +12825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>296</v>
       </c>
@@ -12854,20 +12855,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C198"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>330</v>
       </c>
@@ -12878,7 +12879,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>398</v>
       </c>
@@ -12889,7 +12890,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>398</v>
       </c>
@@ -12900,7 +12901,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>398</v>
       </c>
@@ -12911,7 +12912,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>398</v>
       </c>
@@ -12922,7 +12923,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>398</v>
       </c>
@@ -12933,7 +12934,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>398</v>
       </c>
@@ -12944,7 +12945,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>398</v>
       </c>
@@ -12955,7 +12956,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>398</v>
       </c>
@@ -12966,7 +12967,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>398</v>
       </c>
@@ -12977,7 +12978,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>398</v>
       </c>
@@ -12988,7 +12989,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>398</v>
       </c>
@@ -12999,7 +13000,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>398</v>
       </c>
@@ -13010,7 +13011,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>398</v>
       </c>
@@ -13021,7 +13022,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>398</v>
       </c>
@@ -13032,7 +13033,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>398</v>
       </c>
@@ -13043,7 +13044,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>398</v>
       </c>
@@ -13054,7 +13055,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>398</v>
       </c>
@@ -13065,7 +13066,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>398</v>
       </c>
@@ -13076,7 +13077,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>398</v>
       </c>
@@ -13087,7 +13088,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>398</v>
       </c>
@@ -13098,7 +13099,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>398</v>
       </c>
@@ -13109,7 +13110,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>398</v>
       </c>
@@ -13120,7 +13121,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>398</v>
       </c>
@@ -13131,7 +13132,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>398</v>
       </c>
@@ -13142,7 +13143,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>398</v>
       </c>
@@ -13153,7 +13154,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>398</v>
       </c>
@@ -13164,7 +13165,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>398</v>
       </c>
@@ -13175,7 +13176,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>398</v>
       </c>
@@ -13186,7 +13187,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>398</v>
       </c>
@@ -13197,7 +13198,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>398</v>
       </c>
@@ -13208,7 +13209,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>398</v>
       </c>
@@ -13219,7 +13220,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>398</v>
       </c>
@@ -13230,7 +13231,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>398</v>
       </c>
@@ -13241,7 +13242,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>398</v>
       </c>
@@ -13252,7 +13253,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>398</v>
       </c>
@@ -13263,7 +13264,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>398</v>
       </c>
@@ -13274,7 +13275,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>398</v>
       </c>
@@ -13285,7 +13286,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>398</v>
       </c>
@@ -13296,7 +13297,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>398</v>
       </c>
@@ -13307,7 +13308,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>412</v>
       </c>
@@ -13318,7 +13319,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>412</v>
       </c>
@@ -13329,7 +13330,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>412</v>
       </c>
@@ -13340,7 +13341,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>412</v>
       </c>
@@ -13351,7 +13352,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>412</v>
       </c>
@@ -13362,7 +13363,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>412</v>
       </c>
@@ -13373,7 +13374,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>412</v>
       </c>
@@ -13384,7 +13385,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>412</v>
       </c>
@@ -13395,7 +13396,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>412</v>
       </c>
@@ -13406,7 +13407,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>412</v>
       </c>
@@ -13417,7 +13418,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>412</v>
       </c>
@@ -13428,7 +13429,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>412</v>
       </c>
@@ -13439,7 +13440,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>412</v>
       </c>
@@ -13450,7 +13451,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>412</v>
       </c>
@@ -13461,7 +13462,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>412</v>
       </c>
@@ -13472,7 +13473,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>412</v>
       </c>
@@ -13483,7 +13484,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>412</v>
       </c>
@@ -13494,7 +13495,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>412</v>
       </c>
@@ -13505,7 +13506,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>412</v>
       </c>
@@ -13516,7 +13517,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>412</v>
       </c>
@@ -13527,7 +13528,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>412</v>
       </c>
@@ -13538,7 +13539,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>412</v>
       </c>
@@ -13549,7 +13550,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>412</v>
       </c>
@@ -13560,7 +13561,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>412</v>
       </c>
@@ -13571,7 +13572,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>412</v>
       </c>
@@ -13582,7 +13583,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>412</v>
       </c>
@@ -13593,7 +13594,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>412</v>
       </c>
@@ -13604,7 +13605,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>412</v>
       </c>
@@ -13615,7 +13616,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>412</v>
       </c>
@@ -13626,7 +13627,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>412</v>
       </c>
@@ -13637,7 +13638,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>412</v>
       </c>
@@ -13648,7 +13649,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>412</v>
       </c>
@@ -13659,7 +13660,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>412</v>
       </c>
@@ -13670,7 +13671,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>412</v>
       </c>
@@ -13681,7 +13682,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>412</v>
       </c>
@@ -13692,7 +13693,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>412</v>
       </c>
@@ -13703,7 +13704,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>412</v>
       </c>
@@ -13714,7 +13715,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>412</v>
       </c>
@@ -13725,7 +13726,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>412</v>
       </c>
@@ -13736,7 +13737,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>412</v>
       </c>
@@ -13747,7 +13748,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>412</v>
       </c>
@@ -13758,7 +13759,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>419</v>
       </c>
@@ -13769,7 +13770,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>419</v>
       </c>
@@ -13780,7 +13781,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>419</v>
       </c>
@@ -13791,7 +13792,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>419</v>
       </c>
@@ -13802,7 +13803,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>419</v>
       </c>
@@ -13813,7 +13814,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>419</v>
       </c>
@@ -13824,7 +13825,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>419</v>
       </c>
@@ -13835,7 +13836,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>419</v>
       </c>
@@ -13846,7 +13847,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>419</v>
       </c>
@@ -13857,7 +13858,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>419</v>
       </c>
@@ -13868,7 +13869,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>419</v>
       </c>
@@ -13879,7 +13880,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>419</v>
       </c>
@@ -13890,7 +13891,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>419</v>
       </c>
@@ -13901,7 +13902,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>419</v>
       </c>
@@ -13912,7 +13913,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>419</v>
       </c>
@@ -13923,7 +13924,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>419</v>
       </c>
@@ -13934,7 +13935,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>419</v>
       </c>
@@ -13945,7 +13946,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>419</v>
       </c>
@@ -13956,7 +13957,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>419</v>
       </c>
@@ -13967,7 +13968,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>419</v>
       </c>
@@ -13978,7 +13979,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>419</v>
       </c>
@@ -13989,7 +13990,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>419</v>
       </c>
@@ -14000,7 +14001,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>419</v>
       </c>
@@ -14011,7 +14012,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>419</v>
       </c>
@@ -14022,7 +14023,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>419</v>
       </c>
@@ -14033,7 +14034,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>419</v>
       </c>
@@ -14044,7 +14045,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>419</v>
       </c>
@@ -14055,7 +14056,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>419</v>
       </c>
@@ -14066,7 +14067,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>419</v>
       </c>
@@ -14077,7 +14078,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>419</v>
       </c>
@@ -14088,7 +14089,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>419</v>
       </c>
@@ -14099,7 +14100,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>419</v>
       </c>
@@ -14110,7 +14111,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>419</v>
       </c>
@@ -14121,7 +14122,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>419</v>
       </c>
@@ -14132,7 +14133,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>419</v>
       </c>
@@ -14143,7 +14144,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>419</v>
       </c>
@@ -14154,7 +14155,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>419</v>
       </c>
@@ -14165,7 +14166,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>419</v>
       </c>
@@ -14176,7 +14177,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>419</v>
       </c>
@@ -14187,7 +14188,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>332</v>
       </c>
@@ -14198,7 +14199,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>332</v>
       </c>
@@ -14209,7 +14210,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>332</v>
       </c>
@@ -14220,7 +14221,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>332</v>
       </c>
@@ -14231,7 +14232,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>332</v>
       </c>
@@ -14242,7 +14243,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>332</v>
       </c>
@@ -14253,7 +14254,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>332</v>
       </c>
@@ -14264,7 +14265,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>332</v>
       </c>
@@ -14275,7 +14276,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>332</v>
       </c>
@@ -14286,7 +14287,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>332</v>
       </c>
@@ -14297,7 +14298,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>332</v>
       </c>
@@ -14308,7 +14309,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>332</v>
       </c>
@@ -14319,7 +14320,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>332</v>
       </c>
@@ -14330,7 +14331,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>332</v>
       </c>
@@ -14341,7 +14342,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>332</v>
       </c>
@@ -14352,7 +14353,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>332</v>
       </c>
@@ -14363,7 +14364,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>332</v>
       </c>
@@ -14374,7 +14375,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>332</v>
       </c>
@@ -14385,7 +14386,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>332</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>332</v>
       </c>
@@ -14407,7 +14408,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>332</v>
       </c>
@@ -14418,7 +14419,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>332</v>
       </c>
@@ -14429,7 +14430,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>332</v>
       </c>
@@ -14440,7 +14441,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>332</v>
       </c>
@@ -14451,7 +14452,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>332</v>
       </c>
@@ -14462,7 +14463,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>332</v>
       </c>
@@ -14473,7 +14474,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>332</v>
       </c>
@@ -14484,7 +14485,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>332</v>
       </c>
@@ -14495,7 +14496,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>332</v>
       </c>
@@ -14506,7 +14507,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>332</v>
       </c>
@@ -14517,7 +14518,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>332</v>
       </c>
@@ -14528,7 +14529,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>332</v>
       </c>
@@ -14539,7 +14540,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>332</v>
       </c>
@@ -14550,7 +14551,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>332</v>
       </c>
@@ -14561,7 +14562,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>332</v>
       </c>
@@ -14572,7 +14573,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>332</v>
       </c>
@@ -14583,7 +14584,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>332</v>
       </c>
@@ -14594,7 +14595,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>332</v>
       </c>
@@ -14605,7 +14606,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>332</v>
       </c>
@@ -14616,7 +14617,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>379</v>
       </c>
@@ -14627,7 +14628,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>379</v>
       </c>
@@ -14638,7 +14639,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>379</v>
       </c>
@@ -14649,7 +14650,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>379</v>
       </c>
@@ -14660,7 +14661,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>379</v>
       </c>
@@ -14671,7 +14672,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>379</v>
       </c>
@@ -14682,7 +14683,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>379</v>
       </c>
@@ -14693,7 +14694,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>379</v>
       </c>
@@ -14704,7 +14705,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>379</v>
       </c>
@@ -14715,7 +14716,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>379</v>
       </c>
@@ -14726,7 +14727,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>379</v>
       </c>
@@ -14737,7 +14738,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>379</v>
       </c>
@@ -14748,7 +14749,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>379</v>
       </c>
@@ -14759,7 +14760,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>379</v>
       </c>
@@ -14770,7 +14771,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>379</v>
       </c>
@@ -14781,7 +14782,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>379</v>
       </c>
@@ -14792,7 +14793,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>379</v>
       </c>
@@ -14803,7 +14804,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>379</v>
       </c>
@@ -14814,7 +14815,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>379</v>
       </c>
@@ -14825,7 +14826,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>379</v>
       </c>
@@ -14836,7 +14837,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>379</v>
       </c>
@@ -14847,7 +14848,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>379</v>
       </c>
@@ -14858,7 +14859,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>379</v>
       </c>
@@ -14869,7 +14870,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>379</v>
       </c>
@@ -14880,7 +14881,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>379</v>
       </c>
@@ -14891,7 +14892,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>379</v>
       </c>
@@ -14902,7 +14903,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>379</v>
       </c>
@@ -14913,7 +14914,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>379</v>
       </c>
@@ -14924,7 +14925,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>379</v>
       </c>
@@ -14935,7 +14936,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>379</v>
       </c>
@@ -14946,7 +14947,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>379</v>
       </c>
@@ -14957,7 +14958,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>379</v>
       </c>
@@ -14968,7 +14969,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>379</v>
       </c>
@@ -14979,7 +14980,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>379</v>
       </c>
@@ -14990,7 +14991,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>379</v>
       </c>
@@ -15001,7 +15002,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>379</v>
       </c>
@@ -15012,7 +15013,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>379</v>
       </c>
@@ -15023,7 +15024,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>379</v>
       </c>
@@ -15034,7 +15035,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>379</v>
       </c>

--- a/CORE_TE.xlsx
+++ b/CORE_TE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0 COOP Local\CO-OP planner v03 ChatGPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97F86B2-48E5-4D3E-A37E-1E675511A931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885811BA-8A62-4F5B-BAED-A73E63010A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30600" yWindow="1545" windowWidth="28800" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,6 @@
     <sheet name="Programs" sheetId="4" r:id="rId3"/>
     <sheet name="Sequences" sheetId="3" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Coursses!$A$1:$K$340</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">restrictions!$A$1:$I$22</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3275" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="481">
   <si>
     <t>PROGRAM</t>
   </si>
@@ -1513,19 +1509,13 @@
     <t>ENGR 7962</t>
   </si>
   <si>
-    <t>MIAE 312 is reserved for Co-op students in Summer.</t>
-  </si>
-  <si>
     <t>ECP/MEP: Laboratory PHYS 224 is not required.</t>
   </si>
   <si>
     <t>ECP/MEP: Laboratory PHYS 225 is not required.</t>
   </si>
   <si>
-    <t>Summer offering reserved for Co-op students.</t>
-  </si>
-  <si>
-    <t>MAIE 312</t>
+    <t>MIAE 312 reserved for AERO students in summer</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2081,15 +2071,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2447,9 +2432,10 @@
       <c r="D3" s="35">
         <v>4</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" t="s">
         <v>110</v>
       </c>
+      <c r="F3" s="18"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11" t="s">
@@ -2477,9 +2463,10 @@
       <c r="D4" s="35">
         <v>4</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" t="s">
         <v>110</v>
       </c>
+      <c r="F4" s="18"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
@@ -2507,9 +2494,10 @@
       <c r="D5" s="35">
         <v>4</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" t="s">
         <v>110</v>
       </c>
+      <c r="F5" s="18"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
@@ -6206,16 +6194,16 @@
     </row>
     <row r="124" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="18" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>476</v>
+        <v>152</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>314</v>
+        <v>153</v>
       </c>
       <c r="D124" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E124" s="18"/>
       <c r="F124" s="18"/>
@@ -6230,22 +6218,22 @@
         <v>14</v>
       </c>
       <c r="K124" s="9" t="s">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="U124" s="28"/>
     </row>
     <row r="125" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>477</v>
+        <v>152</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>316</v>
+        <v>153</v>
       </c>
       <c r="D125" s="8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E125" s="18"/>
       <c r="F125" s="18"/>
@@ -6266,7 +6254,7 @@
     </row>
     <row r="126" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="18" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>152</v>
@@ -6297,10 +6285,10 @@
     </row>
     <row r="127" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C127" s="18" t="s">
         <v>153</v>
@@ -6328,10 +6316,10 @@
     </row>
     <row r="128" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C128" s="18" t="s">
         <v>153</v>
@@ -6359,7 +6347,7 @@
     </row>
     <row r="129" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>157</v>
@@ -6390,10 +6378,10 @@
     </row>
     <row r="130" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C130" s="18" t="s">
         <v>153</v>
@@ -6421,10 +6409,10 @@
     </row>
     <row r="131" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C131" s="18" t="s">
         <v>153</v>
@@ -6452,7 +6440,7 @@
     </row>
     <row r="132" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>158</v>
@@ -6482,16 +6470,16 @@
     </row>
     <row r="133" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D133" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E133" s="18"/>
       <c r="F133" s="18"/>
@@ -6512,16 +6500,16 @@
     </row>
     <row r="134" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D134" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E134" s="18"/>
       <c r="F134" s="18"/>
@@ -6542,7 +6530,7 @@
     </row>
     <row r="135" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>159</v>
@@ -6572,10 +6560,10 @@
     </row>
     <row r="136" spans="1:21" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C136" s="18" t="s">
         <v>160</v>
@@ -6602,10 +6590,10 @@
     </row>
     <row r="137" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C137" s="18" t="s">
         <v>160</v>
@@ -6632,7 +6620,7 @@
     </row>
     <row r="138" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>161</v>
@@ -6662,10 +6650,10 @@
     </row>
     <row r="139" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C139" s="18" t="s">
         <v>160</v>
@@ -6692,10 +6680,10 @@
     </row>
     <row r="140" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C140" s="18" t="s">
         <v>160</v>
@@ -6722,7 +6710,7 @@
     </row>
     <row r="141" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>162</v>
@@ -6752,10 +6740,10 @@
     </row>
     <row r="142" spans="1:21" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C142" t="s">
         <v>160</v>
@@ -6783,10 +6771,10 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A143" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B143" s="55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C143" t="s">
         <v>160</v>
@@ -6809,7 +6797,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B144" s="55" t="s">
         <v>163</v>
@@ -6835,10 +6823,10 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B145" s="55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C145" t="s">
         <v>160</v>
@@ -6861,10 +6849,10 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B146" s="55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C146" t="s">
         <v>160</v>
@@ -6887,7 +6875,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B147" s="55" t="s">
         <v>164</v>
@@ -6913,10 +6901,10 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B148" s="55" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C148" t="s">
         <v>160</v>
@@ -6939,10 +6927,10 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C149" t="s">
         <v>160</v>
@@ -6965,7 +6953,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B150" s="55" t="s">
         <v>165</v>
@@ -6991,10 +6979,10 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B151" s="55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C151" t="s">
         <v>160</v>
@@ -7017,10 +7005,10 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B152" s="55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C152" t="s">
         <v>160</v>
@@ -7043,7 +7031,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B153" s="55" t="s">
         <v>166</v>
@@ -7069,10 +7057,10 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B154" s="55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C154" t="s">
         <v>160</v>
@@ -7095,10 +7083,10 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B155" s="55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C155" t="s">
         <v>160</v>
@@ -7121,7 +7109,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B156" s="55" t="s">
         <v>167</v>
@@ -7147,10 +7135,10 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B157" s="55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C157" t="s">
         <v>160</v>
@@ -7173,10 +7161,10 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B158" s="55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C158" t="s">
         <v>160</v>
@@ -7199,7 +7187,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B159" s="55" t="s">
         <v>168</v>
@@ -7225,10 +7213,10 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B160" s="55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C160" t="s">
         <v>160</v>
@@ -7251,10 +7239,10 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B161" s="55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C161" t="s">
         <v>160</v>
@@ -7277,7 +7265,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B162" s="55" t="s">
         <v>169</v>
@@ -7303,10 +7291,10 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B163" s="55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C163" t="s">
         <v>160</v>
@@ -7329,10 +7317,10 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B164" s="55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C164" t="s">
         <v>160</v>
@@ -7355,7 +7343,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B165" s="55" t="s">
         <v>170</v>
@@ -7384,13 +7372,13 @@
         <v>146</v>
       </c>
       <c r="B166" s="55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C166" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D166" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G166" s="20" t="s">
         <v>14</v>
@@ -7410,13 +7398,13 @@
         <v>155</v>
       </c>
       <c r="B167" s="55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D167" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G167" s="20" t="s">
         <v>14</v>
@@ -7433,7 +7421,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="18" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B168" s="55" t="s">
         <v>171</v>
@@ -7459,10 +7447,10 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B169" s="55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C169" t="s">
         <v>172</v>
@@ -7485,10 +7473,10 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B170" s="55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C170" t="s">
         <v>172</v>
@@ -7511,7 +7499,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B171" s="55" t="s">
         <v>173</v>
@@ -7537,10 +7525,10 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B172" s="55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C172" t="s">
         <v>172</v>
@@ -7563,10 +7551,10 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B173" s="55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C173" t="s">
         <v>172</v>
@@ -7589,7 +7577,7 @@
     </row>
     <row r="174" spans="1:11" s="66" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A174" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B174" s="55" t="s">
         <v>174</v>
@@ -7621,13 +7609,13 @@
         <v>146</v>
       </c>
       <c r="B175" s="55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C175" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D175" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G175" s="20" t="s">
         <v>14</v>
@@ -7647,13 +7635,13 @@
         <v>155</v>
       </c>
       <c r="B176" s="55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C176" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D176" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G176" s="20" t="s">
         <v>14</v>
@@ -7670,7 +7658,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="18" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B177" s="55" t="s">
         <v>175</v>
@@ -7696,10 +7684,10 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B178" s="55" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C178" t="s">
         <v>176</v>
@@ -7722,10 +7710,10 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B179" s="55" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C179" t="s">
         <v>176</v>
@@ -7748,7 +7736,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B180" s="55" t="s">
         <v>177</v>
@@ -7774,10 +7762,10 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B181" s="55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C181" t="s">
         <v>176</v>
@@ -7800,10 +7788,10 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B182" s="55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C182" t="s">
         <v>176</v>
@@ -7826,7 +7814,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B183" s="55" t="s">
         <v>178</v>
@@ -7855,13 +7843,13 @@
         <v>146</v>
       </c>
       <c r="B184" s="55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C184" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D184" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G184" s="20" t="s">
         <v>14</v>
@@ -7881,13 +7869,13 @@
         <v>155</v>
       </c>
       <c r="B185" s="55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C185" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D185" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G185" s="20" t="s">
         <v>14</v>
@@ -7904,7 +7892,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="18" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B186" s="55" t="s">
         <v>179</v>
@@ -7930,10 +7918,10 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B187" s="55" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C187" t="s">
         <v>180</v>
@@ -7956,10 +7944,10 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B188" s="55" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C188" t="s">
         <v>180</v>
@@ -7982,7 +7970,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B189" s="55" t="s">
         <v>181</v>
@@ -8008,10 +7996,10 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B190" s="55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C190" t="s">
         <v>180</v>
@@ -8034,10 +8022,10 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B191" s="55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C191" t="s">
         <v>180</v>
@@ -8060,7 +8048,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B192" s="55" t="s">
         <v>182</v>
@@ -8089,13 +8077,13 @@
         <v>146</v>
       </c>
       <c r="B193" s="55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C193" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D193" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G193" s="20" t="s">
         <v>14</v>
@@ -8115,13 +8103,13 @@
         <v>155</v>
       </c>
       <c r="B194" s="55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C194" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D194" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G194" s="20" t="s">
         <v>14</v>
@@ -8138,7 +8126,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="18" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B195" s="55" t="s">
         <v>183</v>
@@ -8164,10 +8152,10 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B196" s="55" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C196" t="s">
         <v>184</v>
@@ -8190,10 +8178,10 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B197" s="55" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C197" t="s">
         <v>184</v>
@@ -8216,7 +8204,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B198" s="55" t="s">
         <v>185</v>
@@ -8242,10 +8230,10 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="18" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B199" s="55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C199" t="s">
         <v>184</v>
@@ -8268,10 +8256,10 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B200" s="55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C200" t="s">
         <v>184</v>
@@ -8294,7 +8282,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B201" s="55" t="s">
         <v>186</v>
@@ -8319,94 +8307,93 @@
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A202" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B202" s="55" t="s">
-        <v>186</v>
+      <c r="A202" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B202" t="s">
+        <v>187</v>
       </c>
       <c r="C202" t="s">
-        <v>184</v>
-      </c>
-      <c r="D202" s="8">
-        <v>8</v>
-      </c>
-      <c r="G202" s="20" t="s">
-        <v>14</v>
+        <v>188</v>
+      </c>
+      <c r="D202" s="35">
+        <v>3</v>
       </c>
       <c r="I202" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J202" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K202" s="9" t="s">
-        <v>154</v>
+      <c r="K202" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A203" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B203" s="55" t="s">
-        <v>186</v>
+      <c r="A203" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B203" t="s">
+        <v>189</v>
       </c>
       <c r="C203" t="s">
-        <v>184</v>
-      </c>
-      <c r="D203" s="8">
-        <v>8</v>
-      </c>
-      <c r="G203" s="20" t="s">
-        <v>14</v>
+        <v>190</v>
+      </c>
+      <c r="D203" s="35">
+        <v>3.5</v>
+      </c>
+      <c r="E203" t="s">
+        <v>138</v>
       </c>
       <c r="I203" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J203" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K203" s="9" t="s">
-        <v>154</v>
+      <c r="K203" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B204" t="s">
-        <v>187</v>
-      </c>
-      <c r="C204" t="s">
-        <v>188</v>
-      </c>
-      <c r="D204" s="35">
-        <v>3</v>
-      </c>
-      <c r="I204" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K204" s="11" t="s">
+      <c r="B204" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C204" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="D204" s="14">
+        <v>3</v>
+      </c>
+      <c r="E204" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="F204" s="57"/>
+      <c r="G204" s="60"/>
+      <c r="H204" s="60"/>
+      <c r="I204" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J204" s="60"/>
+      <c r="K204" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A205" s="13" t="s">
+      <c r="A205" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B205" t="s">
-        <v>189</v>
-      </c>
-      <c r="C205" t="s">
-        <v>190</v>
-      </c>
-      <c r="D205" s="35">
-        <v>3.5</v>
-      </c>
-      <c r="E205" t="s">
-        <v>138</v>
-      </c>
-      <c r="I205" s="20" t="s">
+      <c r="B205" s="54" t="s">
+        <v>194</v>
+      </c>
+      <c r="C205" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D205" s="10">
+        <v>3</v>
+      </c>
+      <c r="E205" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F205" s="19"/>
+      <c r="J205" s="20" t="s">
         <v>14</v>
       </c>
       <c r="K205" s="11" t="s">
@@ -8418,131 +8405,131 @@
         <v>11</v>
       </c>
       <c r="B206" s="53" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C206" s="57" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D206" s="14">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E206" s="57" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F206" s="57"/>
-      <c r="G206" s="60"/>
+      <c r="G206" s="60" t="s">
+        <v>14</v>
+      </c>
       <c r="H206" s="60"/>
-      <c r="I206" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J206" s="60"/>
+      <c r="I206" s="60"/>
+      <c r="J206" s="60" t="s">
+        <v>14</v>
+      </c>
       <c r="K206" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
+      <c r="A207" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B207" s="54" t="s">
-        <v>194</v>
-      </c>
-      <c r="C207" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D207" s="10">
-        <v>3</v>
-      </c>
-      <c r="E207" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="F207" s="19"/>
-      <c r="J207" s="20" t="s">
-        <v>14</v>
-      </c>
+      <c r="B207" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="C207" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="D207" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="E207" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="F207" s="57"/>
+      <c r="G207" s="60"/>
+      <c r="H207" s="60"/>
+      <c r="I207" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J207" s="60"/>
       <c r="K207" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A208" s="13" t="s">
+      <c r="A208" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B208" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="C208" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="D208" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="E208" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="F208" s="57"/>
-      <c r="G208" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H208" s="60"/>
-      <c r="I208" s="60"/>
-      <c r="J208" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K208" s="15" t="s">
+      <c r="B208" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="C208" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D208" s="10">
+        <v>3</v>
+      </c>
+      <c r="E208" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F208" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="I208" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K208" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A209" s="13" t="s">
+      <c r="A209" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B209" s="53" t="s">
+      <c r="B209" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="C209" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D209" s="10">
+        <v>3</v>
+      </c>
+      <c r="E209" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="C209" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="D209" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="E209" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="F209" s="57"/>
-      <c r="G209" s="60"/>
-      <c r="H209" s="60"/>
-      <c r="I209" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J209" s="60"/>
+      <c r="F209" s="19"/>
+      <c r="J209" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="K209" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A210" s="2" t="s">
+      <c r="A210" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B210" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C210" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="D210" s="10">
-        <v>3</v>
-      </c>
-      <c r="E210" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F210" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="I210" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K210" s="11" t="s">
+      <c r="B210" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C210" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="D210" s="14">
+        <v>3</v>
+      </c>
+      <c r="E210" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="F210" s="57"/>
+      <c r="G210" s="60"/>
+      <c r="H210" s="60"/>
+      <c r="I210" s="60"/>
+      <c r="J210" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K210" s="15" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8551,16 +8538,16 @@
         <v>11</v>
       </c>
       <c r="B211" s="54" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D211" s="10">
         <v>3</v>
       </c>
       <c r="E211" s="19" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="F211" s="19"/>
       <c r="J211" s="20" t="s">
@@ -8575,13 +8562,13 @@
         <v>11</v>
       </c>
       <c r="B212" s="53" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C212" s="57" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D212" s="14">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E212" s="57" t="s">
         <v>138</v>
@@ -8589,10 +8576,10 @@
       <c r="F212" s="57"/>
       <c r="G212" s="60"/>
       <c r="H212" s="60"/>
-      <c r="I212" s="60"/>
-      <c r="J212" s="60" t="s">
-        <v>14</v>
-      </c>
+      <c r="I212" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J212" s="60"/>
       <c r="K212" s="15" t="s">
         <v>19</v>
       </c>
@@ -8602,19 +8589,21 @@
         <v>11</v>
       </c>
       <c r="B213" s="54" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D213" s="10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E213" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="F213" s="19"/>
-      <c r="J213" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F213" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="I213" s="20" t="s">
         <v>14</v>
       </c>
       <c r="K213" s="11" t="s">
@@ -8625,26 +8614,23 @@
       <c r="A214" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B214" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="C214" s="57" t="s">
-        <v>209</v>
-      </c>
-      <c r="D214" s="14">
+      <c r="B214" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C214" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="D214" s="10">
         <v>3.5</v>
       </c>
-      <c r="E214" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="F214" s="57"/>
-      <c r="G214" s="60"/>
-      <c r="H214" s="60"/>
-      <c r="I214" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J214" s="60"/>
-      <c r="K214" s="15" t="s">
+      <c r="E214" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F214" s="19"/>
+      <c r="I214" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K214" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -8653,19 +8639,19 @@
         <v>11</v>
       </c>
       <c r="B215" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C215" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D215" s="10">
+        <v>3</v>
+      </c>
+      <c r="E215" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F215" s="19" t="s">
         <v>210</v>
-      </c>
-      <c r="C215" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="D215" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="E215" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="F215" s="19" t="s">
-        <v>189</v>
       </c>
       <c r="I215" s="20" t="s">
         <v>14</v>
@@ -8675,630 +8661,634 @@
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A216" s="13" t="s">
+      <c r="A216" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B216" s="54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C216" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="D216" s="10">
+      <c r="B216" s="88" t="s">
+        <v>217</v>
+      </c>
+      <c r="C216" s="89" t="s">
+        <v>215</v>
+      </c>
+      <c r="D216" s="71">
+        <v>3</v>
+      </c>
+      <c r="E216" s="89" t="s">
+        <v>214</v>
+      </c>
+      <c r="F216" s="89"/>
+      <c r="G216" s="91"/>
+      <c r="H216" s="91"/>
+      <c r="I216" s="91"/>
+      <c r="J216" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="K216" s="65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A217" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B217" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="C217" t="s">
+        <v>219</v>
+      </c>
+      <c r="D217" s="8">
+        <v>6</v>
+      </c>
+      <c r="I217" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K217" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A218" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B218" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C218" t="s">
+        <v>221</v>
+      </c>
+      <c r="D218" s="8">
+        <v>6</v>
+      </c>
+      <c r="J218" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K218" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A219" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="C219" s="107" t="s">
+        <v>222</v>
+      </c>
+      <c r="D219" s="51">
+        <v>3</v>
+      </c>
+      <c r="E219" s="107" t="s">
+        <v>473</v>
+      </c>
+      <c r="F219" s="107"/>
+      <c r="G219" s="122"/>
+      <c r="H219" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="I219" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="J219" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="K219" s="52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A220" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B220" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="C220" s="108" t="s">
+        <v>222</v>
+      </c>
+      <c r="D220" s="31">
+        <v>3</v>
+      </c>
+      <c r="E220" s="108" t="s">
+        <v>473</v>
+      </c>
+      <c r="F220" s="108"/>
+      <c r="G220" s="123"/>
+      <c r="H220" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="I220" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="J220" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="K220" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A221" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B221" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="C221" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="D221" s="41">
+        <v>3</v>
+      </c>
+      <c r="E221" s="58" t="s">
+        <v>473</v>
+      </c>
+      <c r="F221" s="58"/>
+      <c r="G221" s="61"/>
+      <c r="H221" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I221" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="J221" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="K221" s="42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A222" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C222" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="D222" s="14">
+        <v>3</v>
+      </c>
+      <c r="E222" s="57" t="s">
+        <v>473</v>
+      </c>
+      <c r="F222" s="57"/>
+      <c r="G222" s="60"/>
+      <c r="H222" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I222" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J222" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K222" s="60" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C223" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D223" s="10">
+        <v>3</v>
+      </c>
+      <c r="E223" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="F223" s="19"/>
+      <c r="H223" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I223" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J223" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K223" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A224" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="C224" s="105" t="s">
+        <v>224</v>
+      </c>
+      <c r="D224" s="45">
+        <v>3</v>
+      </c>
+      <c r="E224" s="105" t="s">
+        <v>473</v>
+      </c>
+      <c r="F224" s="105"/>
+      <c r="G224" s="121"/>
+      <c r="H224" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="I224" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="J224" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="K224" s="121" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B225" s="98" t="s">
+        <v>223</v>
+      </c>
+      <c r="C225" s="109" t="s">
+        <v>224</v>
+      </c>
+      <c r="D225" s="117">
+        <v>3</v>
+      </c>
+      <c r="E225" s="109" t="s">
+        <v>473</v>
+      </c>
+      <c r="F225" s="109"/>
+      <c r="G225" s="26"/>
+      <c r="H225" s="124" t="s">
+        <v>14</v>
+      </c>
+      <c r="I225" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J225" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="K225" s="124" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A226" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B226" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C226" s="110" t="s">
+        <v>224</v>
+      </c>
+      <c r="D226" s="59">
+        <v>3</v>
+      </c>
+      <c r="E226" s="110" t="s">
+        <v>473</v>
+      </c>
+      <c r="F226" s="110"/>
+      <c r="G226" s="36"/>
+      <c r="H226" s="125" t="s">
+        <v>14</v>
+      </c>
+      <c r="I226" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J226" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="K226" s="125" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B227" s="94" t="s">
+        <v>223</v>
+      </c>
+      <c r="C227" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="D227" s="17">
+        <v>3</v>
+      </c>
+      <c r="E227" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="F227" s="19"/>
+      <c r="G227" s="11"/>
+      <c r="H227" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I227" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J227" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K227" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C228" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D228" s="16">
+        <v>3</v>
+      </c>
+      <c r="E228" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="F228" s="21"/>
+      <c r="G228" s="9"/>
+      <c r="H228" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J228" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K228" s="22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A229" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="95" t="s">
+        <v>225</v>
+      </c>
+      <c r="C229" s="107" t="s">
+        <v>226</v>
+      </c>
+      <c r="D229" s="114">
+        <v>3</v>
+      </c>
+      <c r="E229" s="107" t="s">
+        <v>129</v>
+      </c>
+      <c r="F229" s="107"/>
+      <c r="G229" s="52"/>
+      <c r="H229" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="I229" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="J229" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="K229" s="122" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A230" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B230" s="100" t="s">
+        <v>225</v>
+      </c>
+      <c r="C230" s="108" t="s">
+        <v>226</v>
+      </c>
+      <c r="D230" s="116">
+        <v>3</v>
+      </c>
+      <c r="E230" s="108" t="s">
+        <v>129</v>
+      </c>
+      <c r="F230" s="108"/>
+      <c r="G230" s="32"/>
+      <c r="H230" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="I230" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="J230" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="K230" s="123" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B231" s="99" t="s">
+        <v>225</v>
+      </c>
+      <c r="C231" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="D231" s="118">
+        <v>3</v>
+      </c>
+      <c r="E231" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="F231" s="58"/>
+      <c r="G231" s="42"/>
+      <c r="H231" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I231" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="J231" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="K231" s="61" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A232" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B232" s="96" t="s">
+        <v>225</v>
+      </c>
+      <c r="C232" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="D232" s="113">
+        <v>3</v>
+      </c>
+      <c r="E232" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="F232" s="57"/>
+      <c r="G232" s="15"/>
+      <c r="H232" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I232" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J232" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K232" s="60" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B233" s="94" t="s">
+        <v>225</v>
+      </c>
+      <c r="C233" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="D233" s="17">
+        <v>3</v>
+      </c>
+      <c r="E233" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F233" s="19"/>
+      <c r="G233" s="11"/>
+      <c r="H233" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I233" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J233" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K233" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A234" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C234" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D234" s="16">
         <v>3.5</v>
       </c>
-      <c r="E216" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="F216" s="19"/>
-      <c r="I216" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K216" s="11" t="s">
+      <c r="E234" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F234" s="21"/>
+      <c r="G234" s="9"/>
+      <c r="H234" s="22"/>
+      <c r="I234" s="9"/>
+      <c r="J234" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K234" s="22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B217" s="54" t="s">
-        <v>214</v>
-      </c>
-      <c r="C217" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D217" s="10">
-        <v>3</v>
-      </c>
-      <c r="E217" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="F217" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="I217" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K217" s="11" t="s">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A235" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B235" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="C235" t="s">
+        <v>231</v>
+      </c>
+      <c r="D235" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="E235" t="s">
+        <v>232</v>
+      </c>
+      <c r="G235" s="11"/>
+      <c r="I235" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J235" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K235" s="20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A218" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B218" s="88" t="s">
-        <v>217</v>
-      </c>
-      <c r="C218" s="89" t="s">
-        <v>215</v>
-      </c>
-      <c r="D218" s="71">
-        <v>3</v>
-      </c>
-      <c r="E218" s="89" t="s">
-        <v>214</v>
-      </c>
-      <c r="F218" s="89"/>
-      <c r="G218" s="91"/>
-      <c r="H218" s="91"/>
-      <c r="I218" s="91"/>
-      <c r="J218" s="91" t="s">
-        <v>14</v>
-      </c>
-      <c r="K218" s="65" t="s">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A236" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B236" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="C236" t="s">
+        <v>231</v>
+      </c>
+      <c r="D236" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="E236" t="s">
+        <v>232</v>
+      </c>
+      <c r="G236" s="11"/>
+      <c r="I236" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J236" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K236" s="20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A219" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B219" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="C219" t="s">
-        <v>219</v>
-      </c>
-      <c r="D219" s="8">
-        <v>6</v>
-      </c>
-      <c r="I219" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K219" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A220" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B220" s="55" t="s">
-        <v>220</v>
-      </c>
-      <c r="C220" t="s">
-        <v>221</v>
-      </c>
-      <c r="D220" s="8">
-        <v>6</v>
-      </c>
-      <c r="J220" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K220" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A221" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B221" s="93" t="s">
-        <v>129</v>
-      </c>
-      <c r="C221" s="107" t="s">
-        <v>222</v>
-      </c>
-      <c r="D221" s="51">
-        <v>3</v>
-      </c>
-      <c r="E221" s="107" t="s">
-        <v>473</v>
-      </c>
-      <c r="F221" s="107"/>
-      <c r="G221" s="122"/>
-      <c r="H221" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="I221" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J221" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="K221" s="52" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A222" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B222" s="78" t="s">
-        <v>129</v>
-      </c>
-      <c r="C222" s="108" t="s">
-        <v>222</v>
-      </c>
-      <c r="D222" s="31">
-        <v>3</v>
-      </c>
-      <c r="E222" s="108" t="s">
-        <v>473</v>
-      </c>
-      <c r="F222" s="108"/>
-      <c r="G222" s="123"/>
-      <c r="H222" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="I222" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="J222" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="K222" s="123" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A223" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B223" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="C223" s="58" t="s">
-        <v>222</v>
-      </c>
-      <c r="D223" s="41">
-        <v>3</v>
-      </c>
-      <c r="E223" s="58" t="s">
-        <v>473</v>
-      </c>
-      <c r="F223" s="58"/>
-      <c r="G223" s="61"/>
-      <c r="H223" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="I223" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="J223" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="K223" s="61" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A224" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B224" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="C224" s="57" t="s">
-        <v>222</v>
-      </c>
-      <c r="D224" s="14">
-        <v>3</v>
-      </c>
-      <c r="E224" s="57" t="s">
-        <v>473</v>
-      </c>
-      <c r="F224" s="57"/>
-      <c r="G224" s="60"/>
-      <c r="H224" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I224" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J224" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K224" s="60" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A237" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B225" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="C225" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="D225" s="17">
-        <v>3</v>
-      </c>
-      <c r="E225" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="F225" s="19"/>
-      <c r="G225" s="11"/>
-      <c r="H225" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I225" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J225" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K225" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A226" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B226" s="127" t="s">
-        <v>223</v>
-      </c>
-      <c r="C226" s="105" t="s">
-        <v>224</v>
-      </c>
-      <c r="D226" s="115">
-        <v>3</v>
-      </c>
-      <c r="E226" s="105" t="s">
-        <v>473</v>
-      </c>
-      <c r="F226" s="105"/>
-      <c r="G226" s="46"/>
-      <c r="H226" s="121" t="s">
-        <v>14</v>
-      </c>
-      <c r="I226" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="J226" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="K226" s="121" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A227" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B227" s="98" t="s">
-        <v>223</v>
-      </c>
-      <c r="C227" s="109" t="s">
-        <v>224</v>
-      </c>
-      <c r="D227" s="117">
-        <v>3</v>
-      </c>
-      <c r="E227" s="109" t="s">
-        <v>473</v>
-      </c>
-      <c r="F227" s="109"/>
-      <c r="G227" s="26"/>
-      <c r="H227" s="124" t="s">
-        <v>14</v>
-      </c>
-      <c r="I227" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="J227" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="K227" s="124" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B228" s="102" t="s">
-        <v>223</v>
-      </c>
-      <c r="C228" s="110" t="s">
-        <v>224</v>
-      </c>
-      <c r="D228" s="59">
-        <v>3</v>
-      </c>
-      <c r="E228" s="110" t="s">
-        <v>473</v>
-      </c>
-      <c r="F228" s="110"/>
-      <c r="G228" s="36"/>
-      <c r="H228" s="125" t="s">
-        <v>14</v>
-      </c>
-      <c r="I228" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="J228" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="K228" s="125" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B229" s="94" t="s">
-        <v>223</v>
-      </c>
-      <c r="C229" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="D229" s="17">
-        <v>3</v>
-      </c>
-      <c r="E229" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="F229" s="19"/>
-      <c r="G229" s="11"/>
-      <c r="H229" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I229" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J229" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K229" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A230" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B230" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C230" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="D230" s="16">
-        <v>3</v>
-      </c>
-      <c r="E230" s="21" t="s">
-        <v>473</v>
-      </c>
-      <c r="F230" s="21"/>
-      <c r="G230" s="9"/>
-      <c r="H230" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I230" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J230" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K230" s="22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B231" s="95" t="s">
-        <v>225</v>
-      </c>
-      <c r="C231" s="107" t="s">
-        <v>226</v>
-      </c>
-      <c r="D231" s="114">
-        <v>3</v>
-      </c>
-      <c r="E231" s="107" t="s">
-        <v>129</v>
-      </c>
-      <c r="F231" s="107"/>
-      <c r="G231" s="52"/>
-      <c r="H231" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="I231" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="J231" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="K231" s="122" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A232" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B232" s="100" t="s">
-        <v>225</v>
-      </c>
-      <c r="C232" s="108" t="s">
-        <v>226</v>
-      </c>
-      <c r="D232" s="116">
-        <v>3</v>
-      </c>
-      <c r="E232" s="108" t="s">
-        <v>129</v>
-      </c>
-      <c r="F232" s="108"/>
-      <c r="G232" s="32"/>
-      <c r="H232" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="I232" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J232" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="K232" s="123" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A233" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B233" s="99" t="s">
-        <v>225</v>
-      </c>
-      <c r="C233" s="58" t="s">
-        <v>226</v>
-      </c>
-      <c r="D233" s="118">
-        <v>3</v>
-      </c>
-      <c r="E233" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="F233" s="58"/>
-      <c r="G233" s="42"/>
-      <c r="H233" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="I233" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="J233" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="K233" s="61" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A234" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B234" s="96" t="s">
-        <v>225</v>
-      </c>
-      <c r="C234" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="D234" s="113">
-        <v>3</v>
-      </c>
-      <c r="E234" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="F234" s="57"/>
-      <c r="G234" s="15"/>
-      <c r="H234" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I234" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J234" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K234" s="60" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A235" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B235" s="94" t="s">
-        <v>225</v>
-      </c>
-      <c r="C235" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="D235" s="17">
-        <v>3</v>
-      </c>
-      <c r="E235" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F235" s="19"/>
-      <c r="G235" s="11"/>
-      <c r="H235" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I235" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J235" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K235" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A236" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B236" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C236" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D236" s="16">
+      <c r="B237" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="C237" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D237" s="10">
         <v>3.5</v>
       </c>
-      <c r="E236" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="F236" s="21"/>
-      <c r="G236" s="9"/>
-      <c r="H236" s="22"/>
-      <c r="I236" s="9"/>
-      <c r="J236" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K236" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A237" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B237" t="s">
-        <v>230</v>
-      </c>
-      <c r="C237" t="s">
-        <v>231</v>
-      </c>
-      <c r="D237" s="35">
-        <v>3.5</v>
-      </c>
-      <c r="E237" t="s">
+      <c r="E237" s="19" t="s">
         <v>232</v>
       </c>
+      <c r="F237" s="19"/>
       <c r="I237" s="20" t="s">
         <v>14</v>
       </c>
@@ -9310,48 +9300,52 @@
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A238" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B238" t="s">
+      <c r="A238" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B238" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="C238" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D238" s="8">
+        <v>3</v>
+      </c>
+      <c r="E238" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F238" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="C238" t="s">
-        <v>231</v>
-      </c>
-      <c r="D238" s="35">
+      <c r="G238" s="22"/>
+      <c r="H238" s="22"/>
+      <c r="I238" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J238" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K238" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A239" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B239" t="s">
+        <v>236</v>
+      </c>
+      <c r="C239" t="s">
+        <v>237</v>
+      </c>
+      <c r="D239" s="35">
         <v>3.5</v>
       </c>
-      <c r="E238" t="s">
-        <v>232</v>
-      </c>
-      <c r="I238" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J238" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K238" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A239" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B239" s="54" t="s">
-        <v>230</v>
-      </c>
-      <c r="C239" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="D239" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="E239" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F239" s="19"/>
+      <c r="E239" t="s">
+        <v>127</v>
+      </c>
       <c r="I239" s="20" t="s">
         <v>14</v>
       </c>
@@ -9363,33 +9357,29 @@
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A240" s="1" t="s">
+      <c r="A240" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B240" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="C240" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="D240" s="8">
-        <v>3</v>
-      </c>
-      <c r="E240" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="F240" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="G240" s="22"/>
-      <c r="H240" s="22"/>
-      <c r="I240" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J240" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K240" s="22" t="s">
+      <c r="B240" s="54" t="s">
+        <v>236</v>
+      </c>
+      <c r="C240" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="D240" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="E240" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F240" s="19"/>
+      <c r="I240" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J240" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K240" s="20" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9398,16 +9388,16 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C241" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D241" s="35">
         <v>3.5</v>
       </c>
       <c r="E241" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="I241" s="20" t="s">
         <v>14</v>
@@ -9420,29 +9410,31 @@
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
+      <c r="A242" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B242" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="C242" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="D242" s="10">
+      <c r="B242" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="C242" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D242" s="8">
         <v>3.5</v>
       </c>
-      <c r="E242" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="F242" s="19"/>
-      <c r="I242" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J242" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K242" s="20" t="s">
+      <c r="E242" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="F242" s="21"/>
+      <c r="G242" s="22"/>
+      <c r="H242" s="22"/>
+      <c r="I242" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J242" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K242" s="22" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9451,16 +9443,16 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="C243" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D243" s="35">
         <v>3.5</v>
       </c>
       <c r="E243" t="s">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="I243" s="20" t="s">
         <v>14</v>
@@ -9473,57 +9465,58 @@
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A244" s="1" t="s">
+      <c r="A244" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B244" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="C244" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="D244" s="16">
+      <c r="B244" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C244" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="D244" s="17">
         <v>3.5</v>
       </c>
-      <c r="E244" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="F244" s="21"/>
-      <c r="G244" s="22"/>
-      <c r="H244" s="22"/>
-      <c r="I244" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J244" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K244" s="22" t="s">
+      <c r="E244" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F244" s="19"/>
+      <c r="I244" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J244" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K244" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A245" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B245" t="s">
-        <v>49</v>
-      </c>
-      <c r="C245" t="s">
-        <v>241</v>
-      </c>
-      <c r="D245" s="59">
+      <c r="A245" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B245" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="C245" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D245" s="16">
         <v>3.5</v>
       </c>
-      <c r="E245" t="s">
-        <v>135</v>
-      </c>
-      <c r="I245" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J245" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K245" s="20" t="s">
+      <c r="E245" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="F245" s="21"/>
+      <c r="G245" s="22"/>
+      <c r="H245" s="22"/>
+      <c r="I245" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J245" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K245" s="22" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9532,18 +9525,21 @@
         <v>72</v>
       </c>
       <c r="B246" s="54" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="C246" s="19" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D246" s="17">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E246" s="19" t="s">
-        <v>135</v>
+        <v>247</v>
       </c>
       <c r="F246" s="19"/>
+      <c r="H246" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="I246" s="20" t="s">
         <v>14</v>
       </c>
@@ -9555,61 +9551,52 @@
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A247" s="1" t="s">
+      <c r="A247" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B247" t="s">
+        <v>248</v>
+      </c>
+      <c r="C247" t="s">
+        <v>249</v>
+      </c>
+      <c r="D247" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+      <c r="I247" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K247" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A248" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B247" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="C247" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D247" s="16">
+      <c r="B248" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="C248" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D248" s="16">
         <v>3.5</v>
       </c>
-      <c r="E247" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="F247" s="21"/>
-      <c r="G247" s="22"/>
-      <c r="H247" s="22"/>
-      <c r="I247" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J247" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K247" s="22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A248" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B248" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="C248" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="D248" s="17">
-        <v>3.75</v>
-      </c>
-      <c r="E248" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="F248" s="19"/>
-      <c r="H248" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I248" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J248" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K248" s="20" t="s">
+      <c r="E248" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="F248" s="21"/>
+      <c r="G248" s="22"/>
+      <c r="H248" s="22"/>
+      <c r="I248" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J248" s="22"/>
+      <c r="K248" s="22" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9618,18 +9605,24 @@
         <v>20</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C249" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D249" s="59">
         <v>3.5</v>
       </c>
       <c r="E249" t="s">
-        <v>250</v>
+        <v>253</v>
+      </c>
+      <c r="H249" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="I249" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J249" s="20" t="s">
         <v>14</v>
       </c>
       <c r="K249" s="11" t="s">
@@ -9637,85 +9630,83 @@
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A250" s="55" t="s">
+      <c r="A250" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B250" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="C250" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="D250" s="16">
+      <c r="B250" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C250" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D250" s="17">
         <v>3.5</v>
       </c>
-      <c r="E250" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="F250" s="21"/>
-      <c r="G250" s="22"/>
-      <c r="H250" s="22"/>
-      <c r="I250" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J250" s="22"/>
-      <c r="K250" s="9" t="s">
+      <c r="E250" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F250" s="19"/>
+      <c r="H250" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I250" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J250" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K250" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A251" s="78" t="s">
+      <c r="A251" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B251" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="C251" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="D251" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="E251" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="F251" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="G251" s="22"/>
+      <c r="H251" s="22"/>
+      <c r="I251" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J251" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K251" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A252" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B251" t="s">
-        <v>251</v>
-      </c>
-      <c r="C251" t="s">
-        <v>252</v>
-      </c>
-      <c r="D251" s="59">
+      <c r="B252" t="s">
+        <v>257</v>
+      </c>
+      <c r="C252" t="s">
+        <v>258</v>
+      </c>
+      <c r="D252" s="59">
         <v>3.5</v>
       </c>
-      <c r="E251" t="s">
-        <v>253</v>
-      </c>
-      <c r="H251" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I251" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J251" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K251" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A252" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B252" s="54" t="s">
-        <v>251</v>
-      </c>
-      <c r="C252" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D252" s="17">
-        <v>3.5</v>
-      </c>
-      <c r="E252" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="F252" s="19"/>
-      <c r="H252" s="20" t="s">
-        <v>14</v>
+      <c r="E252" t="s">
+        <v>259</v>
       </c>
       <c r="I252" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J252" s="20" t="s">
         <v>14</v>
       </c>
       <c r="K252" s="11" t="s">
@@ -9723,51 +9714,43 @@
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A253" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B253" s="55" t="s">
-        <v>254</v>
-      </c>
-      <c r="C253" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="D253" s="16">
-        <v>3.5</v>
-      </c>
-      <c r="E253" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="F253" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="G253" s="22"/>
-      <c r="H253" s="22"/>
-      <c r="I253" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J253" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K253" s="9" t="s">
+      <c r="A253" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B253" t="s">
+        <v>260</v>
+      </c>
+      <c r="C253" t="s">
+        <v>261</v>
+      </c>
+      <c r="D253" s="59">
+        <v>3.75</v>
+      </c>
+      <c r="E253" t="s">
+        <v>262</v>
+      </c>
+      <c r="J253" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K253" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A254" s="78" t="s">
-        <v>20</v>
+      <c r="A254" s="77" t="s">
+        <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C254" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D254" s="59">
         <v>3.5</v>
       </c>
       <c r="E254" t="s">
-        <v>259</v>
+        <v>49</v>
       </c>
       <c r="I254" s="20" t="s">
         <v>14</v>
@@ -9777,118 +9760,126 @@
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A255" s="78" t="s">
+      <c r="A255" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B255" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="C255" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="D255" s="16">
+        <v>3</v>
+      </c>
+      <c r="E255" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="F255" s="21"/>
+      <c r="G255" s="22"/>
+      <c r="H255" s="22"/>
+      <c r="I255" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J255" s="22"/>
+      <c r="K255" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A256" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="B256" s="80" t="s">
+        <v>268</v>
+      </c>
+      <c r="C256" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="D256" s="90">
+        <v>3</v>
+      </c>
+      <c r="E256" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="F256" s="74"/>
+      <c r="G256" s="75"/>
+      <c r="H256" s="75"/>
+      <c r="I256" s="75"/>
+      <c r="J256" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="K256" s="76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A257" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B257" t="s">
+        <v>269</v>
+      </c>
+      <c r="C257" t="s">
+        <v>270</v>
+      </c>
+      <c r="D257" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="G257" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I257" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J257" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K257" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A258" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B255" t="s">
-        <v>260</v>
-      </c>
-      <c r="C255" t="s">
-        <v>261</v>
-      </c>
-      <c r="D255" s="59">
-        <v>3.75</v>
-      </c>
-      <c r="E255" t="s">
-        <v>262</v>
-      </c>
-      <c r="J255" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K255" s="11" t="s">
+      <c r="B258" t="s">
+        <v>269</v>
+      </c>
+      <c r="C258" t="s">
+        <v>270</v>
+      </c>
+      <c r="D258" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="G258" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I258" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J258" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K258" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A256" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B256" t="s">
-        <v>263</v>
-      </c>
-      <c r="C256" t="s">
-        <v>264</v>
-      </c>
-      <c r="D256" s="59">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A259" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B259" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="C259" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="D259" s="17">
         <v>3.5</v>
       </c>
-      <c r="E256" t="s">
-        <v>49</v>
-      </c>
-      <c r="I256" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K256" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A257" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B257" s="55" t="s">
-        <v>265</v>
-      </c>
-      <c r="C257" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="D257" s="16">
-        <v>3</v>
-      </c>
-      <c r="E257" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="F257" s="21"/>
-      <c r="G257" s="22"/>
-      <c r="H257" s="22"/>
-      <c r="I257" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J257" s="22"/>
-      <c r="K257" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A258" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="B258" s="80" t="s">
-        <v>268</v>
-      </c>
-      <c r="C258" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="D258" s="90">
-        <v>3</v>
-      </c>
-      <c r="E258" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="F258" s="74"/>
-      <c r="G258" s="75"/>
-      <c r="H258" s="75"/>
-      <c r="I258" s="75"/>
-      <c r="J258" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="K258" s="76" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A259" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B259" t="s">
-        <v>269</v>
-      </c>
-      <c r="C259" t="s">
-        <v>270</v>
-      </c>
-      <c r="D259" s="59">
-        <v>3.5</v>
-      </c>
+      <c r="E259" s="19"/>
+      <c r="F259" s="19"/>
       <c r="G259" s="20" t="s">
         <v>14</v>
       </c>
@@ -9903,47 +9894,51 @@
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A260" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B260" t="s">
+      <c r="A260" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B260" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C260" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="D260" s="59">
+      <c r="D260" s="16">
         <v>3.5</v>
       </c>
-      <c r="G260" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I260" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J260" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K260" s="11" t="s">
+      <c r="E260" s="21"/>
+      <c r="F260" s="21"/>
+      <c r="G260" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H260" s="22"/>
+      <c r="I260" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J260" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K260" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A261" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B261" s="54" t="s">
-        <v>269</v>
-      </c>
-      <c r="C261" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="D261" s="17">
+      <c r="A261" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B261" t="s">
+        <v>271</v>
+      </c>
+      <c r="C261" t="s">
+        <v>272</v>
+      </c>
+      <c r="D261" s="59">
         <v>3.5</v>
       </c>
-      <c r="E261" s="19"/>
-      <c r="F261" s="19"/>
-      <c r="G261" s="20" t="s">
+      <c r="E261" t="s">
+        <v>273</v>
+      </c>
+      <c r="H261" s="20" t="s">
         <v>14</v>
       </c>
       <c r="I261" s="20" t="s">
@@ -9957,79 +9952,82 @@
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A262" s="55" t="s">
+      <c r="A262" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B262" t="s">
+        <v>271</v>
+      </c>
+      <c r="C262" t="s">
+        <v>272</v>
+      </c>
+      <c r="D262" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="E262" t="s">
+        <v>273</v>
+      </c>
+      <c r="H262" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I262" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J262" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K262" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A263" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B263" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="C263" s="57" t="s">
+        <v>272</v>
+      </c>
+      <c r="D263" s="113">
+        <v>3.5</v>
+      </c>
+      <c r="E263" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="F263" s="57"/>
+      <c r="G263" s="60"/>
+      <c r="H263" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I263" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J263" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K263" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A264" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B262" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="C262" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="D262" s="16">
+      <c r="B264" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C264" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D264" s="17">
         <v>3.5</v>
       </c>
-      <c r="E262" s="21"/>
-      <c r="F262" s="21"/>
-      <c r="G262" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H262" s="22"/>
-      <c r="I262" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J262" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K262" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A263" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B263" t="s">
-        <v>271</v>
-      </c>
-      <c r="C263" t="s">
-        <v>272</v>
-      </c>
-      <c r="D263" s="59">
-        <v>3.5</v>
-      </c>
-      <c r="E263" t="s">
+      <c r="E264" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="H263" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I263" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J263" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K263" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A264" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B264" t="s">
-        <v>271</v>
-      </c>
-      <c r="C264" t="s">
-        <v>272</v>
-      </c>
-      <c r="D264" s="59">
-        <v>3.5</v>
-      </c>
-      <c r="E264" t="s">
-        <v>273</v>
-      </c>
+      <c r="F264" s="19"/>
       <c r="H264" s="20" t="s">
         <v>14</v>
       </c>
@@ -10044,55 +10042,46 @@
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A265" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B265" s="53" t="s">
-        <v>271</v>
-      </c>
-      <c r="C265" s="57" t="s">
-        <v>272</v>
-      </c>
-      <c r="D265" s="113">
-        <v>3.5</v>
-      </c>
-      <c r="E265" s="57" t="s">
-        <v>273</v>
-      </c>
-      <c r="F265" s="57"/>
-      <c r="G265" s="60"/>
-      <c r="H265" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I265" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J265" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K265" s="15" t="s">
+      <c r="A265" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B265" t="s">
+        <v>274</v>
+      </c>
+      <c r="C265" t="s">
+        <v>275</v>
+      </c>
+      <c r="D265" s="59">
+        <v>3</v>
+      </c>
+      <c r="E265" t="s">
+        <v>276</v>
+      </c>
+      <c r="I265" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J265" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K265" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A266" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B266" s="54" t="s">
-        <v>271</v>
-      </c>
-      <c r="C266" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="D266" s="17">
-        <v>3.5</v>
-      </c>
-      <c r="E266" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="F266" s="19"/>
-      <c r="H266" s="20" t="s">
-        <v>14</v>
+      <c r="A266" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B266" t="s">
+        <v>274</v>
+      </c>
+      <c r="C266" t="s">
+        <v>275</v>
+      </c>
+      <c r="D266" s="59">
+        <v>3</v>
+      </c>
+      <c r="E266" t="s">
+        <v>276</v>
       </c>
       <c r="I266" s="20" t="s">
         <v>14</v>
@@ -10105,21 +10094,22 @@
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A267" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B267" t="s">
+      <c r="A267" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B267" s="54" t="s">
         <v>274</v>
       </c>
-      <c r="C267" t="s">
+      <c r="C267" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="D267" s="59">
-        <v>3</v>
-      </c>
-      <c r="E267" t="s">
+      <c r="D267" s="17">
+        <v>3</v>
+      </c>
+      <c r="E267" s="19" t="s">
         <v>276</v>
       </c>
+      <c r="F267" s="19"/>
       <c r="I267" s="20" t="s">
         <v>14</v>
       </c>
@@ -10131,52 +10121,54 @@
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A268" s="78" t="s">
+      <c r="A268" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B268" s="55" t="s">
+        <v>274</v>
+      </c>
+      <c r="C268" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="D268" s="16">
+        <v>3</v>
+      </c>
+      <c r="E268" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F268" s="21"/>
+      <c r="G268" s="22"/>
+      <c r="H268" s="22"/>
+      <c r="I268" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J268" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K268" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A269" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B268" t="s">
-        <v>274</v>
-      </c>
-      <c r="C268" t="s">
-        <v>275</v>
-      </c>
-      <c r="D268" s="59">
-        <v>3</v>
-      </c>
-      <c r="E268" t="s">
-        <v>276</v>
-      </c>
-      <c r="I268" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J268" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K268" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A269" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B269" s="54" t="s">
-        <v>274</v>
-      </c>
-      <c r="C269" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="D269" s="17">
-        <v>3</v>
-      </c>
-      <c r="E269" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="F269" s="19"/>
+      <c r="B269" t="s">
+        <v>259</v>
+      </c>
+      <c r="C269" t="s">
+        <v>277</v>
+      </c>
+      <c r="D269" s="59">
+        <v>3</v>
+      </c>
+      <c r="E269" t="s">
+        <v>278</v>
+      </c>
+      <c r="G269" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="I269" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J269" s="20" t="s">
         <v>14</v>
       </c>
       <c r="K269" s="11" t="s">
@@ -10184,50 +10176,51 @@
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A270" s="55" t="s">
+      <c r="A270" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B270" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="C270" s="57" t="s">
+        <v>277</v>
+      </c>
+      <c r="D270" s="113">
+        <v>3</v>
+      </c>
+      <c r="E270" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F270" s="57"/>
+      <c r="G270" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="H270" s="60"/>
+      <c r="I270" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J270" s="60"/>
+      <c r="K270" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A271" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B270" s="55" t="s">
-        <v>274</v>
-      </c>
-      <c r="C270" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="D270" s="16">
-        <v>3</v>
-      </c>
-      <c r="E270" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F270" s="21"/>
-      <c r="G270" s="22"/>
-      <c r="H270" s="22"/>
-      <c r="I270" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J270" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K270" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A271" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B271" t="s">
+      <c r="B271" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="C271" t="s">
+      <c r="C271" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="D271" s="59">
-        <v>3</v>
-      </c>
-      <c r="E271" t="s">
+      <c r="D271" s="17">
+        <v>3</v>
+      </c>
+      <c r="E271" s="19" t="s">
         <v>278</v>
       </c>
+      <c r="F271" s="19"/>
       <c r="G271" s="20" t="s">
         <v>14</v>
       </c>
@@ -10239,52 +10232,49 @@
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A272" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B272" s="53" t="s">
+      <c r="A272" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B272" t="s">
+        <v>279</v>
+      </c>
+      <c r="C272" t="s">
+        <v>280</v>
+      </c>
+      <c r="D272" s="59">
+        <v>1</v>
+      </c>
+      <c r="F272" t="s">
         <v>259</v>
       </c>
-      <c r="C272" s="57" t="s">
-        <v>277</v>
-      </c>
-      <c r="D272" s="113">
-        <v>3</v>
-      </c>
-      <c r="E272" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="F272" s="57"/>
-      <c r="G272" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H272" s="60"/>
-      <c r="I272" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J272" s="60"/>
-      <c r="K272" s="15" t="s">
+      <c r="G272" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I272" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K272" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="54" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B273" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="C273" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="D273" s="17">
+        <v>1</v>
+      </c>
+      <c r="E273" s="19"/>
+      <c r="F273" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="C273" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="D273" s="17">
-        <v>3</v>
-      </c>
-      <c r="E273" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F273" s="19"/>
-      <c r="G273" s="20" t="s">
+      <c r="G273" s="60" t="s">
         <v>14</v>
       </c>
       <c r="I273" s="20" t="s">
@@ -10295,52 +10285,57 @@
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A274" s="78" t="s">
+      <c r="A274" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B274" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="C274" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D274" s="16">
+        <v>1</v>
+      </c>
+      <c r="E274" s="21"/>
+      <c r="F274" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="G274" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H274" s="22"/>
+      <c r="I274" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J274" s="22"/>
+      <c r="K274" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A275" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B274" t="s">
-        <v>279</v>
-      </c>
-      <c r="C274" t="s">
-        <v>280</v>
-      </c>
-      <c r="D274" s="59">
-        <v>1</v>
-      </c>
-      <c r="F274" t="s">
-        <v>259</v>
-      </c>
-      <c r="G274" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I274" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K274" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A275" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B275" s="54" t="s">
-        <v>279</v>
-      </c>
-      <c r="C275" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="D275" s="17">
-        <v>1</v>
-      </c>
-      <c r="E275" s="19"/>
-      <c r="F275" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="G275" s="60" t="s">
+      <c r="B275" t="s">
+        <v>281</v>
+      </c>
+      <c r="C275" t="s">
+        <v>282</v>
+      </c>
+      <c r="D275" s="59">
+        <v>3.5</v>
+      </c>
+      <c r="E275" t="s">
+        <v>283</v>
+      </c>
+      <c r="H275" s="20" t="s">
         <v>14</v>
       </c>
       <c r="I275" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J275" s="20" t="s">
         <v>14</v>
       </c>
       <c r="K275" s="11" t="s">
@@ -10348,50 +10343,53 @@
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A276" s="55" t="s">
+      <c r="A276" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B276" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="C276" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="D276" s="113">
+        <v>3.5</v>
+      </c>
+      <c r="E276" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="F276" s="57"/>
+      <c r="G276" s="60"/>
+      <c r="H276" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I276" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J276" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K276" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A277" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B276" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="C276" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="D276" s="16">
-        <v>1</v>
-      </c>
-      <c r="E276" s="21"/>
-      <c r="F276" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="G276" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H276" s="22"/>
-      <c r="I276" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J276" s="22"/>
-      <c r="K276" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A277" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B277" t="s">
+      <c r="B277" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="C277" t="s">
+      <c r="C277" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="D277" s="59">
+      <c r="D277" s="17">
         <v>3.5</v>
       </c>
-      <c r="E277" t="s">
+      <c r="E277" s="19" t="s">
         <v>283</v>
       </c>
+      <c r="F277" s="19"/>
       <c r="H277" s="20" t="s">
         <v>14</v>
       </c>
@@ -10406,108 +10404,105 @@
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A278" s="53" t="s">
+      <c r="A278" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B278" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="C278" s="57" t="s">
-        <v>282</v>
-      </c>
-      <c r="D278" s="113">
+      <c r="B278" s="54" t="s">
+        <v>284</v>
+      </c>
+      <c r="C278" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="D278" s="17">
+        <v>3</v>
+      </c>
+      <c r="E278" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="F278" s="19"/>
+      <c r="I278" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J278" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K278" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A279" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B279" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="C279" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="D279" s="16">
+        <v>3</v>
+      </c>
+      <c r="E279" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="F279" s="21"/>
+      <c r="G279" s="22"/>
+      <c r="H279" s="22"/>
+      <c r="I279" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J279" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K279" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A280" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B280" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="C280" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D280" s="16">
         <v>3.5</v>
       </c>
-      <c r="E278" s="57" t="s">
-        <v>283</v>
-      </c>
-      <c r="F278" s="57"/>
-      <c r="G278" s="60"/>
-      <c r="H278" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I278" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J278" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K278" s="15" t="s">
+      <c r="E280" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="F280" s="21"/>
+      <c r="G280" s="22"/>
+      <c r="H280" s="22"/>
+      <c r="I280" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J280" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K280" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A279" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B279" s="54" t="s">
-        <v>281</v>
-      </c>
-      <c r="C279" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="D279" s="17">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A281" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B281" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="C281" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D281" s="16">
         <v>3.5</v>
       </c>
-      <c r="E279" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="F279" s="19"/>
-      <c r="H279" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I279" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J279" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K279" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A280" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B280" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="C280" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="D280" s="17">
-        <v>3</v>
-      </c>
-      <c r="E280" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="F280" s="19"/>
-      <c r="I280" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J280" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K280" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A281" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B281" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="C281" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="D281" s="16">
-        <v>3</v>
-      </c>
       <c r="E281" s="21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F281" s="21"/>
       <c r="G281" s="22"/>
@@ -10523,8 +10518,8 @@
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A282" s="77" t="s">
-        <v>16</v>
+      <c r="A282" s="92" t="s">
+        <v>21</v>
       </c>
       <c r="B282" s="55" t="s">
         <v>287</v>
@@ -10552,8 +10547,8 @@
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A283" s="78" t="s">
-        <v>20</v>
+      <c r="A283" s="53" t="s">
+        <v>11</v>
       </c>
       <c r="B283" s="55" t="s">
         <v>287</v>
@@ -10581,8 +10576,8 @@
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A284" s="92" t="s">
-        <v>21</v>
+      <c r="A284" s="55" t="s">
+        <v>72</v>
       </c>
       <c r="B284" s="55" t="s">
         <v>287</v>
@@ -10610,446 +10605,442 @@
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A285" s="53" t="s">
+      <c r="A285" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B285" s="93" t="s">
+        <v>126</v>
+      </c>
+      <c r="C285" s="107" t="s">
+        <v>290</v>
+      </c>
+      <c r="D285" s="114">
+        <v>3</v>
+      </c>
+      <c r="E285" s="107"/>
+      <c r="F285" s="107" t="s">
+        <v>129</v>
+      </c>
+      <c r="G285" s="122"/>
+      <c r="H285" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="I285" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="J285" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="K285" s="52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A286" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B286" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C286" s="108" t="s">
+        <v>290</v>
+      </c>
+      <c r="D286" s="116">
+        <v>3</v>
+      </c>
+      <c r="E286" s="108"/>
+      <c r="F286" s="108" t="s">
+        <v>129</v>
+      </c>
+      <c r="G286" s="123"/>
+      <c r="H286" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="I286" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="J286" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="K286" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A287" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B287" s="79" t="s">
+        <v>126</v>
+      </c>
+      <c r="C287" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="D287" s="118">
+        <v>3</v>
+      </c>
+      <c r="E287" s="58"/>
+      <c r="F287" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="G287" s="61"/>
+      <c r="H287" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I287" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="J287" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="K287" s="42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A288" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B285" s="55" t="s">
-        <v>287</v>
-      </c>
-      <c r="C285" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D285" s="16">
-        <v>3.5</v>
-      </c>
-      <c r="E285" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="F285" s="21"/>
-      <c r="G285" s="22"/>
-      <c r="H285" s="22"/>
-      <c r="I285" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J285" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K285" s="9" t="s">
+      <c r="B288" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C288" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="D288" s="113">
+        <v>3</v>
+      </c>
+      <c r="E288" s="57"/>
+      <c r="F288" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="G288" s="60"/>
+      <c r="H288" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I288" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J288" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K288" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A289" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B289" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="C289" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="D289" s="17">
+        <v>3</v>
+      </c>
+      <c r="E289" s="19"/>
+      <c r="F289" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H289" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I289" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J289" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K289" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A290" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B290" s="77" t="s">
+        <v>291</v>
+      </c>
+      <c r="C290" s="105" t="s">
+        <v>292</v>
+      </c>
+      <c r="D290" s="115">
+        <v>3</v>
+      </c>
+      <c r="E290" s="105" t="s">
+        <v>474</v>
+      </c>
+      <c r="F290" s="105"/>
+      <c r="G290" s="121"/>
+      <c r="H290" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="I290" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="J290" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="K290" s="46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A291" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B291" s="97" t="s">
+        <v>291</v>
+      </c>
+      <c r="C291" s="109" t="s">
+        <v>292</v>
+      </c>
+      <c r="D291" s="117">
+        <v>3</v>
+      </c>
+      <c r="E291" s="109" t="s">
+        <v>474</v>
+      </c>
+      <c r="F291" s="109"/>
+      <c r="G291" s="124"/>
+      <c r="H291" s="124" t="s">
+        <v>14</v>
+      </c>
+      <c r="I291" s="124" t="s">
+        <v>14</v>
+      </c>
+      <c r="J291" s="124" t="s">
+        <v>14</v>
+      </c>
+      <c r="K291" s="26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A292" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B292" s="92" t="s">
+        <v>291</v>
+      </c>
+      <c r="C292" s="110" t="s">
+        <v>292</v>
+      </c>
+      <c r="D292" s="59">
+        <v>3</v>
+      </c>
+      <c r="E292" s="110" t="s">
+        <v>474</v>
+      </c>
+      <c r="F292" s="110"/>
+      <c r="G292" s="125"/>
+      <c r="H292" s="125" t="s">
+        <v>14</v>
+      </c>
+      <c r="I292" s="125" t="s">
+        <v>14</v>
+      </c>
+      <c r="J292" s="125" t="s">
+        <v>14</v>
+      </c>
+      <c r="K292" s="36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A293" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B293" s="54" t="s">
+        <v>291</v>
+      </c>
+      <c r="C293" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="D293" s="17">
+        <v>3</v>
+      </c>
+      <c r="E293" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="F293" s="19"/>
+      <c r="H293" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I293" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J293" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K293" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A294" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B294" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C294" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D294" s="16">
+        <v>3</v>
+      </c>
+      <c r="E294" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="F294" s="21"/>
+      <c r="G294" s="22"/>
+      <c r="H294" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I294" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J294" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K294" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A295" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" t="s">
+        <v>293</v>
+      </c>
+      <c r="C295" t="s">
+        <v>294</v>
+      </c>
+      <c r="D295" s="59">
+        <v>4</v>
+      </c>
+      <c r="F295" t="s">
+        <v>475</v>
+      </c>
+      <c r="I295" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J295" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K295" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A286" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B286" s="55" t="s">
-        <v>287</v>
-      </c>
-      <c r="C286" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D286" s="16">
-        <v>3.5</v>
-      </c>
-      <c r="E286" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="F286" s="21"/>
-      <c r="G286" s="22"/>
-      <c r="H286" s="22"/>
-      <c r="I286" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J286" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K286" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A287" s="77" t="s">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A296" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B296" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="C296" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D296" s="113">
+        <v>3</v>
+      </c>
+      <c r="E296" s="57"/>
+      <c r="F296" s="57"/>
+      <c r="G296" s="60"/>
+      <c r="H296" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I296" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J296" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K296" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A297" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B287" s="93" t="s">
-        <v>126</v>
-      </c>
-      <c r="C287" s="107" t="s">
-        <v>290</v>
-      </c>
-      <c r="D287" s="114">
-        <v>3</v>
-      </c>
-      <c r="E287" s="107"/>
-      <c r="F287" s="107" t="s">
-        <v>129</v>
-      </c>
-      <c r="G287" s="122"/>
-      <c r="H287" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="I287" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J287" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="K287" s="52" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A288" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B288" s="78" t="s">
-        <v>126</v>
-      </c>
-      <c r="C288" s="108" t="s">
-        <v>290</v>
-      </c>
-      <c r="D288" s="116">
-        <v>3</v>
-      </c>
-      <c r="E288" s="108"/>
-      <c r="F288" s="108" t="s">
-        <v>129</v>
-      </c>
-      <c r="G288" s="123"/>
-      <c r="H288" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="I288" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="J288" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="K288" s="32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A289" s="92" t="s">
+      <c r="B297" t="s">
+        <v>296</v>
+      </c>
+      <c r="C297" t="s">
+        <v>297</v>
+      </c>
+      <c r="D297" s="59">
+        <v>3</v>
+      </c>
+      <c r="G297" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H297" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I297" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J297" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K297" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A298" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B289" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="C289" s="58" t="s">
-        <v>290</v>
-      </c>
-      <c r="D289" s="118">
-        <v>3</v>
-      </c>
-      <c r="E289" s="58"/>
-      <c r="F289" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="G289" s="61"/>
-      <c r="H289" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="I289" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="J289" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="K289" s="42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A290" s="53" t="s">
+      <c r="B298" t="s">
+        <v>298</v>
+      </c>
+      <c r="C298" t="s">
+        <v>297</v>
+      </c>
+      <c r="D298" s="59">
+        <v>3</v>
+      </c>
+      <c r="G298" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H298" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I298" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J298" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K298" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A299" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B290" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C290" s="57" t="s">
-        <v>290</v>
-      </c>
-      <c r="D290" s="113">
-        <v>3</v>
-      </c>
-      <c r="E290" s="57"/>
-      <c r="F290" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="G290" s="60"/>
-      <c r="H290" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I290" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J290" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K290" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A291" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B291" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="C291" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="D291" s="17">
-        <v>3</v>
-      </c>
-      <c r="E291" s="19"/>
-      <c r="F291" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="H291" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I291" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J291" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K291" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A292" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B292" s="77" t="s">
-        <v>291</v>
-      </c>
-      <c r="C292" s="105" t="s">
-        <v>292</v>
-      </c>
-      <c r="D292" s="115">
-        <v>3</v>
-      </c>
-      <c r="E292" s="105" t="s">
-        <v>474</v>
-      </c>
-      <c r="F292" s="105"/>
-      <c r="G292" s="121"/>
-      <c r="H292" s="121" t="s">
-        <v>14</v>
-      </c>
-      <c r="I292" s="121" t="s">
-        <v>14</v>
-      </c>
-      <c r="J292" s="121" t="s">
-        <v>14</v>
-      </c>
-      <c r="K292" s="46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A293" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B293" s="97" t="s">
-        <v>291</v>
-      </c>
-      <c r="C293" s="109" t="s">
-        <v>292</v>
-      </c>
-      <c r="D293" s="117">
-        <v>3</v>
-      </c>
-      <c r="E293" s="109" t="s">
-        <v>474</v>
-      </c>
-      <c r="F293" s="109"/>
-      <c r="G293" s="124"/>
-      <c r="H293" s="124" t="s">
-        <v>14</v>
-      </c>
-      <c r="I293" s="124" t="s">
-        <v>14</v>
-      </c>
-      <c r="J293" s="124" t="s">
-        <v>14</v>
-      </c>
-      <c r="K293" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A294" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B294" s="92" t="s">
-        <v>291</v>
-      </c>
-      <c r="C294" s="110" t="s">
-        <v>292</v>
-      </c>
-      <c r="D294" s="59">
-        <v>3</v>
-      </c>
-      <c r="E294" s="110" t="s">
-        <v>474</v>
-      </c>
-      <c r="F294" s="110"/>
-      <c r="G294" s="125"/>
-      <c r="H294" s="125" t="s">
-        <v>14</v>
-      </c>
-      <c r="I294" s="125" t="s">
-        <v>14</v>
-      </c>
-      <c r="J294" s="125" t="s">
-        <v>14</v>
-      </c>
-      <c r="K294" s="36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A295" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B295" s="54" t="s">
-        <v>291</v>
-      </c>
-      <c r="C295" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="D295" s="17">
-        <v>3</v>
-      </c>
-      <c r="E295" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="F295" s="19"/>
-      <c r="H295" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I295" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J295" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K295" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A296" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B296" s="55" t="s">
-        <v>291</v>
-      </c>
-      <c r="C296" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="D296" s="16">
-        <v>3</v>
-      </c>
-      <c r="E296" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="F296" s="21"/>
-      <c r="G296" s="22"/>
-      <c r="H296" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I296" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J296" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K296" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A297" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B297" t="s">
-        <v>293</v>
-      </c>
-      <c r="C297" t="s">
-        <v>294</v>
-      </c>
-      <c r="D297" s="59">
-        <v>4</v>
-      </c>
-      <c r="F297" t="s">
-        <v>475</v>
-      </c>
-      <c r="I297" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J297" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K297" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A298" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B298" s="53" t="s">
-        <v>295</v>
-      </c>
-      <c r="C298" s="57" t="s">
+      <c r="B299" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="C299" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D298" s="113">
-        <v>3</v>
-      </c>
-      <c r="E298" s="57"/>
-      <c r="F298" s="57"/>
-      <c r="G298" s="60"/>
-      <c r="H298" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I298" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J298" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K298" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A299" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B299" t="s">
-        <v>296</v>
-      </c>
-      <c r="C299" t="s">
-        <v>297</v>
-      </c>
-      <c r="D299" s="59">
-        <v>3</v>
-      </c>
-      <c r="G299" s="20" t="s">
-        <v>14</v>
-      </c>
+      <c r="D299" s="17">
+        <v>3</v>
+      </c>
+      <c r="E299" s="19"/>
+      <c r="F299" s="19"/>
       <c r="H299" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I299" s="20" t="s">
         <v>14</v>
       </c>
       <c r="J299" s="20" t="s">
@@ -11060,21 +11051,20 @@
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A300" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B300" t="s">
-        <v>298</v>
-      </c>
-      <c r="C300" t="s">
-        <v>297</v>
-      </c>
-      <c r="D300" s="59">
-        <v>3</v>
-      </c>
-      <c r="G300" s="20" t="s">
-        <v>14</v>
-      </c>
+      <c r="A300" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B300" s="54" t="s">
+        <v>300</v>
+      </c>
+      <c r="C300" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D300" s="17">
+        <v>3</v>
+      </c>
+      <c r="E300" s="19"/>
+      <c r="F300" s="19"/>
       <c r="H300" s="20" t="s">
         <v>14</v>
       </c>
@@ -11089,21 +11079,25 @@
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A301" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B301" s="54" t="s">
-        <v>299</v>
-      </c>
-      <c r="C301" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D301" s="17">
-        <v>3</v>
-      </c>
-      <c r="E301" s="19"/>
-      <c r="F301" s="19"/>
+      <c r="A301" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B301" t="s">
+        <v>301</v>
+      </c>
+      <c r="C301" t="s">
+        <v>302</v>
+      </c>
+      <c r="D301" s="59">
+        <v>3</v>
+      </c>
+      <c r="G301" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="H301" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I301" s="20" t="s">
         <v>14</v>
       </c>
       <c r="J301" s="20" t="s">
@@ -11114,20 +11108,21 @@
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A302" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B302" s="54" t="s">
-        <v>300</v>
-      </c>
-      <c r="C302" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D302" s="17">
-        <v>3</v>
-      </c>
-      <c r="E302" s="19"/>
-      <c r="F302" s="19"/>
+      <c r="A302" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B302" t="s">
+        <v>303</v>
+      </c>
+      <c r="C302" t="s">
+        <v>302</v>
+      </c>
+      <c r="D302" s="59">
+        <v>3</v>
+      </c>
+      <c r="G302" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="H302" s="20" t="s">
         <v>14</v>
       </c>
@@ -11142,305 +11137,299 @@
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A303" s="77" t="s">
+      <c r="A303" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B303" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="C303" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D303" s="113">
+        <v>3</v>
+      </c>
+      <c r="E303" s="57"/>
+      <c r="F303" s="57"/>
+      <c r="G303" s="60"/>
+      <c r="H303" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I303" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="J303" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="K303" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A304" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B304" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="C304" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D304" s="16">
+        <v>3</v>
+      </c>
+      <c r="E304" s="21"/>
+      <c r="F304" s="21"/>
+      <c r="G304" s="22"/>
+      <c r="H304" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I304" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="J304" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K304" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A305" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B305" t="s">
+        <v>306</v>
+      </c>
+      <c r="C305" t="s">
+        <v>307</v>
+      </c>
+      <c r="D305" s="59">
+        <v>3</v>
+      </c>
+      <c r="G305" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H305" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I305" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J305" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K305" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A306" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B306" s="54" t="s">
+        <v>308</v>
+      </c>
+      <c r="C306" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D306" s="17">
+        <v>3</v>
+      </c>
+      <c r="E306" s="19"/>
+      <c r="F306" s="19"/>
+      <c r="H306" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I306" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J306" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K306" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A307" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B303" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="C303" t="s">
-        <v>302</v>
-      </c>
-      <c r="D303" s="59">
-        <v>3</v>
-      </c>
-      <c r="G303" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H303" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I303" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J303" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K303" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A304" s="92" t="s">
+      <c r="B307" s="93" t="s">
+        <v>309</v>
+      </c>
+      <c r="C307" s="107" t="s">
+        <v>310</v>
+      </c>
+      <c r="D307" s="114">
+        <v>3</v>
+      </c>
+      <c r="E307" s="107"/>
+      <c r="F307" s="107"/>
+      <c r="G307" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="H307" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="I307" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="J307" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="K307" s="52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A308" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B308" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="C308" s="108" t="s">
+        <v>310</v>
+      </c>
+      <c r="D308" s="116">
+        <v>3</v>
+      </c>
+      <c r="E308" s="108"/>
+      <c r="F308" s="108"/>
+      <c r="G308" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="H308" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="I308" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="J308" s="123" t="s">
+        <v>14</v>
+      </c>
+      <c r="K308" s="32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A309" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B304" t="s">
-        <v>303</v>
-      </c>
-      <c r="C304" t="s">
-        <v>302</v>
-      </c>
-      <c r="D304" s="59">
-        <v>3</v>
-      </c>
-      <c r="G304" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H304" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I304" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J304" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K304" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A305" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B305" s="53" t="s">
-        <v>304</v>
-      </c>
-      <c r="C305" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="D305" s="113">
-        <v>3</v>
-      </c>
-      <c r="E305" s="57"/>
-      <c r="F305" s="57"/>
-      <c r="G305" s="60"/>
-      <c r="H305" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I305" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J305" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K305" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A306" s="55" t="s">
+      <c r="B309" s="79" t="s">
+        <v>309</v>
+      </c>
+      <c r="C309" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="D309" s="59">
+        <v>3</v>
+      </c>
+      <c r="E309" s="58"/>
+      <c r="F309" s="58"/>
+      <c r="G309" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H309" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I309" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="J309" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="K309" s="42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A310" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B306" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="C306" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D306" s="16">
-        <v>3</v>
-      </c>
-      <c r="E306" s="21"/>
-      <c r="F306" s="21"/>
-      <c r="G306" s="22"/>
-      <c r="H306" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I306" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J306" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K306" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A307" s="92" t="s">
+      <c r="B310" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="C310" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D310" s="17">
+        <v>3</v>
+      </c>
+      <c r="E310" s="19"/>
+      <c r="F310" s="19"/>
+      <c r="G310" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H310" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I310" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J310" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K310" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A311" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B311" s="55" t="s">
+        <v>311</v>
+      </c>
+      <c r="D311" s="16">
+        <v>16</v>
+      </c>
+      <c r="E311" t="s">
+        <v>312</v>
+      </c>
+      <c r="G311" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I311" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J311" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K311" s="18" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A312" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B312" s="55" t="s">
+        <v>311</v>
+      </c>
+      <c r="D312" s="16">
+        <v>16</v>
+      </c>
+      <c r="E312" t="s">
+        <v>312</v>
+      </c>
+      <c r="G312" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I312" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J312" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K312" s="18" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A313" s="92" t="s">
         <v>21</v>
-      </c>
-      <c r="B307" t="s">
-        <v>306</v>
-      </c>
-      <c r="C307" t="s">
-        <v>307</v>
-      </c>
-      <c r="D307" s="59">
-        <v>3</v>
-      </c>
-      <c r="G307" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H307" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I307" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J307" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K307" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A308" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B308" s="54" t="s">
-        <v>308</v>
-      </c>
-      <c r="C308" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D308" s="17">
-        <v>3</v>
-      </c>
-      <c r="E308" s="19"/>
-      <c r="F308" s="19"/>
-      <c r="H308" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I308" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J308" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K308" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A309" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="B309" s="93" t="s">
-        <v>309</v>
-      </c>
-      <c r="C309" s="107" t="s">
-        <v>310</v>
-      </c>
-      <c r="D309" s="114">
-        <v>3</v>
-      </c>
-      <c r="E309" s="107"/>
-      <c r="F309" s="107"/>
-      <c r="G309" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="H309" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="I309" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J309" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="K309" s="52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A310" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="B310" s="78" t="s">
-        <v>309</v>
-      </c>
-      <c r="C310" s="108" t="s">
-        <v>310</v>
-      </c>
-      <c r="D310" s="116">
-        <v>3</v>
-      </c>
-      <c r="E310" s="108"/>
-      <c r="F310" s="108"/>
-      <c r="G310" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="H310" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="I310" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="J310" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="K310" s="32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A311" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B311" s="79" t="s">
-        <v>309</v>
-      </c>
-      <c r="C311" s="58" t="s">
-        <v>310</v>
-      </c>
-      <c r="D311" s="59">
-        <v>3</v>
-      </c>
-      <c r="E311" s="58"/>
-      <c r="F311" s="58"/>
-      <c r="G311" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H311" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="I311" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="J311" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="K311" s="42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A312" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B312" s="54" t="s">
-        <v>309</v>
-      </c>
-      <c r="C312" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D312" s="17">
-        <v>3</v>
-      </c>
-      <c r="E312" s="19"/>
-      <c r="F312" s="19"/>
-      <c r="G312" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H312" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I312" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J312" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K312" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A313" s="77" t="s">
-        <v>16</v>
       </c>
       <c r="B313" s="55" t="s">
         <v>311</v>
@@ -11465,18 +11454,13 @@
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A314" s="78" t="s">
-        <v>20</v>
+      <c r="A314" t="s">
+        <v>156</v>
       </c>
       <c r="B314" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="D314" s="16">
-        <v>16</v>
-      </c>
-      <c r="E314" t="s">
-        <v>312</v>
-      </c>
+      <c r="D314" s="16"/>
       <c r="G314" s="20" t="s">
         <v>14</v>
       </c>
@@ -11491,17 +11475,17 @@
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A315" s="92" t="s">
-        <v>21</v>
+      <c r="A315" t="s">
+        <v>156</v>
       </c>
       <c r="B315" s="55" t="s">
-        <v>311</v>
+        <v>476</v>
+      </c>
+      <c r="C315" t="s">
+        <v>314</v>
       </c>
       <c r="D315" s="16">
-        <v>16</v>
-      </c>
-      <c r="E315" t="s">
-        <v>312</v>
+        <v>6</v>
       </c>
       <c r="G315" s="20" t="s">
         <v>14</v>
@@ -11512,18 +11496,23 @@
       <c r="J315" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K315" s="18" t="s">
-        <v>313</v>
+      <c r="K315" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
-        <v>156</v>
+      <c r="A316" s="53" t="s">
+        <v>11</v>
       </c>
       <c r="B316" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="D316" s="16"/>
+      <c r="D316" s="16">
+        <v>16</v>
+      </c>
+      <c r="E316" t="s">
+        <v>312</v>
+      </c>
       <c r="G316" s="20" t="s">
         <v>14</v>
       </c>
@@ -11538,18 +11527,13 @@
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A317" s="53" t="s">
-        <v>11</v>
+      <c r="A317" t="s">
+        <v>146</v>
       </c>
       <c r="B317" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="D317" s="16">
-        <v>16</v>
-      </c>
-      <c r="E317" t="s">
-        <v>312</v>
-      </c>
+      <c r="D317" s="16"/>
       <c r="G317" s="20" t="s">
         <v>14</v>
       </c>
@@ -11564,13 +11548,18 @@
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
-        <v>146</v>
+      <c r="A318" s="54" t="s">
+        <v>72</v>
       </c>
       <c r="B318" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="D318" s="16"/>
+      <c r="D318" s="16">
+        <v>16</v>
+      </c>
+      <c r="E318" t="s">
+        <v>312</v>
+      </c>
       <c r="G318" s="20" t="s">
         <v>14</v>
       </c>
@@ -11585,18 +11574,13 @@
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A319" s="54" t="s">
-        <v>72</v>
+      <c r="A319" t="s">
+        <v>155</v>
       </c>
       <c r="B319" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="D319" s="16">
-        <v>16</v>
-      </c>
-      <c r="E319" t="s">
-        <v>312</v>
-      </c>
+      <c r="D319" s="16"/>
       <c r="G319" s="20" t="s">
         <v>14</v>
       </c>
@@ -11611,13 +11595,18 @@
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>155</v>
-      </c>
-      <c r="B320" s="55" t="s">
+      <c r="A320" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B320" s="54" t="s">
+        <v>315</v>
+      </c>
+      <c r="D320" s="17">
+        <v>16</v>
+      </c>
+      <c r="E320" t="s">
         <v>311</v>
       </c>
-      <c r="D320" s="16"/>
       <c r="G320" s="20" t="s">
         <v>14</v>
       </c>
@@ -11632,8 +11621,8 @@
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A321" s="77" t="s">
-        <v>16</v>
+      <c r="A321" s="78" t="s">
+        <v>20</v>
       </c>
       <c r="B321" s="54" t="s">
         <v>315</v>
@@ -11658,8 +11647,8 @@
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A322" s="78" t="s">
-        <v>20</v>
+      <c r="A322" s="92" t="s">
+        <v>21</v>
       </c>
       <c r="B322" s="54" t="s">
         <v>315</v>
@@ -11684,17 +11673,17 @@
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A323" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B323" s="54" t="s">
-        <v>315</v>
-      </c>
-      <c r="D323" s="17">
-        <v>16</v>
-      </c>
-      <c r="E323" t="s">
-        <v>311</v>
+      <c r="A323" t="s">
+        <v>156</v>
+      </c>
+      <c r="B323" s="55" t="s">
+        <v>477</v>
+      </c>
+      <c r="C323" t="s">
+        <v>316</v>
+      </c>
+      <c r="D323" s="16">
+        <v>6</v>
       </c>
       <c r="G323" s="20" t="s">
         <v>14</v>
@@ -11705,8 +11694,8 @@
       <c r="J323" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K323" s="18" t="s">
-        <v>313</v>
+      <c r="K323" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.3">
@@ -12182,7 +12171,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K340" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="K1:K1048576">
     <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="PRG">
       <formula>NOT(ISERROR(SEARCH("PRG",K1)))</formula>
@@ -12197,7 +12185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" style="19" customWidth="1"/>
@@ -12240,15 +12228,24 @@
         <v>332</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="85">
+        <v>46055</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>334</v>
+      </c>
       <c r="E2" s="19" t="s">
         <v>335</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="G2" s="84" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="H2" s="19" t="s">
         <v>333</v>
@@ -12257,79 +12254,68 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
         <v>338</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="G3" s="84" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>147</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E4" s="19" t="s">
+        <v>335</v>
       </c>
       <c r="G4" s="84" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="H4" s="19" t="s">
         <v>341</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="B5" s="19" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="G5" s="84" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6" t="s">
-        <v>341</v>
-      </c>
-      <c r="D6" t="s">
-        <v>334</v>
-      </c>
-      <c r="E6" t="s">
-        <v>335</v>
-      </c>
-      <c r="F6" t="s">
-        <v>279</v>
-      </c>
-      <c r="G6" t="s">
-        <v>478</v>
-      </c>
-      <c r="H6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B6" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G6" s="84" t="s">
+        <v>345</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="19" t="s">
         <v>337</v>
       </c>
     </row>
@@ -12337,11 +12323,17 @@
       <c r="B7" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>287</v>
+      <c r="C7" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>335</v>
       </c>
       <c r="G7" s="84" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="H7" s="19" t="s">
         <v>333</v>
@@ -12350,15 +12342,24 @@
         <v>337</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="19" t="s">
-        <v>342</v>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="85">
+        <v>46055</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>348</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="G8" s="84" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>333</v>
@@ -12367,15 +12368,24 @@
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="19" t="s">
-        <v>344</v>
+    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="85">
+        <v>46055</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>351</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="G9" s="84" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>333</v>
@@ -12384,280 +12394,244 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" t="s">
-        <v>479</v>
-      </c>
-      <c r="H10" t="s">
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="85">
+        <v>46055</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="G10" s="84" t="s">
+        <v>354</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="84" t="s">
+        <v>355</v>
+      </c>
+      <c r="H11" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="I10" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11" t="s">
-        <v>291</v>
-      </c>
-      <c r="G11" t="s">
-        <v>480</v>
-      </c>
-      <c r="H11" t="s">
-        <v>341</v>
-      </c>
-      <c r="I11" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I11" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="19" t="s">
+        <v>338</v>
+      </c>
       <c r="F12" s="19" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="G12" s="84" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="H12" s="19" t="s">
         <v>341</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="85">
-        <v>46055</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>335</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="19" t="s">
+        <v>338</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>313</v>
+        <v>147</v>
       </c>
       <c r="G13" s="84" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>337</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="85">
-        <v>46055</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>348</v>
+      <c r="B14" s="19" t="s">
+        <v>358</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>313</v>
       </c>
       <c r="G14" s="84" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="85">
-        <v>46055</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>351</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="19" t="s">
+        <v>358</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="G15" s="84" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="85">
-        <v>46055</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>335</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="19" t="s">
+        <v>338</v>
       </c>
       <c r="F16" s="19" t="s">
         <v>313</v>
       </c>
       <c r="G16" s="84" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H16" s="19" t="s">
         <v>333</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="201.6" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B17" s="19" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>313</v>
       </c>
       <c r="G17" s="84" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="19" t="s">
-        <v>358</v>
-      </c>
+    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F18" s="19" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G18" s="84" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>341</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E19" s="19" t="s">
+        <v>335</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="G19" s="84" t="s">
-        <v>362</v>
+        <v>35</v>
+      </c>
+      <c r="G19" s="127" t="s">
+        <v>364</v>
       </c>
       <c r="H19" s="19" t="s">
         <v>333</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="G20" s="84" t="s">
-        <v>362</v>
-      </c>
-      <c r="H20" s="19" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20"/>
+      <c r="E20" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" t="s">
+        <v>279</v>
+      </c>
+      <c r="G20" s="128" t="s">
+        <v>480</v>
+      </c>
+      <c r="H20" t="s">
         <v>333</v>
       </c>
-      <c r="I20" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E21" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="G21" s="84" t="s">
-        <v>340</v>
-      </c>
-      <c r="H21" s="19" t="s">
+      <c r="I20" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" t="s">
+        <v>478</v>
+      </c>
+      <c r="H21" t="s">
         <v>341</v>
       </c>
-      <c r="I21" s="19" t="s">
+      <c r="I21" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="G22" s="84" t="s">
-        <v>347</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="I22" s="19" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22" t="s">
+        <v>291</v>
+      </c>
+      <c r="G22" t="s">
+        <v>479</v>
+      </c>
+      <c r="H22" t="s">
+        <v>341</v>
+      </c>
+      <c r="I22" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E23" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F23" s="129" t="s">
-        <v>482</v>
-      </c>
-      <c r="G23" s="128" t="s">
-        <v>481</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I22" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
